--- a/database/event/5528/event_5528_evp_summary.xlsx
+++ b/database/event/5528/event_5528_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.3483</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8453</v>
+        <v>1.7915</v>
       </c>
       <c r="E2" t="n">
         <v>5.6109</v>
@@ -548,7 +548,7 @@
         <v>2.1042</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6097</v>
+        <v>1.5591</v>
       </c>
       <c r="E3" t="n">
         <v>5.0276</v>
@@ -594,7 +594,7 @@
         <v>1.9498</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4607</v>
+        <v>1.4122</v>
       </c>
       <c r="E4" t="n">
         <v>4.6588</v>
@@ -640,7 +640,7 @@
         <v>1.641</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1626</v>
+        <v>1.1181</v>
       </c>
       <c r="E5" t="n">
         <v>3.9208</v>
@@ -686,7 +686,7 @@
         <v>1.32</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8527</v>
+        <v>0.8126</v>
       </c>
       <c r="E6" t="n">
         <v>3.1539</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8575</v>
+        <v>2.8046</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1959</v>
+        <v>1.1738</v>
       </c>
       <c r="D7" t="n">
-        <v>0.733</v>
+        <v>0.6734</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8575</v>
+        <v>2.8046</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8575</v>
+        <v>2.8046</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8575</v>
+        <v>2.8046</v>
       </c>
       <c r="I7" t="n">
         <v>2.9246</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.504</v>
+        <v>2.4576</v>
       </c>
       <c r="C8" t="n">
-        <v>1.048</v>
+        <v>1.0286</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5352</v>
       </c>
       <c r="E8" t="n">
-        <v>2.504</v>
+        <v>2.4576</v>
       </c>
       <c r="F8" t="n">
-        <v>2.504</v>
+        <v>2.4576</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.504</v>
+        <v>2.4576</v>
       </c>
       <c r="I8" t="n">
         <v>2.5628</v>
@@ -824,7 +824,7 @@
         <v>0.9913999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5356</v>
+        <v>0.4998</v>
       </c>
       <c r="E9" t="n">
         <v>2.3688</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.7986</v>
+        <v>1.7852</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7528</v>
+        <v>0.7472</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3052</v>
+        <v>0.2673</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7986</v>
+        <v>1.7852</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7986</v>
+        <v>1.7852</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7986</v>
+        <v>1.7852</v>
       </c>
       <c r="I10" t="n">
         <v>1.8154</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.4192</v>
+        <v>1.4139</v>
       </c>
       <c r="C11" t="n">
-        <v>0.594</v>
+        <v>0.5918</v>
       </c>
       <c r="D11" t="n">
-        <v>0.152</v>
+        <v>0.1194</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4192</v>
+        <v>1.4139</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4192</v>
+        <v>1.4139</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4192</v>
+        <v>1.4139</v>
       </c>
       <c r="I11" t="n">
         <v>1.4258</v>
@@ -962,7 +962,7 @@
         <v>0.5063</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0673</v>
+        <v>0.038</v>
       </c>
       <c r="E12" t="n">
         <v>1.2097</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.0824</v>
+        <v>1.0653</v>
       </c>
       <c r="C13" t="n">
-        <v>0.453</v>
+        <v>0.4459</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0159</v>
+        <v>-0.0195</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0824</v>
+        <v>1.0653</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0824</v>
+        <v>0.8224</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.2429</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0824</v>
+        <v>0.8224</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1078</v>
+        <v>0.6666</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.2429</v>
       </c>
       <c r="K13" t="n">
-        <v>189</v>
+        <v>90</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1078</v>
+        <v>0.9095</v>
       </c>
       <c r="N13" t="n">
-        <v>189</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0653</v>
+        <v>1.0623</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4459</v>
+        <v>0.4446</v>
       </c>
       <c r="D14" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.0207</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0653</v>
+        <v>1.0623</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8224</v>
+        <v>1.0623</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2429</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8224</v>
+        <v>1.0623</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6666</v>
+        <v>1.1078</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2429</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="L14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9095</v>
+        <v>1.1078</v>
       </c>
       <c r="N14" t="n">
-        <v>115</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15">
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0373</v>
+        <v>1.0296</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4341</v>
+        <v>0.4309</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0023</v>
+        <v>-0.0337</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0373</v>
+        <v>1.0296</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0373</v>
+        <v>1.0296</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0373</v>
+        <v>1.0296</v>
       </c>
       <c r="I15" t="n">
         <v>1.047</v>
@@ -1146,7 +1146,7 @@
         <v>0.4155</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0203</v>
+        <v>-0.0484</v>
       </c>
       <c r="E16" t="n">
         <v>0.9927</v>
@@ -1192,7 +1192,7 @@
         <v>0.282</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1491</v>
+        <v>-0.1754</v>
       </c>
       <c r="E17" t="n">
         <v>0.6739000000000001</v>
@@ -1238,7 +1238,7 @@
         <v>0.205</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2235</v>
+        <v>-0.2487</v>
       </c>
       <c r="E18" t="n">
         <v>0.4899</v>
@@ -1284,7 +1284,7 @@
         <v>0.1319</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.294</v>
+        <v>-0.3183</v>
       </c>
       <c r="E19" t="n">
         <v>0.3152</v>
@@ -1330,7 +1330,7 @@
         <v>0.0261</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3962</v>
+        <v>-0.4191</v>
       </c>
       <c r="E20" t="n">
         <v>0.0623</v>
@@ -1376,7 +1376,7 @@
         <v>0.0199</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4022</v>
+        <v>-0.425</v>
       </c>
       <c r="E21" t="n">
         <v>0.0475</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1188</v>
+        <v>-0.1166</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0497</v>
+        <v>-0.0488</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4694</v>
+        <v>-0.4904</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1188</v>
+        <v>-0.1166</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1188</v>
+        <v>-0.1166</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1188</v>
+        <v>-0.1166</v>
       </c>
       <c r="I22" t="n">
         <v>-0.1216</v>
@@ -1468,7 +1468,7 @@
         <v>-0.06619999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4853</v>
+        <v>-0.5069</v>
       </c>
       <c r="E23" t="n">
         <v>-0.1582</v>
@@ -1514,7 +1514,7 @@
         <v>-0.07729999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.496</v>
+        <v>-0.5175</v>
       </c>
       <c r="E24" t="n">
         <v>-0.1847</v>
@@ -1560,7 +1560,7 @@
         <v>-0.08069999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4993</v>
+        <v>-0.5208</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1929</v>
@@ -1606,7 +1606,7 @@
         <v>-0.1302</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.547</v>
+        <v>-0.5679</v>
       </c>
       <c r="E26" t="n">
         <v>-0.3111</v>
@@ -1652,7 +1652,7 @@
         <v>-0.2569</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6693</v>
+        <v>-0.6884</v>
       </c>
       <c r="E27" t="n">
         <v>-0.6138</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6563</v>
+        <v>-0.6514</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2747</v>
+        <v>-0.2726</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6865</v>
+        <v>-0.7034</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6563</v>
+        <v>-0.6514</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6563</v>
+        <v>-0.6514</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6563</v>
+        <v>-0.6514</v>
       </c>
       <c r="I28" t="n">
         <v>-0.6624</v>
@@ -1744,7 +1744,7 @@
         <v>-0.3077</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7184</v>
+        <v>-0.7369</v>
       </c>
       <c r="E29" t="n">
         <v>-0.7353</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7769</v>
+        <v>-0.774</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3252</v>
+        <v>-0.3239</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7352</v>
+        <v>-0.7523</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7769</v>
+        <v>-0.774</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7769</v>
+        <v>-0.774</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7769</v>
+        <v>-0.774</v>
       </c>
       <c r="I30" t="n">
         <v>-0.7805</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8176</v>
+        <v>-0.8145</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3422</v>
+        <v>-0.3409</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7517</v>
+        <v>-0.7684</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8176</v>
+        <v>-0.8145</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8176</v>
+        <v>-0.8145</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8176</v>
+        <v>-0.8145</v>
       </c>
       <c r="I31" t="n">
         <v>-0.8214</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4061</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8133</v>
+        <v>-0.8304</v>
       </c>
       <c r="E32" t="n">
         <v>-0.9702</v>
@@ -1928,7 +1928,7 @@
         <v>-0.4253</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8319</v>
+        <v>-0.8488</v>
       </c>
       <c r="E33" t="n">
         <v>-1.0163</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.1765</v>
+        <v>-1.1721</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4924</v>
+        <v>-0.4906</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8966</v>
+        <v>-0.9109</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1765</v>
+        <v>-1.1721</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.1765</v>
+        <v>-1.1721</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.1765</v>
+        <v>-1.1721</v>
       </c>
       <c r="I34" t="n">
         <v>-1.182</v>
@@ -2020,7 +2020,7 @@
         <v>-0.5147</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9182</v>
+        <v>-0.9339</v>
       </c>
       <c r="E35" t="n">
         <v>-1.2299</v>
@@ -2066,7 +2066,7 @@
         <v>-0.5237000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.9425</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2514</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3585</v>
+        <v>-1.3384</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5686</v>
+        <v>-0.5602</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9702</v>
+        <v>-0.9771</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3585</v>
+        <v>-1.3384</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3585</v>
+        <v>-1.3384</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3585</v>
+        <v>-1.3384</v>
       </c>
       <c r="I37" t="n">
         <v>-1.384</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4591</v>
+        <v>-1.4267</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6107</v>
+        <v>-0.5971</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0108</v>
+        <v>-1.0123</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4591</v>
+        <v>-1.4267</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4591</v>
+        <v>-1.4267</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4591</v>
+        <v>-1.4267</v>
       </c>
       <c r="I38" t="n">
         <v>-1.5003</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4869</v>
+        <v>-1.4649</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6223</v>
+        <v>-0.6131</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.022</v>
+        <v>-1.0275</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4869</v>
+        <v>-1.4649</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4869</v>
+        <v>-1.4649</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4869</v>
+        <v>-1.4649</v>
       </c>
       <c r="I39" t="n">
         <v>-1.5148</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5517</v>
+        <v>-1.5459</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6494</v>
+        <v>-0.647</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0482</v>
+        <v>-1.0598</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5517</v>
+        <v>-1.5459</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5517</v>
+        <v>-1.5459</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5517</v>
+        <v>-1.5459</v>
       </c>
       <c r="I40" t="n">
         <v>-1.5589</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6618000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.0602</v>
+        <v>-1.0739</v>
       </c>
       <c r="E41" t="n">
         <v>-1.5813</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.8419</v>
+        <v>-1.8145</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.7709</v>
+        <v>-0.7594</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.1654</v>
+        <v>-1.1668</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.8419</v>
+        <v>-1.8145</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.8419</v>
+        <v>-1.8145</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.8419</v>
+        <v>-1.8145</v>
       </c>
       <c r="I42" t="n">
         <v>-1.8764</v>
@@ -2388,7 +2388,7 @@
         <v>-1.0441</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.4292</v>
+        <v>-1.4378</v>
       </c>
       <c r="E43" t="n">
         <v>-2.4948</v>
@@ -2434,7 +2434,7 @@
         <v>-1.8664</v>
       </c>
       <c r="D44" t="n">
-        <v>-2.2229</v>
+        <v>-2.2205</v>
       </c>
       <c r="E44" t="n">
         <v>-4.4594</v>

--- a/database/event/5528/event_5528_evp_summary.xlsx
+++ b/database/event/5528/event_5528_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.6109</v>
+        <v>6.2968</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3483</v>
+        <v>2.6354</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7915</v>
+        <v>2.2047</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6109</v>
+        <v>6.2968</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9561</v>
+        <v>2.8784</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6548</v>
+        <v>3.4184</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9561</v>
+        <v>4.6552</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5855</v>
+        <v>2.4205</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6548</v>
+        <v>3.4184</v>
       </c>
       <c r="K2" t="n">
         <v>197</v>
@@ -529,7 +529,7 @@
         <v>134</v>
       </c>
       <c r="M2" t="n">
-        <v>5.2403</v>
+        <v>5.838900000000001</v>
       </c>
       <c r="N2" t="n">
         <v>331</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0276</v>
+        <v>4.4924</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1042</v>
+        <v>1.8802</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5591</v>
+        <v>1.3901</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0276</v>
+        <v>4.4924</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4901</v>
+        <v>2.8261</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5375</v>
+        <v>1.6663</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4901</v>
+        <v>4.471</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8288</v>
+        <v>2.3247</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5375</v>
+        <v>1.6663</v>
       </c>
       <c r="K3" t="n">
         <v>167</v>
@@ -575,7 +575,7 @@
         <v>137</v>
       </c>
       <c r="M3" t="n">
-        <v>4.366300000000001</v>
+        <v>3.991</v>
       </c>
       <c r="N3" t="n">
         <v>304</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6588</v>
+        <v>4.4568</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9498</v>
+        <v>1.8653</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4122</v>
+        <v>1.374</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6588</v>
+        <v>4.4568</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8171</v>
+        <v>3.2281</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8417</v>
+        <v>1.2287</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8171</v>
+        <v>5.8874</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2833</v>
+        <v>3.0612</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8417</v>
+        <v>1.2287</v>
       </c>
       <c r="K4" t="n">
         <v>167</v>
@@ -621,7 +621,7 @@
         <v>137</v>
       </c>
       <c r="M4" t="n">
-        <v>4.125</v>
+        <v>4.289899999999999</v>
       </c>
       <c r="N4" t="n">
         <v>304</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9208</v>
+        <v>3.5662</v>
       </c>
       <c r="C5" t="n">
-        <v>1.641</v>
+        <v>1.4925</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1181</v>
+        <v>0.9719</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9208</v>
+        <v>3.5662</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3876</v>
+        <v>4.045</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4668</v>
+        <v>-0.4788</v>
       </c>
       <c r="H5" t="n">
-        <v>5.0919</v>
+        <v>8.765599999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1271</v>
+        <v>4.5577</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4668</v>
+        <v>-0.4788</v>
       </c>
       <c r="K5" t="n">
         <v>117</v>
@@ -667,7 +667,7 @@
         <v>56</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6603</v>
+        <v>4.0789</v>
       </c>
       <c r="N5" t="n">
         <v>173</v>
@@ -676,1243 +676,1243 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1539</v>
+        <v>2.8158</v>
       </c>
       <c r="C6" t="n">
-        <v>1.32</v>
+        <v>1.1785</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8126</v>
+        <v>0.6332</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1539</v>
+        <v>2.8158</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5718</v>
+        <v>2.4686</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4179</v>
+        <v>0.3472</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5718</v>
+        <v>3.2114</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8951</v>
+        <v>1.6698</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4179</v>
+        <v>0.3472</v>
       </c>
       <c r="K6" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="L6" t="n">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4772</v>
+        <v>2.017</v>
       </c>
       <c r="N6" t="n">
-        <v>250</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8046</v>
+        <v>2.7758</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1738</v>
+        <v>1.1617</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6734</v>
+        <v>0.6151</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8046</v>
+        <v>2.7758</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8046</v>
+        <v>3.1579</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0.3821</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8046</v>
+        <v>5.6401</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9246</v>
+        <v>2.9326</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.3821</v>
       </c>
       <c r="K7" t="n">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9246</v>
+        <v>2.5505</v>
       </c>
       <c r="N7" t="n">
-        <v>170</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4576</v>
+        <v>2.6363</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0286</v>
+        <v>1.1034</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5352</v>
+        <v>0.5521</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4576</v>
+        <v>2.6363</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4576</v>
+        <v>2.6363</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4576</v>
+        <v>2.6363</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5628</v>
+        <v>2.8576</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5628</v>
+        <v>2.8576</v>
       </c>
       <c r="N8" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3688</v>
+        <v>2.5421</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9913999999999999</v>
+        <v>1.0639</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4998</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3688</v>
+        <v>2.5421</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0437</v>
+        <v>2.5421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3251</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0437</v>
+        <v>2.5421</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6565</v>
+        <v>3.1096</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3251</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="L9" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9816</v>
+        <v>3.1096</v>
       </c>
       <c r="N9" t="n">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.7852</v>
+        <v>2.5292</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7472</v>
+        <v>1.0585</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2673</v>
+        <v>0.5038</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7852</v>
+        <v>2.5292</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7852</v>
+        <v>2.5292</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7852</v>
+        <v>2.5292</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8154</v>
+        <v>3.0939</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8154</v>
+        <v>3.0939</v>
       </c>
       <c r="N10" t="n">
-        <v>201</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.4139</v>
+        <v>2.4481</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5918</v>
+        <v>1.0246</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1194</v>
+        <v>0.4672</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4139</v>
+        <v>2.4481</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4139</v>
+        <v>2.4868</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.0387</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4139</v>
+        <v>3.2755</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4258</v>
+        <v>1.7031</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.0387</v>
       </c>
       <c r="K11" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4258</v>
+        <v>1.6644</v>
       </c>
       <c r="N11" t="n">
-        <v>153</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.2097</v>
+        <v>1.9543</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5063</v>
+        <v>0.8179</v>
       </c>
       <c r="D12" t="n">
-        <v>0.038</v>
+        <v>0.2443</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2097</v>
+        <v>1.9543</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5048</v>
+        <v>1.3805</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2951</v>
+        <v>0.5738</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5048</v>
+        <v>1.3805</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2196</v>
+        <v>0.7178</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2951</v>
+        <v>0.5738</v>
       </c>
       <c r="K12" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="L12" t="n">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9245000000000001</v>
+        <v>1.2916</v>
       </c>
       <c r="N12" t="n">
-        <v>304</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.0653</v>
+        <v>1.8769</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4459</v>
+        <v>0.7855</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0195</v>
+        <v>0.2093</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0653</v>
+        <v>1.8769</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8224</v>
+        <v>1.4547</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2429</v>
+        <v>0.4222</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8224</v>
+        <v>1.4547</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6666</v>
+        <v>0.7564</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2429</v>
+        <v>0.4222</v>
       </c>
       <c r="K13" t="n">
-        <v>90</v>
+        <v>156</v>
       </c>
       <c r="L13" t="n">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9095</v>
+        <v>1.1786</v>
       </c>
       <c r="N13" t="n">
-        <v>115</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0623</v>
+        <v>1.7532</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4446</v>
+        <v>0.7338</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0207</v>
+        <v>0.1535</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0623</v>
+        <v>1.7532</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0623</v>
+        <v>1.5617</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.1915</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0623</v>
+        <v>1.5617</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1078</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.1915</v>
       </c>
       <c r="K14" t="n">
-        <v>189</v>
+        <v>90</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1078</v>
+        <v>1.0035</v>
       </c>
       <c r="N14" t="n">
-        <v>189</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0296</v>
+        <v>1.5286</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4309</v>
+        <v>0.6398</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0337</v>
+        <v>0.0521</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0296</v>
+        <v>1.5286</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0296</v>
+        <v>1.5286</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0296</v>
+        <v>1.5286</v>
       </c>
       <c r="I15" t="n">
-        <v>1.047</v>
+        <v>1.5915</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.047</v>
+        <v>1.5915</v>
       </c>
       <c r="N15" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9927</v>
+        <v>1.3288</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4155</v>
+        <v>0.5561</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0484</v>
+        <v>-0.0381</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9927</v>
+        <v>1.3288</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4815</v>
+        <v>2.6138</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5112</v>
+        <v>-1.285</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4815</v>
+        <v>3.7232</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3903</v>
+        <v>1.9359</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5112</v>
+        <v>-1.285</v>
       </c>
       <c r="K16" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="L16" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9015</v>
+        <v>0.6509</v>
       </c>
       <c r="N16" t="n">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6739000000000001</v>
+        <v>1.2278</v>
       </c>
       <c r="C17" t="n">
-        <v>0.282</v>
+        <v>0.5139</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1754</v>
+        <v>-0.0837</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6739000000000001</v>
+        <v>1.2278</v>
       </c>
       <c r="F17" t="n">
-        <v>0.436</v>
+        <v>1.2278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2379</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.436</v>
+        <v>1.2278</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3534</v>
+        <v>1.3309</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2379</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="L17" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5912999999999999</v>
+        <v>1.3309</v>
       </c>
       <c r="N17" t="n">
-        <v>337</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4899</v>
+        <v>1.0642</v>
       </c>
       <c r="C18" t="n">
-        <v>0.205</v>
+        <v>0.4454</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2487</v>
+        <v>-0.1576</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4899</v>
+        <v>1.0642</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1629</v>
+        <v>0.8897</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.673</v>
+        <v>0.1745</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1629</v>
+        <v>0.8897</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7531</v>
+        <v>0.4626</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.673</v>
+        <v>0.1745</v>
       </c>
       <c r="K18" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="L18" t="n">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>0.08010000000000006</v>
+        <v>0.6371</v>
       </c>
       <c r="N18" t="n">
-        <v>304</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3152</v>
+        <v>0.9409</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1319</v>
+        <v>0.3938</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3183</v>
+        <v>-0.2132</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3152</v>
+        <v>0.9409</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2466</v>
+        <v>1.082</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.1411</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2466</v>
+        <v>1.082</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1999</v>
+        <v>0.5626</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.1411</v>
       </c>
       <c r="K19" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="L19" t="n">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2685</v>
+        <v>0.4215</v>
       </c>
       <c r="N19" t="n">
-        <v>212</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0623</v>
+        <v>0.8984</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0261</v>
+        <v>0.376</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4191</v>
+        <v>-0.2324</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0623</v>
+        <v>0.8984</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6612</v>
+        <v>0.8984</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7235</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6612</v>
+        <v>0.8984</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5359</v>
+        <v>1.099</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7235</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="L20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1876</v>
+        <v>1.099</v>
       </c>
       <c r="N20" t="n">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0475</v>
+        <v>0.4713</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0199</v>
+        <v>0.1973</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.425</v>
+        <v>-0.4252</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0475</v>
+        <v>0.4713</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0475</v>
+        <v>0.4713</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0475</v>
+        <v>0.4713</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0475</v>
+        <v>0.5765</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0475</v>
+        <v>0.5765</v>
       </c>
       <c r="N21" t="n">
-        <v>94</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1166</v>
+        <v>0.3361</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0488</v>
+        <v>0.1407</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4904</v>
+        <v>-0.4863</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1166</v>
+        <v>0.3361</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1166</v>
+        <v>0.3361</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1166</v>
+        <v>0.3361</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1216</v>
+        <v>0.3361</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>216</v>
+        <v>94</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1216</v>
+        <v>0.3361</v>
       </c>
       <c r="N22" t="n">
-        <v>216</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1582</v>
+        <v>0.0538</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.0225</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5069</v>
+        <v>-0.6137</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1582</v>
+        <v>0.0538</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5748</v>
+        <v>-0.6556</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4166</v>
+        <v>0.7094</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5748</v>
+        <v>-0.6556</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4659</v>
+        <v>-0.3409</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4166</v>
+        <v>0.7094</v>
       </c>
       <c r="K23" t="n">
-        <v>27</v>
+        <v>238</v>
       </c>
       <c r="L23" t="n">
-        <v>29</v>
+        <v>188</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.04929999999999995</v>
+        <v>0.3685</v>
       </c>
       <c r="N23" t="n">
-        <v>56</v>
+        <v>426</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1847</v>
+        <v>-0.2231</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0934</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5175</v>
+        <v>-0.7387</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1847</v>
+        <v>-0.2231</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3922</v>
+        <v>-0.4868</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5769</v>
+        <v>0.2637</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3922</v>
+        <v>-0.4868</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3179</v>
+        <v>-0.2531</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5769</v>
+        <v>0.2637</v>
       </c>
       <c r="K24" t="n">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="L24" t="n">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.259</v>
+        <v>0.0106</v>
       </c>
       <c r="N24" t="n">
-        <v>304</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1929</v>
+        <v>-0.2244</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0939</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5208</v>
+        <v>-0.7393</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1929</v>
+        <v>-0.2244</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0621</v>
+        <v>-0.5812</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8692</v>
+        <v>0.3568</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0621</v>
+        <v>-0.5812</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8609</v>
+        <v>-0.3022</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8692</v>
+        <v>0.3568</v>
       </c>
       <c r="K25" t="n">
-        <v>238</v>
+        <v>27</v>
       </c>
       <c r="L25" t="n">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c r="M25" t="n">
-        <v>0.008299999999999974</v>
+        <v>0.05459999999999998</v>
       </c>
       <c r="N25" t="n">
-        <v>426</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bubzkji</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3111</v>
+        <v>-0.2336</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1302</v>
+        <v>-0.0978</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5679</v>
+        <v>-0.7435</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3111</v>
+        <v>-0.2336</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0.1423</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3111</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>-0.1423</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>-0.074</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3111</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3111</v>
+        <v>-0.1653</v>
       </c>
       <c r="N26" t="n">
-        <v>27</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Bubzkji</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6138</v>
+        <v>-0.263</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2569</v>
+        <v>-0.1101</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6884</v>
+        <v>-0.7567</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6138</v>
+        <v>-0.263</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8465</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2327</v>
+        <v>-0.263</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8465</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6861</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2327</v>
+        <v>-0.263</v>
       </c>
       <c r="K27" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.4534</v>
+        <v>-0.263</v>
       </c>
       <c r="N27" t="n">
-        <v>235</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6514</v>
+        <v>-0.3388</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2726</v>
+        <v>-0.1418</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7034</v>
+        <v>-0.791</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6514</v>
+        <v>-0.3388</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6514</v>
+        <v>-0.3388</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6514</v>
+        <v>-0.3388</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6624</v>
+        <v>-0.3527</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.6624</v>
+        <v>-0.3527</v>
       </c>
       <c r="N28" t="n">
-        <v>67</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.7353</v>
+        <v>-0.3816</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3077</v>
+        <v>-0.1597</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7369</v>
+        <v>-0.8103</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7353</v>
+        <v>-0.3816</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7353</v>
+        <v>-0.3816</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7353</v>
+        <v>-0.3816</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7353</v>
+        <v>-0.3973</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.7353</v>
+        <v>-0.3973</v>
       </c>
       <c r="N29" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.774</v>
+        <v>-0.4536</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3239</v>
+        <v>-0.1898</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7523</v>
+        <v>-0.8428</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.774</v>
+        <v>-0.4536</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.774</v>
+        <v>-0.8141</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.3605</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.774</v>
+        <v>-0.8141</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7805</v>
+        <v>-0.4233</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.3605</v>
       </c>
       <c r="K30" t="n">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7805</v>
+        <v>-0.06280000000000002</v>
       </c>
       <c r="N30" t="n">
-        <v>153</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8145</v>
+        <v>-0.4582</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3409</v>
+        <v>-0.1918</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7684</v>
+        <v>-0.8449</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8145</v>
+        <v>-0.4582</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8145</v>
+        <v>-0.4582</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8145</v>
+        <v>-0.4582</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8214</v>
+        <v>-0.5383</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8214</v>
+        <v>-0.5383</v>
       </c>
       <c r="N31" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9702</v>
+        <v>-0.5676</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4061</v>
+        <v>-0.2376</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8304</v>
+        <v>-0.8943</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9702</v>
+        <v>-0.5676</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6222</v>
+        <v>-0.5676</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.348</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6222</v>
+        <v>-0.5676</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5043</v>
+        <v>-0.5676</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.348</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>191</v>
+        <v>94</v>
       </c>
       <c r="L32" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.5676</v>
       </c>
       <c r="N32" t="n">
-        <v>248</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0163</v>
+        <v>-0.6704</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4253</v>
+        <v>-0.2806</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8488</v>
+        <v>-0.9407</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0163</v>
+        <v>-0.6704</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0163</v>
+        <v>-0.6704</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0163</v>
+        <v>-0.6704</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.0163</v>
+        <v>-0.6704</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0163</v>
+        <v>-0.6704</v>
       </c>
       <c r="N33" t="n">
         <v>94</v>
@@ -1964,323 +1964,323 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.1721</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4906</v>
+        <v>-0.2964</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9109</v>
+        <v>-0.9577</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1721</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.1721</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.1721</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.182</v>
+        <v>-0.7677</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.182</v>
+        <v>-0.7677</v>
       </c>
       <c r="N34" t="n">
-        <v>153</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.2299</v>
+        <v>-0.7604</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.5147</v>
+        <v>-0.3182</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9339</v>
+        <v>-0.9813</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2299</v>
+        <v>-0.7604</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.2299</v>
+        <v>-0.7604</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.2299</v>
+        <v>-0.7604</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2299</v>
+        <v>-0.7917</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2299</v>
+        <v>-0.7917</v>
       </c>
       <c r="N35" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2514</v>
+        <v>-0.8569</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.3586</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9425</v>
+        <v>-1.0249</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2514</v>
+        <v>-0.8569</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3967</v>
+        <v>-0.8569</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3967</v>
+        <v>-0.8569</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1321</v>
+        <v>-0.8569</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="L36" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9868000000000001</v>
+        <v>-0.8569</v>
       </c>
       <c r="N36" t="n">
-        <v>379</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Nivera</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3384</v>
+        <v>-0.9321</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5602</v>
+        <v>-0.3901</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9771</v>
+        <v>-1.0588</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3384</v>
+        <v>-0.9321</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3384</v>
+        <v>-0.9321</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3384</v>
+        <v>-0.9321</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.384</v>
+        <v>-1.1871</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.384</v>
+        <v>-1.1871</v>
       </c>
       <c r="N37" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nivera</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4267</v>
+        <v>-0.952</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5971</v>
+        <v>-0.3984</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0123</v>
+        <v>-1.0678</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4267</v>
+        <v>-0.952</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4267</v>
+        <v>-0.952</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4267</v>
+        <v>-0.952</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5003</v>
+        <v>-1.1185</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5003</v>
+        <v>-1.1185</v>
       </c>
       <c r="N38" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4649</v>
+        <v>-1.0664</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6131</v>
+        <v>-0.4463</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0275</v>
+        <v>-1.1194</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4649</v>
+        <v>-1.0664</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4649</v>
+        <v>-1.0664</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4649</v>
+        <v>-1.0664</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5148</v>
+        <v>-1.1103</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>230</v>
+        <v>153</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5148</v>
+        <v>-1.1103</v>
       </c>
       <c r="N39" t="n">
-        <v>230</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5459</v>
+        <v>-1.1178</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.647</v>
+        <v>-0.4678</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0598</v>
+        <v>-1.1426</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5459</v>
+        <v>-1.1178</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5459</v>
+        <v>-1.1178</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5459</v>
+        <v>-1.1178</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5589</v>
+        <v>-1.3134</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5589</v>
+        <v>-1.3134</v>
       </c>
       <c r="N40" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5813</v>
+        <v>-1.1653</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.4877</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.0739</v>
+        <v>-1.1641</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5813</v>
+        <v>-1.1653</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5813</v>
+        <v>-1.1653</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5813</v>
+        <v>-1.1653</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5813</v>
+        <v>-1.1653</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5813</v>
+        <v>-1.1653</v>
       </c>
       <c r="N41" t="n">
         <v>94</v>
@@ -2332,47 +2332,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.8145</v>
+        <v>-1.24</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.7594</v>
+        <v>-0.519</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.1668</v>
+        <v>-1.1978</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.8145</v>
+        <v>-1.24</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.8145</v>
+        <v>-1.4709</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.2309</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.8145</v>
+        <v>-1.4709</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.8764</v>
+        <v>-0.7648</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.2309</v>
       </c>
       <c r="K42" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.8764</v>
+        <v>-0.5339</v>
       </c>
       <c r="N42" t="n">
-        <v>201</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43">
@@ -2382,31 +2382,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-2.4948</v>
+        <v>-3.3515</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.0441</v>
+        <v>-1.4027</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.4378</v>
+        <v>-2.151</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.4948</v>
+        <v>-3.3515</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.1448</v>
+        <v>-3.1364</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.35</v>
+        <v>-0.2151</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.1448</v>
+        <v>-3.1364</v>
       </c>
       <c r="I43" t="n">
-        <v>-1.7384</v>
+        <v>-1.6308</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.35</v>
+        <v>-0.2151</v>
       </c>
       <c r="K43" t="n">
         <v>155</v>
@@ -2415,7 +2415,7 @@
         <v>57</v>
       </c>
       <c r="M43" t="n">
-        <v>-2.0884</v>
+        <v>-1.8459</v>
       </c>
       <c r="N43" t="n">
         <v>212</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-4.4594</v>
+        <v>-5.8522</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.8664</v>
+        <v>-2.4493</v>
       </c>
       <c r="D44" t="n">
-        <v>-2.2205</v>
+        <v>-3.28</v>
       </c>
       <c r="E44" t="n">
-        <v>-4.4594</v>
+        <v>-5.8522</v>
       </c>
       <c r="F44" t="n">
-        <v>-3.4594</v>
+        <v>-4.8522</v>
       </c>
       <c r="G44" t="n">
         <v>-1</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.4594</v>
+        <v>-4.8522</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.8039</v>
+        <v>-2.5229</v>
       </c>
       <c r="J44" t="n">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>81</v>
       </c>
       <c r="M44" t="n">
-        <v>-3.8039</v>
+        <v>-3.5229</v>
       </c>
       <c r="N44" t="n">
         <v>198</v>
@@ -2567,10 +2567,10 @@
         <v>1.44</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0928</v>
+        <v>1.0608</v>
       </c>
       <c r="J2" t="n">
-        <v>29.5056</v>
+        <v>28.6416</v>
       </c>
     </row>
     <row r="3">
@@ -2607,10 +2607,10 @@
         <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7836</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>21.1572</v>
+        <v>21.3246</v>
       </c>
     </row>
     <row r="4">
@@ -2647,10 +2647,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6058</v>
+        <v>0.628</v>
       </c>
       <c r="J4" t="n">
-        <v>16.3566</v>
+        <v>16.956</v>
       </c>
     </row>
     <row r="5">
@@ -2687,10 +2687,10 @@
         <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4245</v>
+        <v>0.485</v>
       </c>
       <c r="J5" t="n">
-        <v>11.4615</v>
+        <v>13.095</v>
       </c>
     </row>
     <row r="6">
@@ -2727,10 +2727,10 @@
         <v>0.93</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3946</v>
+        <v>-0.3174</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.6542</v>
+        <v>-8.569800000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2767,10 +2767,10 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3502</v>
+        <v>0.3846</v>
       </c>
       <c r="J7" t="n">
-        <v>9.455399999999999</v>
+        <v>10.3842</v>
       </c>
     </row>
     <row r="8">
@@ -2807,10 +2807,10 @@
         <v>1.14</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3348</v>
+        <v>0.3645</v>
       </c>
       <c r="J8" t="n">
-        <v>9.0396</v>
+        <v>9.8415</v>
       </c>
     </row>
     <row r="9">
@@ -2847,10 +2847,10 @@
         <v>0.92</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1274</v>
+        <v>-0.1013</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.4398</v>
+        <v>-2.7351</v>
       </c>
     </row>
     <row r="10">
@@ -2887,10 +2887,10 @@
         <v>0.75</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4262</v>
+        <v>-0.2745</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.5074</v>
+        <v>-7.4115</v>
       </c>
     </row>
     <row r="11">
@@ -2927,10 +2927,10 @@
         <v>0.48</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7729</v>
+        <v>-0.5262</v>
       </c>
       <c r="J11" t="n">
-        <v>-20.8683</v>
+        <v>-14.2074</v>
       </c>
     </row>
     <row r="12">
@@ -2967,10 +2967,10 @@
         <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.656</v>
+        <v>1.4281</v>
       </c>
       <c r="J12" t="n">
-        <v>44.712</v>
+        <v>38.5587</v>
       </c>
     </row>
     <row r="13">
@@ -3007,10 +3007,10 @@
         <v>1.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6016</v>
+        <v>1.3912</v>
       </c>
       <c r="J13" t="n">
-        <v>43.2432</v>
+        <v>37.5624</v>
       </c>
     </row>
     <row r="14">
@@ -3047,10 +3047,10 @@
         <v>1.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0133</v>
+        <v>0.0835</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3591</v>
+        <v>2.2545</v>
       </c>
     </row>
     <row r="15">
@@ -3087,10 +3087,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7071</v>
+        <v>-0.6501</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.0917</v>
+        <v>-17.5527</v>
       </c>
     </row>
     <row r="16">
@@ -3127,10 +3127,10 @@
         <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8461</v>
+        <v>-0.8027</v>
       </c>
       <c r="J16" t="n">
-        <v>-22.8447</v>
+        <v>-21.6729</v>
       </c>
     </row>
     <row r="17">
@@ -3167,10 +3167,10 @@
         <v>1.19</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4006</v>
+        <v>0.4525</v>
       </c>
       <c r="J17" t="n">
-        <v>10.8162</v>
+        <v>12.2175</v>
       </c>
     </row>
     <row r="18">
@@ -3207,10 +3207,10 @@
         <v>1.07</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2092</v>
+        <v>0.2079</v>
       </c>
       <c r="J18" t="n">
-        <v>5.6484</v>
+        <v>5.6133</v>
       </c>
     </row>
     <row r="19">
@@ -3247,10 +3247,10 @@
         <v>1.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1717</v>
+        <v>0.162</v>
       </c>
       <c r="J19" t="n">
-        <v>4.6359</v>
+        <v>4.374</v>
       </c>
     </row>
     <row r="20">
@@ -3287,10 +3287,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.3352</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.9212</v>
+        <v>-9.0504</v>
       </c>
     </row>
     <row r="21">
@@ -3327,10 +3327,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.681</v>
+        <v>-0.4562</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.387</v>
+        <v>-12.3174</v>
       </c>
     </row>
     <row r="22">
@@ -3367,10 +3367,10 @@
         <v>1.54</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3565</v>
+        <v>1.2246</v>
       </c>
       <c r="J22" t="n">
-        <v>35.269</v>
+        <v>31.8396</v>
       </c>
     </row>
     <row r="23">
@@ -3407,10 +3407,10 @@
         <v>1.22</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6622</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>17.2172</v>
+        <v>16.5256</v>
       </c>
     </row>
     <row r="24">
@@ -3447,10 +3447,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3193</v>
+        <v>-0.2542</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.3018</v>
+        <v>-6.6092</v>
       </c>
     </row>
     <row r="25">
@@ -3487,10 +3487,10 @@
         <v>0.9</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4393</v>
+        <v>-0.375</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.4218</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="26">
@@ -3527,10 +3527,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5486</v>
+        <v>-0.4877</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.2636</v>
+        <v>-12.6802</v>
       </c>
     </row>
     <row r="27">
@@ -3567,10 +3567,10 @@
         <v>1.11</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2621</v>
+        <v>0.2796</v>
       </c>
       <c r="J27" t="n">
-        <v>6.8146</v>
+        <v>7.2696</v>
       </c>
     </row>
     <row r="28">
@@ -3607,10 +3607,10 @@
         <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1742</v>
+        <v>0.1729</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5292</v>
+        <v>4.4954</v>
       </c>
     </row>
     <row r="29">
@@ -3647,10 +3647,10 @@
         <v>0.91</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1932</v>
+        <v>-0.1181</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.0232</v>
+        <v>-3.0706</v>
       </c>
     </row>
     <row r="30">
@@ -3687,10 +3687,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.263</v>
+        <v>-0.1616</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.838</v>
+        <v>-4.2016</v>
       </c>
     </row>
     <row r="31">
@@ -3727,10 +3727,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3422</v>
+        <v>-0.2134</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.8972</v>
+        <v>-5.5484</v>
       </c>
     </row>
     <row r="32">
@@ -3767,10 +3767,10 @@
         <v>1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>0.417</v>
+        <v>0.426</v>
       </c>
       <c r="J32" t="n">
-        <v>11.259</v>
+        <v>11.502</v>
       </c>
     </row>
     <row r="33">
@@ -3807,10 +3807,10 @@
         <v>1.18</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3303</v>
+        <v>0.363</v>
       </c>
       <c r="J33" t="n">
-        <v>8.918100000000001</v>
+        <v>9.801</v>
       </c>
     </row>
     <row r="34">
@@ -3847,10 +3847,10 @@
         <v>1.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2679</v>
+        <v>0.3089</v>
       </c>
       <c r="J34" t="n">
-        <v>7.2333</v>
+        <v>8.340299999999999</v>
       </c>
     </row>
     <row r="35">
@@ -3887,10 +3887,10 @@
         <v>1.01</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0281</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.0162</v>
+        <v>0.7587</v>
       </c>
     </row>
     <row r="36">
@@ -3927,10 +3927,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4394</v>
+        <v>-0.2763</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.8638</v>
+        <v>-7.4601</v>
       </c>
     </row>
     <row r="37">
@@ -3967,10 +3967,10 @@
         <v>1.82</v>
       </c>
       <c r="I37" t="n">
-        <v>1.8135</v>
+        <v>1.3212</v>
       </c>
       <c r="J37" t="n">
-        <v>48.9645</v>
+        <v>35.6724</v>
       </c>
     </row>
     <row r="38">
@@ -4007,10 +4007,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4097</v>
+        <v>0.3638</v>
       </c>
       <c r="J38" t="n">
-        <v>11.0619</v>
+        <v>9.8226</v>
       </c>
     </row>
     <row r="39">
@@ -4047,10 +4047,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3697</v>
+        <v>-0.3087</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.9819</v>
+        <v>-8.334899999999999</v>
       </c>
     </row>
     <row r="40">
@@ -4087,10 +4087,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5653</v>
+        <v>-0.5077</v>
       </c>
       <c r="J40" t="n">
-        <v>-15.2631</v>
+        <v>-13.7079</v>
       </c>
     </row>
     <row r="41">
@@ -4127,10 +4127,10 @@
         <v>0.62</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0972</v>
+        <v>-1.0849</v>
       </c>
       <c r="J41" t="n">
-        <v>-29.6244</v>
+        <v>-29.2923</v>
       </c>
     </row>
     <row r="42">
@@ -4167,10 +4167,10 @@
         <v>1.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2333</v>
+        <v>0.2356</v>
       </c>
       <c r="J42" t="n">
-        <v>6.999</v>
+        <v>7.068</v>
       </c>
     </row>
     <row r="43">
@@ -4207,10 +4207,10 @@
         <v>1.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0612</v>
       </c>
       <c r="J43" t="n">
-        <v>2.682</v>
+        <v>1.836</v>
       </c>
     </row>
     <row r="44">
@@ -4247,10 +4247,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0919</v>
+        <v>-0.0788</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.757</v>
+        <v>-2.364</v>
       </c>
     </row>
     <row r="45">
@@ -4287,10 +4287,10 @@
         <v>0.89</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1993</v>
+        <v>-0.1344</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.979</v>
+        <v>-4.032</v>
       </c>
     </row>
     <row r="46">
@@ -4327,10 +4327,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6783</v>
+        <v>-0.4543</v>
       </c>
       <c r="J46" t="n">
-        <v>-20.349</v>
+        <v>-13.629</v>
       </c>
     </row>
     <row r="47">
@@ -4367,10 +4367,10 @@
         <v>1.5</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2392</v>
+        <v>0.8764</v>
       </c>
       <c r="J47" t="n">
-        <v>37.176</v>
+        <v>26.292</v>
       </c>
     </row>
     <row r="48">
@@ -4407,10 +4407,10 @@
         <v>1.45</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1378</v>
+        <v>0.8114</v>
       </c>
       <c r="J48" t="n">
-        <v>34.134</v>
+        <v>24.342</v>
       </c>
     </row>
     <row r="49">
@@ -4447,10 +4447,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1607</v>
       </c>
       <c r="J49" t="n">
-        <v>2.958</v>
+        <v>4.821</v>
       </c>
     </row>
     <row r="50">
@@ -4487,10 +4487,10 @@
         <v>0.99</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1689</v>
+        <v>-0.0949</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.067</v>
+        <v>-2.847</v>
       </c>
     </row>
     <row r="51">
@@ -4527,10 +4527,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6236</v>
+        <v>-0.5616</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.708</v>
+        <v>-16.848</v>
       </c>
     </row>
     <row r="52">
@@ -4567,10 +4567,10 @@
         <v>1.31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5141</v>
+        <v>0.4989</v>
       </c>
       <c r="J52" t="n">
-        <v>14.9089</v>
+        <v>14.4681</v>
       </c>
     </row>
     <row r="53">
@@ -4607,10 +4607,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2555</v>
+        <v>0.2923</v>
       </c>
       <c r="J53" t="n">
-        <v>7.4095</v>
+        <v>8.476699999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4647,10 +4647,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2388</v>
+        <v>0.2731</v>
       </c>
       <c r="J54" t="n">
-        <v>6.9252</v>
+        <v>7.9199</v>
       </c>
     </row>
     <row r="55">
@@ -4687,10 +4687,10 @@
         <v>0.92</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2103</v>
+        <v>-0.1179</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.0987</v>
+        <v>-3.4191</v>
       </c>
     </row>
     <row r="56">
@@ -4727,10 +4727,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3818</v>
+        <v>-0.2355</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.0722</v>
+        <v>-6.8295</v>
       </c>
     </row>
     <row r="57">
@@ -4767,10 +4767,10 @@
         <v>0.46</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.4105</v>
+        <v>-1.4449</v>
       </c>
       <c r="J57" t="n">
-        <v>-40.9045</v>
+        <v>-41.9021</v>
       </c>
     </row>
     <row r="58">
@@ -4807,10 +4807,10 @@
         <v>1.25</v>
       </c>
       <c r="I58" t="n">
-        <v>0.781</v>
+        <v>0.5746</v>
       </c>
       <c r="J58" t="n">
-        <v>22.649</v>
+        <v>16.6634</v>
       </c>
     </row>
     <row r="59">
@@ -4847,10 +4847,10 @@
         <v>1.19</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6337</v>
+        <v>0.4842</v>
       </c>
       <c r="J59" t="n">
-        <v>18.3773</v>
+        <v>14.0418</v>
       </c>
     </row>
     <row r="60">
@@ -4887,10 +4887,10 @@
         <v>1.11</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4166</v>
+        <v>0.3568</v>
       </c>
       <c r="J60" t="n">
-        <v>12.0814</v>
+        <v>10.3472</v>
       </c>
     </row>
     <row r="61">
@@ -4927,10 +4927,10 @@
         <v>1.06</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2594</v>
+        <v>0.225</v>
       </c>
       <c r="J61" t="n">
-        <v>7.5226</v>
+        <v>6.525</v>
       </c>
     </row>
     <row r="62">
@@ -4967,10 +4967,10 @@
         <v>0.58</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.6912</v>
+        <v>-0.464</v>
       </c>
       <c r="J62" t="n">
-        <v>-17.28</v>
+        <v>-11.6</v>
       </c>
     </row>
     <row r="63">
@@ -5007,10 +5007,10 @@
         <v>1.61</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8283</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>20.7075</v>
+        <v>14.4025</v>
       </c>
     </row>
     <row r="64">
@@ -5047,10 +5047,10 @@
         <v>1.37</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5494</v>
+        <v>0.4205</v>
       </c>
       <c r="J64" t="n">
-        <v>13.735</v>
+        <v>10.5125</v>
       </c>
     </row>
     <row r="65">
@@ -5087,10 +5087,10 @@
         <v>1.33</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4982</v>
+        <v>0.3936</v>
       </c>
       <c r="J65" t="n">
-        <v>12.455</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="66">
@@ -5127,10 +5127,10 @@
         <v>1.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>1.725</v>
+        <v>2.345</v>
       </c>
     </row>
     <row r="67">
@@ -5167,10 +5167,10 @@
         <v>0.58</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.6572</v>
+        <v>-0.4383</v>
       </c>
       <c r="J67" t="n">
-        <v>-16.43</v>
+        <v>-10.9575</v>
       </c>
     </row>
     <row r="68">
@@ -5207,10 +5207,10 @@
         <v>1.09</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2429</v>
+        <v>0.1915</v>
       </c>
       <c r="J68" t="n">
-        <v>6.0725</v>
+        <v>4.7875</v>
       </c>
     </row>
     <row r="69">
@@ -5247,10 +5247,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1701</v>
+        <v>0.123</v>
       </c>
       <c r="J69" t="n">
-        <v>4.2525</v>
+        <v>3.075</v>
       </c>
     </row>
     <row r="70">
@@ -5287,10 +5287,10 @@
         <v>0.98</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0147</v>
+        <v>-0.0283</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.3675</v>
+        <v>-0.7075</v>
       </c>
     </row>
     <row r="71">
@@ -5327,10 +5327,10 @@
         <v>0.88</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2304</v>
+        <v>-0.1468</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.76</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="72">
@@ -5367,10 +5367,10 @@
         <v>0.59</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.4835</v>
+        <v>-0.3745</v>
       </c>
       <c r="J72" t="n">
-        <v>-13.0545</v>
+        <v>-10.1115</v>
       </c>
     </row>
     <row r="73">
@@ -5407,10 +5407,10 @@
         <v>0.7</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.3111</v>
+        <v>-0.263</v>
       </c>
       <c r="J73" t="n">
-        <v>-8.399699999999999</v>
+        <v>-7.101</v>
       </c>
     </row>
     <row r="74">
@@ -5447,10 +5447,10 @@
         <v>0.6</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.467</v>
+        <v>-0.365</v>
       </c>
       <c r="J74" t="n">
-        <v>-12.609</v>
+        <v>-9.855</v>
       </c>
     </row>
     <row r="75">
@@ -5487,10 +5487,10 @@
         <v>0.46</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7141</v>
+        <v>-0.4926</v>
       </c>
       <c r="J75" t="n">
-        <v>-19.2807</v>
+        <v>-13.3002</v>
       </c>
     </row>
     <row r="76">
@@ -5527,10 +5527,10 @@
         <v>0.4</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.5502</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.5703</v>
+        <v>-14.8554</v>
       </c>
     </row>
     <row r="77">
@@ -5567,10 +5567,10 @@
         <v>0.74</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.7516</v>
+        <v>-0.7289</v>
       </c>
       <c r="J77" t="n">
-        <v>-20.2932</v>
+        <v>-19.6803</v>
       </c>
     </row>
     <row r="78">
@@ -5607,10 +5607,10 @@
         <v>1.27</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9245</v>
+        <v>0.6616</v>
       </c>
       <c r="J78" t="n">
-        <v>24.9615</v>
+        <v>17.8632</v>
       </c>
     </row>
     <row r="79">
@@ -5647,10 +5647,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5645</v>
+        <v>-0.551</v>
       </c>
       <c r="J79" t="n">
-        <v>-15.2415</v>
+        <v>-14.877</v>
       </c>
     </row>
     <row r="80">
@@ -5687,10 +5687,10 @@
         <v>0.75</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.7262</v>
+        <v>-0.7038</v>
       </c>
       <c r="J80" t="n">
-        <v>-19.6074</v>
+        <v>-19.0026</v>
       </c>
     </row>
     <row r="81">
@@ -5727,10 +5727,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7768</v>
+        <v>-0.754</v>
       </c>
       <c r="J81" t="n">
-        <v>-20.9736</v>
+        <v>-20.358</v>
       </c>
     </row>
     <row r="82">
@@ -5767,10 +5767,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5366</v>
+        <v>0.6443</v>
       </c>
       <c r="J82" t="n">
-        <v>16.098</v>
+        <v>19.329</v>
       </c>
     </row>
     <row r="83">
@@ -5807,10 +5807,10 @@
         <v>1.3</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4978</v>
+        <v>0.5936</v>
       </c>
       <c r="J83" t="n">
-        <v>14.934</v>
+        <v>17.808</v>
       </c>
     </row>
     <row r="84">
@@ -5847,10 +5847,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2173</v>
+        <v>0.2518</v>
       </c>
       <c r="J84" t="n">
-        <v>6.519</v>
+        <v>7.554</v>
       </c>
     </row>
     <row r="85">
@@ -5887,10 +5887,10 @@
         <v>0.85</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3253</v>
+        <v>-0.1956</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.759</v>
+        <v>-5.868</v>
       </c>
     </row>
     <row r="86">
@@ -5927,10 +5927,10 @@
         <v>0.75</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4664</v>
+        <v>-0.2958</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.992</v>
+        <v>-8.874000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5967,10 +5967,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9363</v>
+        <v>0.9095</v>
       </c>
       <c r="J87" t="n">
-        <v>28.089</v>
+        <v>27.285</v>
       </c>
     </row>
     <row r="88">
@@ -6007,10 +6007,10 @@
         <v>1.21</v>
       </c>
       <c r="I88" t="n">
-        <v>0.678</v>
+        <v>0.6364</v>
       </c>
       <c r="J88" t="n">
-        <v>20.34</v>
+        <v>19.092</v>
       </c>
     </row>
     <row r="89">
@@ -6047,10 +6047,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.216</v>
+        <v>-0.1705</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.48</v>
+        <v>-5.115</v>
       </c>
     </row>
     <row r="90">
@@ -6087,10 +6087,10 @@
         <v>0.83</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6009</v>
+        <v>-0.5494</v>
       </c>
       <c r="J90" t="n">
-        <v>-18.027</v>
+        <v>-16.482</v>
       </c>
     </row>
     <row r="91">
@@ -6127,10 +6127,10 @@
         <v>0.8</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6768</v>
+        <v>-0.6283</v>
       </c>
       <c r="J91" t="n">
-        <v>-20.304</v>
+        <v>-18.849</v>
       </c>
     </row>
     <row r="92">
@@ -6167,10 +6167,10 @@
         <v>0.89</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0229</v>
+        <v>-0.007</v>
       </c>
       <c r="J92" t="n">
-        <v>0.4351</v>
+        <v>-0.133</v>
       </c>
     </row>
     <row r="93">
@@ -6207,10 +6207,10 @@
         <v>0.62</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.4011</v>
+        <v>-0.3294</v>
       </c>
       <c r="J93" t="n">
-        <v>-7.6209</v>
+        <v>-6.2586</v>
       </c>
     </row>
     <row r="94">
@@ -6247,10 +6247,10 @@
         <v>0.35</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.8498</v>
+        <v>-0.5884</v>
       </c>
       <c r="J94" t="n">
-        <v>-16.1462</v>
+        <v>-11.1796</v>
       </c>
     </row>
     <row r="95">
@@ -6287,10 +6287,10 @@
         <v>0.32</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.8908</v>
+        <v>-0.6183</v>
       </c>
       <c r="J95" t="n">
-        <v>-16.9252</v>
+        <v>-11.7477</v>
       </c>
     </row>
     <row r="96">
@@ -6327,10 +6327,10 @@
         <v>0.32</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8908</v>
+        <v>-0.6183</v>
       </c>
       <c r="J96" t="n">
-        <v>-16.9252</v>
+        <v>-11.7477</v>
       </c>
     </row>
     <row r="97">
@@ -6367,10 +6367,10 @@
         <v>1.82</v>
       </c>
       <c r="I97" t="n">
-        <v>1.6462</v>
+        <v>1.445</v>
       </c>
       <c r="J97" t="n">
-        <v>31.2778</v>
+        <v>27.455</v>
       </c>
     </row>
     <row r="98">
@@ -6407,10 +6407,10 @@
         <v>1.74</v>
       </c>
       <c r="I98" t="n">
-        <v>1.5007</v>
+        <v>1.3562</v>
       </c>
       <c r="J98" t="n">
-        <v>28.5133</v>
+        <v>25.7678</v>
       </c>
     </row>
     <row r="99">
@@ -6447,10 +6447,10 @@
         <v>1.59</v>
       </c>
       <c r="I99" t="n">
-        <v>1.1856</v>
+        <v>1.1894</v>
       </c>
       <c r="J99" t="n">
-        <v>22.5264</v>
+        <v>22.5986</v>
       </c>
     </row>
     <row r="100">
@@ -6487,10 +6487,10 @@
         <v>1.48</v>
       </c>
       <c r="I100" t="n">
-        <v>0.9546</v>
+        <v>1.0614</v>
       </c>
       <c r="J100" t="n">
-        <v>18.1374</v>
+        <v>20.1666</v>
       </c>
     </row>
     <row r="101">
@@ -6527,10 +6527,10 @@
         <v>1.38</v>
       </c>
       <c r="I101" t="n">
-        <v>0.7501</v>
+        <v>0.8938</v>
       </c>
       <c r="J101" t="n">
-        <v>14.2519</v>
+        <v>16.9822</v>
       </c>
     </row>
     <row r="102">
@@ -6567,10 +6567,10 @@
         <v>0.93</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0838</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.575</v>
+        <v>-1.5084</v>
       </c>
     </row>
     <row r="103">
@@ -6607,10 +6607,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1063</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.9134</v>
+        <v>-1.7226</v>
       </c>
     </row>
     <row r="104">
@@ -6647,10 +6647,10 @@
         <v>0.86</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2175</v>
+        <v>-0.1613</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.915</v>
+        <v>-2.9034</v>
       </c>
     </row>
     <row r="105">
@@ -6687,10 +6687,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2824</v>
+        <v>-0.1907</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.0832</v>
+        <v>-3.4326</v>
       </c>
     </row>
     <row r="106">
@@ -6727,10 +6727,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4987</v>
+        <v>-0.3265</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.976599999999999</v>
+        <v>-5.877</v>
       </c>
     </row>
     <row r="107">
@@ -6767,10 +6767,10 @@
         <v>1.04</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.0343</v>
+        <v>0.0159</v>
       </c>
       <c r="J107" t="n">
-        <v>-0.6173999999999999</v>
+        <v>0.2862</v>
       </c>
     </row>
     <row r="108">
@@ -6807,10 +6807,10 @@
         <v>2.44</v>
       </c>
       <c r="I108" t="n">
-        <v>1.5138</v>
+        <v>1.3267</v>
       </c>
       <c r="J108" t="n">
-        <v>27.2484</v>
+        <v>23.8806</v>
       </c>
     </row>
     <row r="109">
@@ -6847,10 +6847,10 @@
         <v>1.98</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0991</v>
+        <v>1.0624</v>
       </c>
       <c r="J109" t="n">
-        <v>19.7838</v>
+        <v>19.1232</v>
       </c>
     </row>
     <row r="110">
@@ -6887,10 +6887,10 @@
         <v>1.62</v>
       </c>
       <c r="I110" t="n">
-        <v>0.7109</v>
+        <v>0.7432</v>
       </c>
       <c r="J110" t="n">
-        <v>12.7962</v>
+        <v>13.3776</v>
       </c>
     </row>
     <row r="111">
@@ -6927,10 +6927,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0163</v>
+        <v>0.0337</v>
       </c>
       <c r="J111" t="n">
-        <v>-0.2934</v>
+        <v>0.6066</v>
       </c>
     </row>
     <row r="112">
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>-1.2861</v>
+        <v>-0.9467</v>
       </c>
       <c r="J112" t="n">
-        <v>-52.7301</v>
+        <v>-38.8147</v>
       </c>
     </row>
     <row r="113">
@@ -7007,10 +7007,10 @@
         <v>0.78</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.4071</v>
+        <v>-3.1283</v>
       </c>
     </row>
     <row r="114">
@@ -7047,10 +7047,10 @@
         <v>0.55</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4388</v>
+        <v>-0.3627</v>
       </c>
       <c r="J114" t="n">
-        <v>-17.9908</v>
+        <v>-14.8707</v>
       </c>
     </row>
     <row r="115">
@@ -7087,10 +7087,10 @@
         <v>0.43</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6375</v>
+        <v>-0.49</v>
       </c>
       <c r="J115" t="n">
-        <v>-26.1375</v>
+        <v>-20.09</v>
       </c>
     </row>
     <row r="116">
@@ -7127,10 +7127,10 @@
         <v>0.27</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.9271</v>
+        <v>-0.6471</v>
       </c>
       <c r="J116" t="n">
-        <v>-38.0111</v>
+        <v>-26.5311</v>
       </c>
     </row>
     <row r="117">
@@ -7167,10 +7167,10 @@
         <v>0.64</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.9978</v>
+        <v>-0.9816</v>
       </c>
       <c r="J117" t="n">
-        <v>-40.9098</v>
+        <v>-40.2456</v>
       </c>
     </row>
     <row r="118">
@@ -7207,10 +7207,10 @@
         <v>1.52</v>
       </c>
       <c r="I118" t="n">
-        <v>1.4478</v>
+        <v>1.2964</v>
       </c>
       <c r="J118" t="n">
-        <v>59.3598</v>
+        <v>53.1524</v>
       </c>
     </row>
     <row r="119">
@@ -7247,10 +7247,10 @@
         <v>0.87</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3922</v>
+        <v>-0.3988</v>
       </c>
       <c r="J119" t="n">
-        <v>-16.0802</v>
+        <v>-16.3508</v>
       </c>
     </row>
     <row r="120">
@@ -7287,10 +7287,10 @@
         <v>0.75</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.7351</v>
+        <v>-0.7093</v>
       </c>
       <c r="J120" t="n">
-        <v>-30.1391</v>
+        <v>-29.0813</v>
       </c>
     </row>
     <row r="121">
@@ -7327,10 +7327,10 @@
         <v>0.6</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.0872</v>
+        <v>-1.0785</v>
       </c>
       <c r="J121" t="n">
-        <v>-44.5752</v>
+        <v>-44.2185</v>
       </c>
     </row>
     <row r="122">
@@ -7367,10 +7367,10 @@
         <v>0.64</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.5834</v>
+        <v>-0.3838</v>
       </c>
       <c r="J122" t="n">
-        <v>-12.2514</v>
+        <v>-8.059799999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7407,10 +7407,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3962</v>
+        <v>0.4475</v>
       </c>
       <c r="J123" t="n">
-        <v>8.3202</v>
+        <v>9.397500000000001</v>
       </c>
     </row>
     <row r="124">
@@ -7447,10 +7447,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1861</v>
+        <v>0.1815</v>
       </c>
       <c r="J124" t="n">
-        <v>3.9081</v>
+        <v>3.8115</v>
       </c>
     </row>
     <row r="125">
@@ -7487,10 +7487,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.057</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.3482</v>
+        <v>-1.197</v>
       </c>
     </row>
     <row r="126">
@@ -7527,10 +7527,10 @@
         <v>0.77</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4076</v>
+        <v>-0.2596</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.5596</v>
+        <v>-5.4516</v>
       </c>
     </row>
     <row r="127">
@@ -7567,10 +7567,10 @@
         <v>0.83</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0289</v>
+        <v>-0.0614</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.6069</v>
+        <v>-1.2894</v>
       </c>
     </row>
     <row r="128">
@@ -7607,10 +7607,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.759</v>
+        <v>-0.9355</v>
       </c>
       <c r="J128" t="n">
-        <v>-15.939</v>
+        <v>-19.6455</v>
       </c>
     </row>
     <row r="129">
@@ -7647,10 +7647,10 @@
         <v>0.27</v>
       </c>
       <c r="I129" t="n">
-        <v>-1.6241</v>
+        <v>-1.6926</v>
       </c>
       <c r="J129" t="n">
-        <v>-34.1061</v>
+        <v>-35.5446</v>
       </c>
     </row>
     <row r="130">
@@ -7687,10 +7687,10 @@
         <v>0.24</v>
       </c>
       <c r="I130" t="n">
-        <v>-1.6976</v>
+        <v>-1.7752</v>
       </c>
       <c r="J130" t="n">
-        <v>-35.6496</v>
+        <v>-37.2792</v>
       </c>
     </row>
     <row r="131">
@@ -7727,10 +7727,10 @@
         <v>0.21</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.7693</v>
+        <v>-1.8587</v>
       </c>
       <c r="J131" t="n">
-        <v>-37.1553</v>
+        <v>-39.0327</v>
       </c>
     </row>
     <row r="132">
@@ -7767,10 +7767,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1175</v>
+        <v>1.067</v>
       </c>
       <c r="J132" t="n">
-        <v>39.1125</v>
+        <v>37.345</v>
       </c>
     </row>
     <row r="133">
@@ -7807,10 +7807,10 @@
         <v>1.17</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5366</v>
+        <v>0.5111</v>
       </c>
       <c r="J133" t="n">
-        <v>18.781</v>
+        <v>17.8885</v>
       </c>
     </row>
     <row r="134">
@@ -7847,10 +7847,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4243</v>
+        <v>0.4063</v>
       </c>
       <c r="J134" t="n">
-        <v>14.8505</v>
+        <v>14.2205</v>
       </c>
     </row>
     <row r="135">
@@ -7887,10 +7887,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.012</v>
+        <v>0.0354</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.42</v>
+        <v>1.239</v>
       </c>
     </row>
     <row r="136">
@@ -7927,10 +7927,10 @@
         <v>0.7</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.9296</v>
+        <v>-0.8974</v>
       </c>
       <c r="J136" t="n">
-        <v>-32.536</v>
+        <v>-31.409</v>
       </c>
     </row>
     <row r="137">
@@ -7967,10 +7967,10 @@
         <v>1.2</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3843</v>
+        <v>0.4393</v>
       </c>
       <c r="J137" t="n">
-        <v>13.4505</v>
+        <v>15.3755</v>
       </c>
     </row>
     <row r="138">
@@ -8007,10 +8007,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3402</v>
+        <v>0.3835</v>
       </c>
       <c r="J138" t="n">
-        <v>11.907</v>
+        <v>13.4225</v>
       </c>
     </row>
     <row r="139">
@@ -8047,10 +8047,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2456</v>
+        <v>0.2671</v>
       </c>
       <c r="J139" t="n">
-        <v>8.596</v>
+        <v>9.3485</v>
       </c>
     </row>
     <row r="140">
@@ -8087,10 +8087,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0922</v>
       </c>
       <c r="J140" t="n">
-        <v>3.2655</v>
+        <v>3.227</v>
       </c>
     </row>
     <row r="141">
@@ -8127,10 +8127,10 @@
         <v>0.48</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7864</v>
+        <v>-0.537</v>
       </c>
       <c r="J141" t="n">
-        <v>-27.524</v>
+        <v>-18.795</v>
       </c>
     </row>
     <row r="142">
@@ -8167,10 +8167,10 @@
         <v>1.52</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2963</v>
+        <v>1.1858</v>
       </c>
       <c r="J142" t="n">
-        <v>33.7038</v>
+        <v>30.8308</v>
       </c>
     </row>
     <row r="143">
@@ -8207,10 +8207,10 @@
         <v>1.41</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0721</v>
+        <v>1.0395</v>
       </c>
       <c r="J143" t="n">
-        <v>27.8746</v>
+        <v>27.027</v>
       </c>
     </row>
     <row r="144">
@@ -8247,10 +8247,10 @@
         <v>1.21</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6121</v>
+        <v>0.5986</v>
       </c>
       <c r="J144" t="n">
-        <v>15.9146</v>
+        <v>15.5636</v>
       </c>
     </row>
     <row r="145">
@@ -8287,10 +8287,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.7359</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>-19.1334</v>
+        <v>-17.784</v>
       </c>
     </row>
     <row r="146">
@@ -8327,10 +8327,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8743</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>-22.7318</v>
+        <v>-21.7152</v>
       </c>
     </row>
     <row r="147">
@@ -8367,10 +8367,10 @@
         <v>1.33</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5542</v>
+        <v>0.6635</v>
       </c>
       <c r="J147" t="n">
-        <v>14.4092</v>
+        <v>17.251</v>
       </c>
     </row>
     <row r="148">
@@ -8407,10 +8407,10 @@
         <v>1.08</v>
       </c>
       <c r="I148" t="n">
-        <v>0.187</v>
+        <v>0.2018</v>
       </c>
       <c r="J148" t="n">
-        <v>4.862</v>
+        <v>5.2468</v>
       </c>
     </row>
     <row r="149">
@@ -8447,10 +8447,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0896</v>
       </c>
       <c r="J149" t="n">
-        <v>2.1996</v>
+        <v>2.3296</v>
       </c>
     </row>
     <row r="150">
@@ -8487,10 +8487,10 @@
         <v>0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.249</v>
+        <v>-0.1468</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.474</v>
+        <v>-3.8168</v>
       </c>
     </row>
     <row r="151">
@@ -8527,10 +8527,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.47</v>
+        <v>-0.2996</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.22</v>
+        <v>-7.7896</v>
       </c>
     </row>
     <row r="152">
@@ -8567,10 +8567,10 @@
         <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0158</v>
+        <v>0.9913</v>
       </c>
       <c r="J152" t="n">
-        <v>29.4582</v>
+        <v>28.7477</v>
       </c>
     </row>
     <row r="153">
@@ -8607,10 +8607,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6202</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>17.9858</v>
+        <v>17.1158</v>
       </c>
     </row>
     <row r="154">
@@ -8647,10 +8647,10 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0677</v>
+        <v>-0.0173</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.9633</v>
+        <v>-0.5017</v>
       </c>
     </row>
     <row r="155">
@@ -8687,10 +8687,10 @@
         <v>0.96</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2462</v>
+        <v>-0.1849</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.1398</v>
+        <v>-5.3621</v>
       </c>
     </row>
     <row r="156">
@@ -8727,10 +8727,10 @@
         <v>0.86</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5435</v>
+        <v>-0.4838</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.7615</v>
+        <v>-14.0302</v>
       </c>
     </row>
     <row r="157">
@@ -8767,10 +8767,10 @@
         <v>1.29</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5188</v>
+        <v>0.6132</v>
       </c>
       <c r="J157" t="n">
-        <v>15.0452</v>
+        <v>17.7828</v>
       </c>
     </row>
     <row r="158">
@@ -8807,10 +8807,10 @@
         <v>1.07</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1881</v>
+        <v>0.1919</v>
       </c>
       <c r="J158" t="n">
-        <v>5.4549</v>
+        <v>5.5651</v>
       </c>
     </row>
     <row r="159">
@@ -8847,10 +8847,10 @@
         <v>0.98</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0404</v>
+        <v>-0.0337</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.1716</v>
+        <v>-0.9772999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8887,10 +8887,10 @@
         <v>0.83</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3304</v>
+        <v>-0.2046</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.5816</v>
+        <v>-5.9334</v>
       </c>
     </row>
     <row r="161">
@@ -8927,10 +8927,10 @@
         <v>0.66</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5657</v>
+        <v>-0.37</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.4053</v>
+        <v>-10.73</v>
       </c>
     </row>
     <row r="162">
@@ -8967,10 +8967,10 @@
         <v>1.27</v>
       </c>
       <c r="I162" t="n">
-        <v>0.435</v>
+        <v>0.401</v>
       </c>
       <c r="J162" t="n">
-        <v>20.445</v>
+        <v>18.847</v>
       </c>
     </row>
     <row r="163">
@@ -9007,10 +9007,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3932</v>
+        <v>0.3621</v>
       </c>
       <c r="J163" t="n">
-        <v>18.4804</v>
+        <v>17.0187</v>
       </c>
     </row>
     <row r="164">
@@ -9047,10 +9047,10 @@
         <v>1.15</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2531</v>
+        <v>0.2418</v>
       </c>
       <c r="J164" t="n">
-        <v>11.8957</v>
+        <v>11.3646</v>
       </c>
     </row>
     <row r="165">
@@ -9087,10 +9087,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.045</v>
+        <v>0.0728</v>
       </c>
       <c r="J165" t="n">
-        <v>2.115</v>
+        <v>3.4216</v>
       </c>
     </row>
     <row r="166">
@@ -9127,10 +9127,10 @@
         <v>0.99</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0337</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.2488</v>
+        <v>-1.5839</v>
       </c>
     </row>
     <row r="167">
@@ -9167,10 +9167,10 @@
         <v>1.05</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1557</v>
+        <v>0.1071</v>
       </c>
       <c r="J167" t="n">
-        <v>7.3179</v>
+        <v>5.0337</v>
       </c>
     </row>
     <row r="168">
@@ -9207,10 +9207,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0568</v>
+        <v>-0.0465</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.6696</v>
+        <v>-2.1855</v>
       </c>
     </row>
     <row r="169">
@@ -9247,10 +9247,10 @@
         <v>0.96</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0809</v>
+        <v>-0.0596</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.8023</v>
+        <v>-2.8012</v>
       </c>
     </row>
     <row r="170">
@@ -9287,10 +9287,10 @@
         <v>0.91</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1923</v>
+        <v>-0.1179</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.0381</v>
+        <v>-5.5413</v>
       </c>
     </row>
     <row r="171">
@@ -9327,10 +9327,10 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2623</v>
+        <v>-0.1614</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.3281</v>
+        <v>-7.5858</v>
       </c>
     </row>
     <row r="172">
@@ -9367,10 +9367,10 @@
         <v>1.82</v>
       </c>
       <c r="I172" t="n">
-        <v>1.7047</v>
+        <v>1.4701</v>
       </c>
       <c r="J172" t="n">
-        <v>34.094</v>
+        <v>29.402</v>
       </c>
     </row>
     <row r="173">
@@ -9407,10 +9407,10 @@
         <v>1.76</v>
       </c>
       <c r="I173" t="n">
-        <v>1.5982</v>
+        <v>1.4014</v>
       </c>
       <c r="J173" t="n">
-        <v>31.964</v>
+        <v>28.028</v>
       </c>
     </row>
     <row r="174">
@@ -9447,10 +9447,10 @@
         <v>1.35</v>
       </c>
       <c r="I174" t="n">
-        <v>0.7382</v>
+        <v>0.8562</v>
       </c>
       <c r="J174" t="n">
-        <v>14.764</v>
+        <v>17.124</v>
       </c>
     </row>
     <row r="175">
@@ -9487,10 +9487,10 @@
         <v>1.24</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4918</v>
+        <v>0.6054</v>
       </c>
       <c r="J175" t="n">
-        <v>9.836</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="176">
@@ -9527,10 +9527,10 @@
         <v>1.11</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1753</v>
+        <v>0.273</v>
       </c>
       <c r="J176" t="n">
-        <v>3.506</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="177">
@@ -9567,10 +9567,10 @@
         <v>0.88</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.0887</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J177" t="n">
-        <v>-1.774</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="178">
@@ -9607,10 +9607,10 @@
         <v>0.74</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.3133</v>
+        <v>-0.2529</v>
       </c>
       <c r="J178" t="n">
-        <v>-6.266</v>
+        <v>-5.058</v>
       </c>
     </row>
     <row r="179">
@@ -9647,10 +9647,10 @@
         <v>0.74</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3133</v>
+        <v>-0.2529</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.266</v>
+        <v>-5.058</v>
       </c>
     </row>
     <row r="180">
@@ -9687,10 +9687,10 @@
         <v>0.49</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.7137</v>
+        <v>-0.4854</v>
       </c>
       <c r="J180" t="n">
-        <v>-14.274</v>
+        <v>-9.708</v>
       </c>
     </row>
     <row r="181">
@@ -9727,10 +9727,10 @@
         <v>0.45</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.766</v>
+        <v>-0.5231</v>
       </c>
       <c r="J181" t="n">
-        <v>-15.32</v>
+        <v>-10.462</v>
       </c>
     </row>
     <row r="182">
@@ -9767,10 +9767,10 @@
         <v>1.16</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5482</v>
+        <v>0.5051</v>
       </c>
       <c r="J182" t="n">
-        <v>22.4762</v>
+        <v>20.7091</v>
       </c>
     </row>
     <row r="183">
@@ -9807,10 +9807,10 @@
         <v>1.03</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1329</v>
+        <v>0.1247</v>
       </c>
       <c r="J183" t="n">
-        <v>5.4489</v>
+        <v>5.1127</v>
       </c>
     </row>
     <row r="184">
@@ -9847,10 +9847,10 @@
         <v>1.02</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0805</v>
+        <v>0.0892</v>
       </c>
       <c r="J184" t="n">
-        <v>3.3005</v>
+        <v>3.6572</v>
       </c>
     </row>
     <row r="185">
@@ -9887,10 +9887,10 @@
         <v>0.98</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1395</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.7195</v>
+        <v>-4.0795</v>
       </c>
     </row>
     <row r="186">
@@ -9927,10 +9927,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2862</v>
+        <v>-0.2361</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.7342</v>
+        <v>-9.680099999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9967,10 +9967,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7159</v>
+        <v>0.8858</v>
       </c>
       <c r="J187" t="n">
-        <v>29.3519</v>
+        <v>36.3178</v>
       </c>
     </row>
     <row r="188">
@@ -10007,10 +10007,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1756</v>
+        <v>0.1967</v>
       </c>
       <c r="J188" t="n">
-        <v>7.1996</v>
+        <v>8.0647</v>
       </c>
     </row>
     <row r="189">
@@ -10047,10 +10047,10 @@
         <v>0.99</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0601</v>
+        <v>-0.024</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.4641</v>
+        <v>-0.984</v>
       </c>
     </row>
     <row r="190">
@@ -10087,10 +10087,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2561</v>
+        <v>-0.1497</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.5001</v>
+        <v>-6.1377</v>
       </c>
     </row>
     <row r="191">
@@ -10127,10 +10127,10 @@
         <v>0.77</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4342</v>
+        <v>-0.2733</v>
       </c>
       <c r="J191" t="n">
-        <v>-17.8022</v>
+        <v>-11.2053</v>
       </c>
     </row>
     <row r="192">
@@ -10167,10 +10167,10 @@
         <v>1.44</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1161</v>
+        <v>1.0715</v>
       </c>
       <c r="J192" t="n">
-        <v>29.0186</v>
+        <v>27.859</v>
       </c>
     </row>
     <row r="193">
@@ -10207,10 +10207,10 @@
         <v>1.36</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9457</v>
+        <v>0.9392</v>
       </c>
       <c r="J193" t="n">
-        <v>24.5882</v>
+        <v>24.4192</v>
       </c>
     </row>
     <row r="194">
@@ -10247,10 +10247,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3712</v>
+        <v>0.4176</v>
       </c>
       <c r="J194" t="n">
-        <v>9.651199999999999</v>
+        <v>10.8576</v>
       </c>
     </row>
     <row r="195">
@@ -10287,10 +10287,10 @@
         <v>1.05</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0977</v>
+        <v>0.1602</v>
       </c>
       <c r="J195" t="n">
-        <v>2.5402</v>
+        <v>4.1652</v>
       </c>
     </row>
     <row r="196">
@@ -10327,10 +10327,10 @@
         <v>0.85</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5989</v>
+        <v>-0.5352</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.5714</v>
+        <v>-13.9152</v>
       </c>
     </row>
     <row r="197">
@@ -10367,10 +10367,10 @@
         <v>1.46</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>19.1204</v>
+        <v>23.7588</v>
       </c>
     </row>
     <row r="198">
@@ -10407,10 +10407,10 @@
         <v>0.92</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1713</v>
+        <v>-0.1063</v>
       </c>
       <c r="J198" t="n">
-        <v>-4.4538</v>
+        <v>-2.7638</v>
       </c>
     </row>
     <row r="199">
@@ -10447,10 +10447,10 @@
         <v>0.89</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2267</v>
+        <v>-0.1395</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.8942</v>
+        <v>-3.627</v>
       </c>
     </row>
     <row r="200">
@@ -10487,10 +10487,10 @@
         <v>0.87</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2609</v>
+        <v>-0.1609</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.7834</v>
+        <v>-4.1834</v>
       </c>
     </row>
     <row r="201">
@@ -10527,10 +10527,10 @@
         <v>0.6</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6379</v>
+        <v>-0.4236</v>
       </c>
       <c r="J201" t="n">
-        <v>-16.5854</v>
+        <v>-11.0136</v>
       </c>
     </row>
     <row r="202">
@@ -10567,10 +10567,10 @@
         <v>1.47</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1516</v>
+        <v>1.0984</v>
       </c>
       <c r="J202" t="n">
-        <v>28.79</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="203">
@@ -10607,10 +10607,10 @@
         <v>1.32</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8337</v>
       </c>
       <c r="J203" t="n">
-        <v>20.6775</v>
+        <v>20.8425</v>
       </c>
     </row>
     <row r="204">
@@ -10647,10 +10647,10 @@
         <v>1.26</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6814</v>
+        <v>0.6964</v>
       </c>
       <c r="J204" t="n">
-        <v>17.035</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="205">
@@ -10687,10 +10687,10 @@
         <v>1.19</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4756</v>
+        <v>0.5333</v>
       </c>
       <c r="J205" t="n">
-        <v>11.89</v>
+        <v>13.3325</v>
       </c>
     </row>
     <row r="206">
@@ -10727,10 +10727,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5878</v>
+        <v>-0.5208</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.695</v>
+        <v>-13.02</v>
       </c>
     </row>
     <row r="207">
@@ -10767,10 +10767,10 @@
         <v>1.19</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4014</v>
+        <v>0.4533</v>
       </c>
       <c r="J207" t="n">
-        <v>10.035</v>
+        <v>11.3325</v>
       </c>
     </row>
     <row r="208">
@@ -10807,10 +10807,10 @@
         <v>0.99</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0137</v>
+        <v>-0.0115</v>
       </c>
       <c r="J208" t="n">
-        <v>0.3425</v>
+        <v>-0.2875</v>
       </c>
     </row>
     <row r="209">
@@ -10847,10 +10847,10 @@
         <v>0.95</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0784</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.96</v>
+        <v>-1.7025</v>
       </c>
     </row>
     <row r="210">
@@ -10887,10 +10887,10 @@
         <v>0.89</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2087</v>
+        <v>-0.1356</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.2175</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="211">
@@ -10927,10 +10927,10 @@
         <v>0.53</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7169</v>
+        <v>-0.4833</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.9225</v>
+        <v>-12.0825</v>
       </c>
     </row>
     <row r="212">
@@ -10967,10 +10967,10 @@
         <v>1.84</v>
       </c>
       <c r="I212" t="n">
-        <v>1.6981</v>
+        <v>1.4737</v>
       </c>
       <c r="J212" t="n">
-        <v>32.2639</v>
+        <v>28.0003</v>
       </c>
     </row>
     <row r="213">
@@ -11007,10 +11007,10 @@
         <v>1.55</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1247</v>
+        <v>1.1473</v>
       </c>
       <c r="J213" t="n">
-        <v>21.3693</v>
+        <v>21.7987</v>
       </c>
     </row>
     <row r="214">
@@ -11047,10 +11047,10 @@
         <v>1.54</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1013</v>
+        <v>1.136</v>
       </c>
       <c r="J214" t="n">
-        <v>20.9247</v>
+        <v>21.584</v>
       </c>
     </row>
     <row r="215">
@@ -11087,10 +11087,10 @@
         <v>1.49</v>
       </c>
       <c r="I215" t="n">
-        <v>0.993</v>
+        <v>1.0776</v>
       </c>
       <c r="J215" t="n">
-        <v>18.867</v>
+        <v>20.4744</v>
       </c>
     </row>
     <row r="216">
@@ -11127,10 +11127,10 @@
         <v>1.38</v>
       </c>
       <c r="I216" t="n">
-        <v>0.7635</v>
+        <v>0.9015</v>
       </c>
       <c r="J216" t="n">
-        <v>14.5065</v>
+        <v>17.1285</v>
       </c>
     </row>
     <row r="217">
@@ -11167,10 +11167,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I217" t="n">
-        <v>0.0648</v>
+        <v>0.0295</v>
       </c>
       <c r="J217" t="n">
-        <v>1.2312</v>
+        <v>0.5605</v>
       </c>
     </row>
     <row r="218">
@@ -11207,10 +11207,10 @@
         <v>0.66</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3876</v>
+        <v>-0.3121</v>
       </c>
       <c r="J218" t="n">
-        <v>-7.3644</v>
+        <v>-5.9299</v>
       </c>
     </row>
     <row r="219">
@@ -11247,10 +11247,10 @@
         <v>0.59</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.5029</v>
+        <v>-0.3791</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.555099999999999</v>
+        <v>-7.2029</v>
       </c>
     </row>
     <row r="220">
@@ -11287,10 +11287,10 @@
         <v>0.42</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.7799</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="J220" t="n">
-        <v>-14.8181</v>
+        <v>-10.1802</v>
       </c>
     </row>
     <row r="221">
@@ -11327,10 +11327,10 @@
         <v>0.26</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.9851</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="J221" t="n">
-        <v>-18.7169</v>
+        <v>-13.129</v>
       </c>
     </row>
     <row r="222">
@@ -11367,10 +11367,10 @@
         <v>1.14</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4742</v>
+        <v>0.4414</v>
       </c>
       <c r="J222" t="n">
-        <v>12.8034</v>
+        <v>11.9178</v>
       </c>
     </row>
     <row r="223">
@@ -11407,10 +11407,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3872</v>
+        <v>0.3597</v>
       </c>
       <c r="J223" t="n">
-        <v>10.4544</v>
+        <v>9.7119</v>
       </c>
     </row>
     <row r="224">
@@ -11447,10 +11447,10 @@
         <v>1.06</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2191</v>
+        <v>0.2158</v>
       </c>
       <c r="J224" t="n">
-        <v>5.9157</v>
+        <v>5.8266</v>
       </c>
     </row>
     <row r="225">
@@ -11487,10 +11487,10 @@
         <v>0.99</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.115</v>
+        <v>-0.0663</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.105</v>
+        <v>-1.7901</v>
       </c>
     </row>
     <row r="226">
@@ -11527,10 +11527,10 @@
         <v>0.98</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.159</v>
+        <v>-0.1071</v>
       </c>
       <c r="J226" t="n">
-        <v>-4.293</v>
+        <v>-2.8917</v>
       </c>
     </row>
     <row r="227">
@@ -11567,10 +11567,10 @@
         <v>1.37</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5863</v>
+        <v>0.7103</v>
       </c>
       <c r="J227" t="n">
-        <v>15.8301</v>
+        <v>19.1781</v>
       </c>
     </row>
     <row r="228">
@@ -11607,10 +11607,10 @@
         <v>1.32</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5232</v>
+        <v>0.6269</v>
       </c>
       <c r="J228" t="n">
-        <v>14.1264</v>
+        <v>16.9263</v>
       </c>
     </row>
     <row r="229">
@@ -11647,10 +11647,10 @@
         <v>1.19</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3445</v>
+        <v>0.4009</v>
       </c>
       <c r="J229" t="n">
-        <v>9.301500000000001</v>
+        <v>10.8243</v>
       </c>
     </row>
     <row r="230">
@@ -11687,10 +11687,10 @@
         <v>0.82</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3699</v>
+        <v>-0.2267</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.987299999999999</v>
+        <v>-6.1209</v>
       </c>
     </row>
     <row r="231">
@@ -11727,10 +11727,10 @@
         <v>0.65</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5946</v>
+        <v>-0.3903</v>
       </c>
       <c r="J231" t="n">
-        <v>-16.0542</v>
+        <v>-10.5381</v>
       </c>
     </row>
     <row r="232">
@@ -11767,10 +11767,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4131</v>
+        <v>1.2633</v>
       </c>
       <c r="J232" t="n">
-        <v>42.393</v>
+        <v>37.899</v>
       </c>
     </row>
     <row r="233">
@@ -11807,10 +11807,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3404</v>
+        <v>0.3718</v>
       </c>
       <c r="J233" t="n">
-        <v>10.212</v>
+        <v>11.154</v>
       </c>
     </row>
     <row r="234">
@@ -11847,10 +11847,10 @@
         <v>1.07</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1819</v>
+        <v>0.2312</v>
       </c>
       <c r="J234" t="n">
-        <v>5.457</v>
+        <v>6.936</v>
       </c>
     </row>
     <row r="235">
@@ -11887,10 +11887,10 @@
         <v>1.01</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0361</v>
+        <v>0.0236</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.083</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="236">
@@ -11927,10 +11927,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5092</v>
+        <v>-0.443</v>
       </c>
       <c r="J236" t="n">
-        <v>-15.276</v>
+        <v>-13.29</v>
       </c>
     </row>
     <row r="237">
@@ -11967,10 +11967,10 @@
         <v>1.09</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2537</v>
+        <v>0.2604</v>
       </c>
       <c r="J237" t="n">
-        <v>7.611</v>
+        <v>7.812</v>
       </c>
     </row>
     <row r="238">
@@ -12007,10 +12007,10 @@
         <v>0.9</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1672</v>
+        <v>-0.1235</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.016</v>
+        <v>-3.705</v>
       </c>
     </row>
     <row r="239">
@@ -12047,10 +12047,10 @@
         <v>0.89</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.189</v>
+        <v>-0.134</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.67</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="240">
@@ -12087,10 +12087,10 @@
         <v>0.83</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3037</v>
+        <v>-0.1953</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.111000000000001</v>
+        <v>-5.859</v>
       </c>
     </row>
     <row r="241">
@@ -12127,10 +12127,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4547</v>
+        <v>-0.2939</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.641</v>
+        <v>-8.817</v>
       </c>
     </row>
     <row r="242">
@@ -12167,10 +12167,10 @@
         <v>0.85</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.53</v>
+        <v>-0.4836</v>
       </c>
       <c r="J242" t="n">
-        <v>-14.31</v>
+        <v>-13.0572</v>
       </c>
     </row>
     <row r="243">
@@ -12207,10 +12207,10 @@
         <v>0.68</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.9453</v>
+        <v>-0.9182</v>
       </c>
       <c r="J243" t="n">
-        <v>-25.5231</v>
+        <v>-24.7914</v>
       </c>
     </row>
     <row r="244">
@@ -12247,10 +12247,10 @@
         <v>0.57</v>
       </c>
       <c r="I244" t="n">
-        <v>-1.1827</v>
+        <v>-1.1822</v>
       </c>
       <c r="J244" t="n">
-        <v>-31.9329</v>
+        <v>-31.9194</v>
       </c>
     </row>
     <row r="245">
@@ -12287,10 +12287,10 @@
         <v>1.51</v>
       </c>
       <c r="I245" t="n">
-        <v>1.3583</v>
+        <v>1.2266</v>
       </c>
       <c r="J245" t="n">
-        <v>36.6741</v>
+        <v>33.1182</v>
       </c>
     </row>
     <row r="246">
@@ -12327,10 +12327,10 @@
         <v>1.31</v>
       </c>
       <c r="I246" t="n">
-        <v>0.9372</v>
+        <v>0.9071</v>
       </c>
       <c r="J246" t="n">
-        <v>25.3044</v>
+        <v>24.4917</v>
       </c>
     </row>
     <row r="247">
@@ -12367,10 +12367,10 @@
         <v>1.16</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3692</v>
+        <v>0.4089</v>
       </c>
       <c r="J247" t="n">
-        <v>9.968400000000001</v>
+        <v>11.0403</v>
       </c>
     </row>
     <row r="248">
@@ -12407,10 +12407,10 @@
         <v>0.72</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.4659</v>
+        <v>-0.3022</v>
       </c>
       <c r="J248" t="n">
-        <v>-12.5793</v>
+        <v>-8.1594</v>
       </c>
     </row>
     <row r="249">
@@ -12447,10 +12447,10 @@
         <v>0.37</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.6238</v>
       </c>
       <c r="J249" t="n">
-        <v>-24.2379</v>
+        <v>-16.8426</v>
       </c>
     </row>
     <row r="250">
@@ -12487,10 +12487,10 @@
         <v>1.12</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3072</v>
+        <v>0.3278</v>
       </c>
       <c r="J250" t="n">
-        <v>8.2944</v>
+        <v>8.8506</v>
       </c>
     </row>
     <row r="251">
@@ -12527,10 +12527,10 @@
         <v>1.02</v>
       </c>
       <c r="I251" t="n">
-        <v>0.122</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="J251" t="n">
-        <v>3.294</v>
+        <v>2.6082</v>
       </c>
     </row>
     <row r="252">
@@ -12567,10 +12567,10 @@
         <v>0.8</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.6493</v>
+        <v>-0.6082</v>
       </c>
       <c r="J252" t="n">
-        <v>-18.8297</v>
+        <v>-17.6378</v>
       </c>
     </row>
     <row r="253">
@@ -12607,10 +12607,10 @@
         <v>0.67</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.9594</v>
+        <v>-0.9348</v>
       </c>
       <c r="J253" t="n">
-        <v>-27.8226</v>
+        <v>-27.1092</v>
       </c>
     </row>
     <row r="254">
@@ -12647,10 +12647,10 @@
         <v>0.67</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.9594</v>
+        <v>-0.9348</v>
       </c>
       <c r="J254" t="n">
-        <v>-27.8226</v>
+        <v>-27.1092</v>
       </c>
     </row>
     <row r="255">
@@ -12687,10 +12687,10 @@
         <v>1.5</v>
       </c>
       <c r="I255" t="n">
-        <v>1.3542</v>
+        <v>1.2246</v>
       </c>
       <c r="J255" t="n">
-        <v>39.2718</v>
+        <v>35.5134</v>
       </c>
     </row>
     <row r="256">
@@ -12727,10 +12727,10 @@
         <v>1.15</v>
       </c>
       <c r="I256" t="n">
-        <v>0.5642</v>
+        <v>0.5069</v>
       </c>
       <c r="J256" t="n">
-        <v>16.3618</v>
+        <v>14.7001</v>
       </c>
     </row>
     <row r="257">
@@ -12767,10 +12767,10 @@
         <v>0.88</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.2243</v>
+        <v>-0.1456</v>
       </c>
       <c r="J257" t="n">
-        <v>-6.5047</v>
+        <v>-4.2224</v>
       </c>
     </row>
     <row r="258">
@@ -12807,10 +12807,10 @@
         <v>0.86</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2601</v>
+        <v>-0.1665</v>
       </c>
       <c r="J258" t="n">
-        <v>-7.5429</v>
+        <v>-4.8285</v>
       </c>
     </row>
     <row r="259">
@@ -12847,10 +12847,10 @@
         <v>0.61</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.6177</v>
+        <v>-0.4092</v>
       </c>
       <c r="J259" t="n">
-        <v>-17.9133</v>
+        <v>-11.8668</v>
       </c>
     </row>
     <row r="260">
@@ -12887,10 +12887,10 @@
         <v>1.14</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3288</v>
+        <v>0.358</v>
       </c>
       <c r="J260" t="n">
-        <v>9.5352</v>
+        <v>10.382</v>
       </c>
     </row>
     <row r="261">
@@ -12927,10 +12927,10 @@
         <v>1.03</v>
       </c>
       <c r="I261" t="n">
-        <v>0.1339</v>
+        <v>0.1152</v>
       </c>
       <c r="J261" t="n">
-        <v>3.8831</v>
+        <v>3.3408</v>
       </c>
     </row>
     <row r="262">
@@ -12967,10 +12967,10 @@
         <v>1.64</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4513</v>
+        <v>1.2949</v>
       </c>
       <c r="J262" t="n">
-        <v>33.3799</v>
+        <v>29.7827</v>
       </c>
     </row>
     <row r="263">
@@ -13007,10 +13007,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0128</v>
+        <v>1.0172</v>
       </c>
       <c r="J263" t="n">
-        <v>23.2944</v>
+        <v>23.3956</v>
       </c>
     </row>
     <row r="264">
@@ -13047,10 +13047,10 @@
         <v>1.3</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7325</v>
+        <v>0.7743</v>
       </c>
       <c r="J264" t="n">
-        <v>16.8475</v>
+        <v>17.8089</v>
       </c>
     </row>
     <row r="265">
@@ -13087,10 +13087,10 @@
         <v>1.27</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6411</v>
+        <v>0.7087</v>
       </c>
       <c r="J265" t="n">
-        <v>14.7453</v>
+        <v>16.3001</v>
       </c>
     </row>
     <row r="266">
@@ -13127,10 +13127,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7261</v>
+        <v>-0.6691</v>
       </c>
       <c r="J266" t="n">
-        <v>-16.7003</v>
+        <v>-15.3893</v>
       </c>
     </row>
     <row r="267">
@@ -13167,10 +13167,10 @@
         <v>1.07</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2368</v>
+        <v>0.2346</v>
       </c>
       <c r="J267" t="n">
-        <v>5.4464</v>
+        <v>5.3958</v>
       </c>
     </row>
     <row r="268">
@@ -13207,10 +13207,10 @@
         <v>1.06</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2186</v>
+        <v>0.2114</v>
       </c>
       <c r="J268" t="n">
-        <v>5.0278</v>
+        <v>4.8622</v>
       </c>
     </row>
     <row r="269">
@@ -13247,10 +13247,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3649</v>
+        <v>-0.2393</v>
       </c>
       <c r="J269" t="n">
-        <v>-8.3927</v>
+        <v>-5.5039</v>
       </c>
     </row>
     <row r="270">
@@ -13287,10 +13287,10 @@
         <v>0.68</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5114</v>
+        <v>-0.3354</v>
       </c>
       <c r="J270" t="n">
-        <v>-11.7622</v>
+        <v>-7.7142</v>
       </c>
     </row>
     <row r="271">
@@ -13327,10 +13327,10 @@
         <v>0.62</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5918</v>
+        <v>-0.3919</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.6114</v>
+        <v>-9.0137</v>
       </c>
     </row>
     <row r="272">
@@ -13367,10 +13367,10 @@
         <v>1.55</v>
       </c>
       <c r="I272" t="n">
-        <v>1.3171</v>
+        <v>1.2031</v>
       </c>
       <c r="J272" t="n">
-        <v>35.5617</v>
+        <v>32.4837</v>
       </c>
     </row>
     <row r="273">
@@ -13407,10 +13407,10 @@
         <v>1.3</v>
       </c>
       <c r="I273" t="n">
-        <v>0.7872</v>
+        <v>0.7913</v>
       </c>
       <c r="J273" t="n">
-        <v>21.2544</v>
+        <v>21.3651</v>
       </c>
     </row>
     <row r="274">
@@ -13447,10 +13447,10 @@
         <v>1.29</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7634</v>
+        <v>0.7684</v>
       </c>
       <c r="J274" t="n">
-        <v>20.6118</v>
+        <v>20.7468</v>
       </c>
     </row>
     <row r="275">
@@ -13487,10 +13487,10 @@
         <v>1.18</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4565</v>
+        <v>0.511</v>
       </c>
       <c r="J275" t="n">
-        <v>12.3255</v>
+        <v>13.797</v>
       </c>
     </row>
     <row r="276">
@@ -13527,10 +13527,10 @@
         <v>0.72</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.9135</v>
+        <v>-0.8776</v>
       </c>
       <c r="J276" t="n">
-        <v>-24.6645</v>
+        <v>-23.6952</v>
       </c>
     </row>
     <row r="277">
@@ -13567,10 +13567,10 @@
         <v>1.06</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1892</v>
+        <v>0.184</v>
       </c>
       <c r="J277" t="n">
-        <v>5.1084</v>
+        <v>4.968</v>
       </c>
     </row>
     <row r="278">
@@ -13607,10 +13607,10 @@
         <v>1.02</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1064</v>
+        <v>0.0849</v>
       </c>
       <c r="J278" t="n">
-        <v>2.8728</v>
+        <v>2.2923</v>
       </c>
     </row>
     <row r="279">
@@ -13647,10 +13647,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0461</v>
+        <v>0.0164</v>
       </c>
       <c r="J279" t="n">
-        <v>1.2447</v>
+        <v>0.4428</v>
       </c>
     </row>
     <row r="280">
@@ -13687,10 +13687,10 @@
         <v>0.8</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.361</v>
+        <v>-0.2289</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.747</v>
+        <v>-6.1803</v>
       </c>
     </row>
     <row r="281">
@@ -13727,10 +13727,10 @@
         <v>0.7</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5031</v>
+        <v>-0.3262</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.5837</v>
+        <v>-8.807399999999999</v>
       </c>
     </row>
     <row r="282">
@@ -13767,10 +13767,10 @@
         <v>0.99</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.0726</v>
+        <v>-0.0538</v>
       </c>
       <c r="J282" t="n">
-        <v>-2.6136</v>
+        <v>-1.9368</v>
       </c>
     </row>
     <row r="283">
@@ -13807,10 +13807,10 @@
         <v>0.96</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.2007</v>
+        <v>-0.1648</v>
       </c>
       <c r="J283" t="n">
-        <v>-7.2252</v>
+        <v>-5.9328</v>
       </c>
     </row>
     <row r="284">
@@ -13847,10 +13847,10 @@
         <v>0.91</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3675</v>
+        <v>-0.3203</v>
       </c>
       <c r="J284" t="n">
-        <v>-13.23</v>
+        <v>-11.5308</v>
       </c>
     </row>
     <row r="285">
@@ -13887,10 +13887,10 @@
         <v>1.09</v>
       </c>
       <c r="I285" t="n">
-        <v>0.365</v>
+        <v>0.3191</v>
       </c>
       <c r="J285" t="n">
-        <v>13.14</v>
+        <v>11.4876</v>
       </c>
     </row>
     <row r="286">
@@ -13927,10 +13927,10 @@
         <v>1.06</v>
       </c>
       <c r="I286" t="n">
-        <v>0.2686</v>
+        <v>0.2284</v>
       </c>
       <c r="J286" t="n">
-        <v>9.669600000000001</v>
+        <v>8.2224</v>
       </c>
     </row>
     <row r="287">
@@ -13967,10 +13967,10 @@
         <v>0.78</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.378</v>
+        <v>-0.2436</v>
       </c>
       <c r="J287" t="n">
-        <v>-13.608</v>
+        <v>-8.769600000000001</v>
       </c>
     </row>
     <row r="288">
@@ -14007,10 +14007,10 @@
         <v>0.61</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.6121</v>
+        <v>-0.4057</v>
       </c>
       <c r="J288" t="n">
-        <v>-22.0356</v>
+        <v>-14.6052</v>
       </c>
     </row>
     <row r="289">
@@ -14047,10 +14047,10 @@
         <v>0.33</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.9419</v>
+        <v>-0.6591</v>
       </c>
       <c r="J289" t="n">
-        <v>-33.9084</v>
+        <v>-23.7276</v>
       </c>
     </row>
     <row r="290">
@@ -14087,10 +14087,10 @@
         <v>1.34</v>
       </c>
       <c r="I290" t="n">
-        <v>0.616</v>
+        <v>0.7472</v>
       </c>
       <c r="J290" t="n">
-        <v>22.176</v>
+        <v>26.8992</v>
       </c>
     </row>
     <row r="291">
@@ -14127,10 +14127,10 @@
         <v>1.32</v>
       </c>
       <c r="I291" t="n">
-        <v>0.5905</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J291" t="n">
-        <v>21.258</v>
+        <v>25.6032</v>
       </c>
     </row>
     <row r="292">
@@ -14167,10 +14167,10 @@
         <v>0.76</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.3331</v>
+        <v>-0.2479</v>
       </c>
       <c r="J292" t="n">
-        <v>-7.6613</v>
+        <v>-5.7017</v>
       </c>
     </row>
     <row r="293">
@@ -14207,10 +14207,10 @@
         <v>0.74</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.3776</v>
+        <v>-0.2659</v>
       </c>
       <c r="J293" t="n">
-        <v>-8.684799999999999</v>
+        <v>-6.1157</v>
       </c>
     </row>
     <row r="294">
@@ -14247,10 +14247,10 @@
         <v>0.58</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.6194</v>
+        <v>-0.4153</v>
       </c>
       <c r="J294" t="n">
-        <v>-14.2462</v>
+        <v>-9.5519</v>
       </c>
     </row>
     <row r="295">
@@ -14287,10 +14287,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1475</v>
+        <v>-0.1345</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.3925</v>
+        <v>-3.0935</v>
       </c>
     </row>
     <row r="296">
@@ -14327,10 +14327,10 @@
         <v>0.78</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2977</v>
+        <v>-0.2288</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.8471</v>
+        <v>-5.2624</v>
       </c>
     </row>
     <row r="297">
@@ -14367,10 +14367,10 @@
         <v>0.46</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.5423</v>
       </c>
       <c r="J297" t="n">
-        <v>-18.2597</v>
+        <v>-12.4729</v>
       </c>
     </row>
     <row r="298">
@@ -14407,10 +14407,10 @@
         <v>0.23</v>
       </c>
       <c r="I298" t="n">
-        <v>-1.0498</v>
+        <v>-0.7469</v>
       </c>
       <c r="J298" t="n">
-        <v>-24.1454</v>
+        <v>-17.1787</v>
       </c>
     </row>
     <row r="299">
@@ -14447,10 +14447,10 @@
         <v>0.21</v>
       </c>
       <c r="I299" t="n">
-        <v>-1.071</v>
+        <v>-0.7644</v>
       </c>
       <c r="J299" t="n">
-        <v>-24.633</v>
+        <v>-17.5812</v>
       </c>
     </row>
     <row r="300">
@@ -14487,10 +14487,10 @@
         <v>2</v>
       </c>
       <c r="I300" t="n">
-        <v>1.3393</v>
+        <v>1.1908</v>
       </c>
       <c r="J300" t="n">
-        <v>30.8039</v>
+        <v>27.3884</v>
       </c>
     </row>
     <row r="301">
@@ -14527,10 +14527,10 @@
         <v>1.45</v>
       </c>
       <c r="I301" t="n">
-        <v>0.7529</v>
+        <v>0.673</v>
       </c>
       <c r="J301" t="n">
-        <v>17.3167</v>
+        <v>15.479</v>
       </c>
     </row>
     <row r="302">
@@ -14567,10 +14567,10 @@
         <v>1.21</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6708</v>
+        <v>0.6314</v>
       </c>
       <c r="J302" t="n">
-        <v>19.4532</v>
+        <v>18.3106</v>
       </c>
     </row>
     <row r="303">
@@ -14607,10 +14607,10 @@
         <v>0.95</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2584</v>
+        <v>-0.2068</v>
       </c>
       <c r="J303" t="n">
-        <v>-7.4936</v>
+        <v>-5.9972</v>
       </c>
     </row>
     <row r="304">
@@ -14647,10 +14647,10 @@
         <v>0.78</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.7301</v>
+        <v>-0.6835</v>
       </c>
       <c r="J304" t="n">
-        <v>-21.1729</v>
+        <v>-19.8215</v>
       </c>
     </row>
     <row r="305">
@@ -14687,10 +14687,10 @@
         <v>1.13</v>
       </c>
       <c r="I305" t="n">
-        <v>0.4594</v>
+        <v>0.4208</v>
       </c>
       <c r="J305" t="n">
-        <v>13.3226</v>
+        <v>12.2032</v>
       </c>
     </row>
     <row r="306">
@@ -14727,10 +14727,10 @@
         <v>1.11</v>
       </c>
       <c r="I306" t="n">
-        <v>0.4015</v>
+        <v>0.3655</v>
       </c>
       <c r="J306" t="n">
-        <v>11.6435</v>
+        <v>10.5995</v>
       </c>
     </row>
     <row r="307">
@@ -14767,10 +14767,10 @@
         <v>1.1</v>
       </c>
       <c r="I307" t="n">
-        <v>0.1626</v>
+        <v>0.2255</v>
       </c>
       <c r="J307" t="n">
-        <v>4.7154</v>
+        <v>6.5395</v>
       </c>
     </row>
     <row r="308">
@@ -14807,10 +14807,10 @@
         <v>0.98</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1113</v>
+        <v>-0.0481</v>
       </c>
       <c r="J308" t="n">
-        <v>-3.2277</v>
+        <v>-1.3949</v>
       </c>
     </row>
     <row r="309">
@@ -14847,10 +14847,10 @@
         <v>0.98</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1113</v>
+        <v>-0.0481</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.2277</v>
+        <v>-1.3949</v>
       </c>
     </row>
     <row r="310">
@@ -14887,10 +14887,10 @@
         <v>1.57</v>
       </c>
       <c r="I310" t="n">
-        <v>0.8034</v>
+        <v>0.9974</v>
       </c>
       <c r="J310" t="n">
-        <v>23.2986</v>
+        <v>28.9246</v>
       </c>
     </row>
     <row r="311">
@@ -14927,10 +14927,10 @@
         <v>0.99</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.0868</v>
+        <v>-0.0323</v>
       </c>
       <c r="J311" t="n">
-        <v>-2.5172</v>
+        <v>-0.9367</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5528/event_5528_evp_summary.xlsx
+++ b/database/event/5528/event_5528_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2968</v>
+        <v>6.2645</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6354</v>
+        <v>2.6219</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2047</v>
+        <v>2.2275</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2968</v>
+        <v>6.2645</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8784</v>
+        <v>2.7396</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4184</v>
+        <v>3.5249</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6552</v>
+        <v>4.1449</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4205</v>
+        <v>2.2382</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4184</v>
+        <v>3.5249</v>
       </c>
       <c r="K2" t="n">
         <v>197</v>
@@ -529,7 +529,7 @@
         <v>134</v>
       </c>
       <c r="M2" t="n">
-        <v>5.838900000000001</v>
+        <v>5.7631</v>
       </c>
       <c r="N2" t="n">
         <v>331</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.4924</v>
+        <v>4.6072</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8802</v>
+        <v>1.9282</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3901</v>
+        <v>1.4731</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4924</v>
+        <v>4.6072</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8261</v>
+        <v>2.7795</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6663</v>
+        <v>1.8277</v>
       </c>
       <c r="H3" t="n">
-        <v>4.471</v>
+        <v>4.2765</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3247</v>
+        <v>2.3093</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6663</v>
+        <v>1.8277</v>
       </c>
       <c r="K3" t="n">
         <v>167</v>
@@ -575,7 +575,7 @@
         <v>137</v>
       </c>
       <c r="M3" t="n">
-        <v>3.991</v>
+        <v>4.137</v>
       </c>
       <c r="N3" t="n">
         <v>304</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4568</v>
+        <v>4.4511</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8653</v>
+        <v>1.8629</v>
       </c>
       <c r="D4" t="n">
-        <v>1.374</v>
+        <v>1.402</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4568</v>
+        <v>4.4511</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2281</v>
+        <v>3.1453</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2287</v>
+        <v>1.3058</v>
       </c>
       <c r="H4" t="n">
-        <v>5.8874</v>
+        <v>5.4832</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0612</v>
+        <v>2.9609</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2287</v>
+        <v>1.3058</v>
       </c>
       <c r="K4" t="n">
         <v>167</v>
@@ -621,7 +621,7 @@
         <v>137</v>
       </c>
       <c r="M4" t="n">
-        <v>4.289899999999999</v>
+        <v>4.2667</v>
       </c>
       <c r="N4" t="n">
         <v>304</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5662</v>
+        <v>3.4888</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4925</v>
+        <v>1.4602</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9719</v>
+        <v>0.964</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5662</v>
+        <v>3.4888</v>
       </c>
       <c r="F5" t="n">
-        <v>4.045</v>
+        <v>3.9297</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4788</v>
+        <v>-0.4409</v>
       </c>
       <c r="H5" t="n">
-        <v>8.765599999999999</v>
+        <v>8.071199999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5577</v>
+        <v>4.3584</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4788</v>
+        <v>-0.4409</v>
       </c>
       <c r="K5" t="n">
         <v>117</v>
@@ -667,7 +667,7 @@
         <v>56</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0789</v>
+        <v>3.9175</v>
       </c>
       <c r="N5" t="n">
         <v>173</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8158</v>
+        <v>2.7646</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1785</v>
+        <v>1.1571</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6332</v>
+        <v>0.6343</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8158</v>
+        <v>2.7646</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4686</v>
+        <v>2.3835</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3472</v>
+        <v>0.3811</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2114</v>
+        <v>2.9699</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6698</v>
+        <v>1.6037</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3472</v>
+        <v>0.3811</v>
       </c>
       <c r="K6" t="n">
         <v>96</v>
@@ -713,7 +713,7 @@
         <v>57</v>
       </c>
       <c r="M6" t="n">
-        <v>2.017</v>
+        <v>1.9848</v>
       </c>
       <c r="N6" t="n">
         <v>153</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7758</v>
+        <v>2.7234</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1617</v>
+        <v>1.1398</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6151</v>
+        <v>0.6155</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7758</v>
+        <v>2.7234</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1579</v>
+        <v>3.0481</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3821</v>
+        <v>-0.3247</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6401</v>
+        <v>5.1625</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9326</v>
+        <v>2.7877</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3821</v>
+        <v>-0.3247</v>
       </c>
       <c r="K7" t="n">
         <v>144</v>
@@ -759,7 +759,7 @@
         <v>106</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5505</v>
+        <v>2.463</v>
       </c>
       <c r="N7" t="n">
         <v>250</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6363</v>
+        <v>2.5105</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1034</v>
+        <v>1.0507</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5521</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6363</v>
+        <v>2.5105</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6363</v>
+        <v>2.5105</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6363</v>
+        <v>2.7697</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8576</v>
+        <v>3.1454</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8576</v>
+        <v>3.1454</v>
       </c>
       <c r="N8" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5421</v>
+        <v>2.4424</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0639</v>
+        <v>1.0222</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.4876</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5421</v>
+        <v>2.4424</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5421</v>
+        <v>2.4424</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5421</v>
+        <v>2.6207</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1096</v>
+        <v>2.7575</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1096</v>
+        <v>2.7575</v>
       </c>
       <c r="N9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5292</v>
+        <v>2.4092</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0585</v>
+        <v>1.0083</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5038</v>
+        <v>0.4725</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5292</v>
+        <v>2.4092</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5292</v>
+        <v>2.4092</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5292</v>
+        <v>2.5479</v>
       </c>
       <c r="I10" t="n">
-        <v>3.0939</v>
+        <v>2.8936</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0939</v>
+        <v>2.8936</v>
       </c>
       <c r="N10" t="n">
         <v>170</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4481</v>
+        <v>2.3658</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0246</v>
+        <v>0.9901</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4672</v>
+        <v>0.4528</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4481</v>
+        <v>2.3658</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4868</v>
+        <v>2.409</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0387</v>
+        <v>-0.0432</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2755</v>
+        <v>3.0539</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7031</v>
+        <v>1.6491</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0387</v>
+        <v>-0.0432</v>
       </c>
       <c r="K11" t="n">
         <v>167</v>
@@ -943,7 +943,7 @@
         <v>137</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6644</v>
+        <v>1.6059</v>
       </c>
       <c r="N11" t="n">
         <v>304</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9543</v>
+        <v>1.845</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8179</v>
+        <v>0.7722</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2443</v>
+        <v>0.2157</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9543</v>
+        <v>1.845</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3805</v>
+        <v>1.2171</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5738</v>
+        <v>0.6279</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3805</v>
+        <v>1.2171</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7178</v>
+        <v>0.6572</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5738</v>
+        <v>0.6279</v>
       </c>
       <c r="K12" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="L12" t="n">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2916</v>
+        <v>1.2851</v>
       </c>
       <c r="N12" t="n">
-        <v>337</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8769</v>
+        <v>1.7625</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7855</v>
+        <v>0.7377</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2093</v>
+        <v>0.1781</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8769</v>
+        <v>1.7625</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4547</v>
+        <v>1.1363</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4222</v>
+        <v>0.6262</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4547</v>
+        <v>1.1363</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7564</v>
+        <v>0.6136</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4222</v>
+        <v>0.6262</v>
       </c>
       <c r="K13" t="n">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="L13" t="n">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1786</v>
+        <v>1.2398</v>
       </c>
       <c r="N13" t="n">
-        <v>290</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7532</v>
+        <v>1.6309</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7338</v>
+        <v>0.6826</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1535</v>
+        <v>0.1182</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7532</v>
+        <v>1.6309</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5617</v>
+        <v>1.4347</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1915</v>
+        <v>0.1962</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5617</v>
+        <v>1.4347</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1915</v>
+        <v>0.1962</v>
       </c>
       <c r="K14" t="n">
         <v>90</v>
@@ -1081,7 +1081,7 @@
         <v>25</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0035</v>
+        <v>0.9709000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>115</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5286</v>
+        <v>1.4877</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6398</v>
+        <v>0.6226</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0521</v>
+        <v>0.053</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5286</v>
+        <v>1.4877</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5286</v>
+        <v>1.4877</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5286</v>
+        <v>1.4877</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5915</v>
+        <v>1.526</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5915</v>
+        <v>1.526</v>
       </c>
       <c r="N15" t="n">
         <v>153</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3288</v>
+        <v>1.2272</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5561</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0381</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3288</v>
+        <v>1.2272</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6138</v>
+        <v>2.5446</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.285</v>
+        <v>-1.3174</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7232</v>
+        <v>3.5015</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9359</v>
+        <v>1.8908</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.285</v>
+        <v>-1.3174</v>
       </c>
       <c r="K16" t="n">
         <v>167</v>
@@ -1173,7 +1173,7 @@
         <v>137</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6509</v>
+        <v>0.5734000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>304</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2278</v>
+        <v>1.2227</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5139</v>
+        <v>0.5117</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0837</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2278</v>
+        <v>1.2227</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2278</v>
+        <v>1.2227</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2278</v>
+        <v>1.2227</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3309</v>
+        <v>1.2865</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3309</v>
+        <v>1.2865</v>
       </c>
       <c r="N17" t="n">
         <v>172</v>
@@ -1228,139 +1228,139 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0642</v>
+        <v>1.0061</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4454</v>
+        <v>0.4211</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1576</v>
+        <v>-0.1662</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0642</v>
+        <v>1.0061</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8897</v>
+        <v>1.1226</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1745</v>
+        <v>-0.1165</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8897</v>
+        <v>1.1226</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4626</v>
+        <v>0.6062</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1745</v>
+        <v>-0.1165</v>
       </c>
       <c r="K18" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="L18" t="n">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6371</v>
+        <v>0.4897</v>
       </c>
       <c r="N18" t="n">
-        <v>212</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9409</v>
+        <v>0.9629</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3938</v>
+        <v>0.403</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2132</v>
+        <v>-0.1859</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9409</v>
+        <v>0.9629</v>
       </c>
       <c r="F19" t="n">
-        <v>1.082</v>
+        <v>0.9629</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1411</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.082</v>
+        <v>0.9629</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5626</v>
+        <v>1.0935</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1411</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="L19" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4215</v>
+        <v>1.0935</v>
       </c>
       <c r="N19" t="n">
-        <v>304</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8984</v>
+        <v>0.8864</v>
       </c>
       <c r="C20" t="n">
-        <v>0.376</v>
+        <v>0.371</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2324</v>
+        <v>-0.2207</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8984</v>
+        <v>0.8864</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8984</v>
+        <v>0.7202</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1662</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8984</v>
+        <v>0.7202</v>
       </c>
       <c r="I20" t="n">
-        <v>1.099</v>
+        <v>0.3889</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1662</v>
       </c>
       <c r="K20" t="n">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M20" t="n">
-        <v>1.099</v>
+        <v>0.5551</v>
       </c>
       <c r="N20" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4713</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1973</v>
+        <v>0.2411</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4252</v>
+        <v>-0.362</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4713</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4713</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4713</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5765</v>
+        <v>0.6542</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5765</v>
+        <v>0.6542</v>
       </c>
       <c r="N21" t="n">
         <v>216</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3361</v>
+        <v>0.3093</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1407</v>
+        <v>0.1295</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4863</v>
+        <v>-0.4834</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3361</v>
+        <v>0.3093</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3361</v>
+        <v>0.3093</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3361</v>
+        <v>0.3093</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3361</v>
+        <v>0.3093</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3361</v>
+        <v>0.3093</v>
       </c>
       <c r="N22" t="n">
         <v>94</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0538</v>
+        <v>0.0258</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0225</v>
+        <v>0.0108</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6137</v>
+        <v>-0.6125</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0538</v>
+        <v>0.0258</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6556</v>
+        <v>-0.7758</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7094</v>
+        <v>0.8016</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6556</v>
+        <v>-0.7758</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3409</v>
+        <v>-0.4189</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7094</v>
+        <v>0.8016</v>
       </c>
       <c r="K23" t="n">
         <v>238</v>
@@ -1495,7 +1495,7 @@
         <v>188</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3685</v>
+        <v>0.3827</v>
       </c>
       <c r="N23" t="n">
         <v>426</v>
@@ -1504,446 +1504,446 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2231</v>
+        <v>-0.2011</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0934</v>
+        <v>-0.0842</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7387</v>
+        <v>-0.7157</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2231</v>
+        <v>-0.2011</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4868</v>
+        <v>-0.1239</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2637</v>
+        <v>-0.0772</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4868</v>
+        <v>-0.1239</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2531</v>
+        <v>-0.0669</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2637</v>
+        <v>-0.0772</v>
       </c>
       <c r="K24" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="L24" t="n">
         <v>57</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0106</v>
+        <v>-0.1441</v>
       </c>
       <c r="N24" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2244</v>
+        <v>-0.2125</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0939</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7393</v>
+        <v>-0.7209</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2244</v>
+        <v>-0.2125</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5812</v>
+        <v>-0.4839</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3568</v>
+        <v>0.2714</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5812</v>
+        <v>-0.4839</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3022</v>
+        <v>-0.2613</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3568</v>
+        <v>0.2714</v>
       </c>
       <c r="K25" t="n">
-        <v>27</v>
+        <v>178</v>
       </c>
       <c r="L25" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M25" t="n">
-        <v>0.05459999999999998</v>
+        <v>0.0101</v>
       </c>
       <c r="N25" t="n">
-        <v>56</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2336</v>
+        <v>-0.223</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0978</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7435</v>
+        <v>-0.7257</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2336</v>
+        <v>-0.223</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1423</v>
+        <v>-0.5878</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.3648</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1423</v>
+        <v>-0.5878</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.074</v>
+        <v>-0.3174</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.3648</v>
       </c>
       <c r="K26" t="n">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1653</v>
+        <v>0.0474</v>
       </c>
       <c r="N26" t="n">
-        <v>248</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bubzkji</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.263</v>
+        <v>-0.2475</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1101</v>
+        <v>-0.1036</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7567</v>
+        <v>-0.7369</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.263</v>
+        <v>-0.2475</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.263</v>
+        <v>0.4879</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-0.3971</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.263</v>
+        <v>0.4879</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.263</v>
+        <v>0.09079999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>27</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Bubzkji</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3388</v>
+        <v>-0.2907</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1418</v>
+        <v>-0.1217</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.791</v>
+        <v>-0.7565</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3388</v>
+        <v>-0.2907</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3388</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
+        <v>-0.2907</v>
+      </c>
+      <c r="H28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="n">
-        <v>-0.3388</v>
-      </c>
       <c r="I28" t="n">
-        <v>-0.3527</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
+        <v>-0.2907</v>
+      </c>
+      <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="K28" t="n">
-        <v>153</v>
-      </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3527</v>
+        <v>-0.2907</v>
       </c>
       <c r="N28" t="n">
-        <v>153</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3816</v>
+        <v>-0.367</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1597</v>
+        <v>-0.1536</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8103</v>
+        <v>-0.7913</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3816</v>
+        <v>-0.367</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3816</v>
+        <v>-0.367</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3816</v>
+        <v>-0.367</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3973</v>
+        <v>-0.4063</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3973</v>
+        <v>-0.4063</v>
       </c>
       <c r="N29" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4536</v>
+        <v>-0.4229</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1898</v>
+        <v>-0.177</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8428</v>
+        <v>-0.8167</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4536</v>
+        <v>-0.4229</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.8141</v>
+        <v>-0.4229</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3605</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.8141</v>
+        <v>-0.4229</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4233</v>
+        <v>-0.4338</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3605</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>90</v>
+        <v>153</v>
       </c>
       <c r="L30" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.06280000000000002</v>
+        <v>-0.4338</v>
       </c>
       <c r="N30" t="n">
-        <v>198</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4582</v>
+        <v>-0.4302</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1918</v>
+        <v>-0.1801</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8449</v>
+        <v>-0.82</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4582</v>
+        <v>-0.4302</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4582</v>
+        <v>-0.4302</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4582</v>
+        <v>-0.4302</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5383</v>
+        <v>-0.4413</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5383</v>
+        <v>-0.4413</v>
       </c>
       <c r="N31" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5676</v>
+        <v>-0.6014</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2376</v>
+        <v>-0.2517</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8943</v>
+        <v>-0.898</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5676</v>
+        <v>-0.6014</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5676</v>
+        <v>-0.6014</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5676</v>
+        <v>-0.6014</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5676</v>
+        <v>-0.6328</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5676</v>
+        <v>-0.6328</v>
       </c>
       <c r="N32" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6704</v>
+        <v>-0.6083</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2806</v>
+        <v>-0.2546</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9407</v>
+        <v>-0.9011</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6704</v>
+        <v>-0.6083</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6704</v>
+        <v>-0.6083</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6704</v>
+        <v>-0.6083</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6704</v>
+        <v>-0.6083</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6704</v>
+        <v>-0.6083</v>
       </c>
       <c r="N33" t="n">
         <v>94</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.7631</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2964</v>
+        <v>-0.3194</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9577</v>
+        <v>-0.9716</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.7631</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.7631</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.7631</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7677</v>
+        <v>-0.7631</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7677</v>
+        <v>-0.7631</v>
       </c>
       <c r="N34" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7604</v>
+        <v>-0.8202</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3182</v>
+        <v>-0.3433</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9813</v>
+        <v>-0.9976</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7604</v>
+        <v>-0.8202</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7604</v>
+        <v>-0.8202</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7604</v>
+        <v>-0.8202</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7917</v>
+        <v>-0.8413</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7917</v>
+        <v>-0.8413</v>
       </c>
       <c r="N35" t="n">
         <v>153</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Nivera</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8569</v>
+        <v>-0.8511</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3586</v>
+        <v>-0.3562</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0249</v>
+        <v>-1.0116</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8569</v>
+        <v>-0.8511</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8569</v>
+        <v>-0.8511</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8569</v>
+        <v>-0.8511</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8569</v>
+        <v>-0.9915</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8569</v>
+        <v>-0.9915</v>
       </c>
       <c r="N36" t="n">
-        <v>94</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nivera</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9321</v>
+        <v>-0.877</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3901</v>
+        <v>-0.367</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0588</v>
+        <v>-1.0234</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9321</v>
+        <v>-0.877</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9321</v>
+        <v>-0.877</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9321</v>
+        <v>-0.877</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1871</v>
+        <v>-0.877</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1871</v>
+        <v>-0.877</v>
       </c>
       <c r="N37" t="n">
-        <v>218</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.952</v>
+        <v>-0.9797</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3984</v>
+        <v>-0.41</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0678</v>
+        <v>-1.0702</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.952</v>
+        <v>-0.9797</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.952</v>
+        <v>-0.9797</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.952</v>
+        <v>-0.9797</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1185</v>
+        <v>-1.0846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1185</v>
+        <v>-1.0846</v>
       </c>
       <c r="N38" t="n">
         <v>230</v>
@@ -2194,185 +2194,185 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0664</v>
+        <v>-1.0629</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4463</v>
+        <v>-0.4449</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1194</v>
+        <v>-1.1081</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0664</v>
+        <v>-1.0629</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0664</v>
+        <v>-1.0629</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0664</v>
+        <v>-1.0629</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1103</v>
+        <v>-1.1768</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1103</v>
+        <v>-1.1768</v>
       </c>
       <c r="N39" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1178</v>
+        <v>-1.145</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4678</v>
+        <v>-0.4792</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1426</v>
+        <v>-1.1454</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1178</v>
+        <v>-1.145</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1178</v>
+        <v>-1.145</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1178</v>
+        <v>-1.145</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3134</v>
+        <v>-1.1745</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3134</v>
+        <v>-1.1745</v>
       </c>
       <c r="N40" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ottoNd</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.1653</v>
+        <v>-1.1755</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4877</v>
+        <v>-0.492</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1641</v>
+        <v>-1.1593</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.1653</v>
+        <v>-1.1755</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1653</v>
+        <v>-1.4898</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.3143</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1653</v>
+        <v>-1.4898</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.1653</v>
+        <v>-0.8045</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.3143</v>
       </c>
       <c r="K41" t="n">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.1653</v>
+        <v>-0.4902</v>
       </c>
       <c r="N41" t="n">
-        <v>94</v>
+        <v>379</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>ottoNd</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.24</v>
+        <v>-1.2245</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.519</v>
+        <v>-0.5125</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.1978</v>
+        <v>-1.1816</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.24</v>
+        <v>-1.2245</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.4709</v>
+        <v>-1.2245</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2309</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.4709</v>
+        <v>-1.2245</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.7648</v>
+        <v>-1.2245</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2309</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="L42" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.5339</v>
+        <v>-1.2245</v>
       </c>
       <c r="N42" t="n">
-        <v>379</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43">
@@ -2382,31 +2382,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-3.3515</v>
+        <v>-3.1999</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.4027</v>
+        <v>-1.3392</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.151</v>
+        <v>-2.0809</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.3515</v>
+        <v>-3.1999</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.1364</v>
+        <v>-2.9725</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.2151</v>
+        <v>-0.2274</v>
       </c>
       <c r="H43" t="n">
-        <v>-3.1364</v>
+        <v>-2.9725</v>
       </c>
       <c r="I43" t="n">
-        <v>-1.6308</v>
+        <v>-1.6051</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.2151</v>
+        <v>-0.2274</v>
       </c>
       <c r="K43" t="n">
         <v>155</v>
@@ -2415,7 +2415,7 @@
         <v>57</v>
       </c>
       <c r="M43" t="n">
-        <v>-1.8459</v>
+        <v>-1.8325</v>
       </c>
       <c r="N43" t="n">
         <v>212</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-5.8522</v>
+        <v>-5.4449</v>
       </c>
       <c r="C44" t="n">
-        <v>-2.4493</v>
+        <v>-2.2788</v>
       </c>
       <c r="D44" t="n">
-        <v>-3.28</v>
+        <v>-3.1028</v>
       </c>
       <c r="E44" t="n">
-        <v>-5.8522</v>
+        <v>-5.4449</v>
       </c>
       <c r="F44" t="n">
-        <v>-4.8522</v>
+        <v>-4.4449</v>
       </c>
       <c r="G44" t="n">
         <v>-1</v>
       </c>
       <c r="H44" t="n">
-        <v>-4.8522</v>
+        <v>-4.4449</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.5229</v>
+        <v>-2.4002</v>
       </c>
       <c r="J44" t="n">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>81</v>
       </c>
       <c r="M44" t="n">
-        <v>-3.5229</v>
+        <v>-3.4002</v>
       </c>
       <c r="N44" t="n">
         <v>198</v>
@@ -2567,10 +2567,10 @@
         <v>1.44</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0608</v>
+        <v>1.0232</v>
       </c>
       <c r="J2" t="n">
-        <v>28.6416</v>
+        <v>27.6264</v>
       </c>
     </row>
     <row r="3">
@@ -2607,10 +2607,10 @@
         <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7504</v>
       </c>
       <c r="J3" t="n">
-        <v>21.3246</v>
+        <v>20.2608</v>
       </c>
     </row>
     <row r="4">
@@ -2647,10 +2647,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.628</v>
+        <v>0.6068</v>
       </c>
       <c r="J4" t="n">
-        <v>16.956</v>
+        <v>16.3836</v>
       </c>
     </row>
     <row r="5">
@@ -2687,10 +2687,10 @@
         <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.485</v>
+        <v>0.4778</v>
       </c>
       <c r="J5" t="n">
-        <v>13.095</v>
+        <v>12.9006</v>
       </c>
     </row>
     <row r="6">
@@ -2727,10 +2727,10 @@
         <v>0.93</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3174</v>
+        <v>-0.2996</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.569800000000001</v>
+        <v>-8.0892</v>
       </c>
     </row>
     <row r="7">
@@ -2767,10 +2767,10 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3846</v>
+        <v>0.3752</v>
       </c>
       <c r="J7" t="n">
-        <v>10.3842</v>
+        <v>10.1304</v>
       </c>
     </row>
     <row r="8">
@@ -2807,10 +2807,10 @@
         <v>1.14</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3645</v>
+        <v>0.3565</v>
       </c>
       <c r="J8" t="n">
-        <v>9.8415</v>
+        <v>9.625500000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2847,10 +2847,10 @@
         <v>0.92</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1013</v>
+        <v>-0.1158</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7351</v>
+        <v>-3.1266</v>
       </c>
     </row>
     <row r="10">
@@ -2887,10 +2887,10 @@
         <v>0.75</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2745</v>
+        <v>-0.2902</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.4115</v>
+        <v>-7.8354</v>
       </c>
     </row>
     <row r="11">
@@ -2927,10 +2927,10 @@
         <v>0.48</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5262</v>
+        <v>-0.5311</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.2074</v>
+        <v>-14.3397</v>
       </c>
     </row>
     <row r="12">
@@ -2967,10 +2967,10 @@
         <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4281</v>
+        <v>1.5405</v>
       </c>
       <c r="J12" t="n">
-        <v>38.5587</v>
+        <v>41.5935</v>
       </c>
     </row>
     <row r="13">
@@ -3007,10 +3007,10 @@
         <v>1.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3912</v>
+        <v>1.494</v>
       </c>
       <c r="J13" t="n">
-        <v>37.5624</v>
+        <v>40.338</v>
       </c>
     </row>
     <row r="14">
@@ -3047,10 +3047,10 @@
         <v>1.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0835</v>
+        <v>0.1035</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2545</v>
+        <v>2.7945</v>
       </c>
     </row>
     <row r="15">
@@ -3087,10 +3087,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6501</v>
+        <v>-0.603</v>
       </c>
       <c r="J15" t="n">
-        <v>-17.5527</v>
+        <v>-16.281</v>
       </c>
     </row>
     <row r="16">
@@ -3127,10 +3127,10 @@
         <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8027</v>
+        <v>-0.7381</v>
       </c>
       <c r="J16" t="n">
-        <v>-21.6729</v>
+        <v>-19.9287</v>
       </c>
     </row>
     <row r="17">
@@ -3167,10 +3167,10 @@
         <v>1.19</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4525</v>
+        <v>0.4403</v>
       </c>
       <c r="J17" t="n">
-        <v>12.2175</v>
+        <v>11.8881</v>
       </c>
     </row>
     <row r="18">
@@ -3207,10 +3207,10 @@
         <v>1.07</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2079</v>
+        <v>0.2093</v>
       </c>
       <c r="J18" t="n">
-        <v>5.6133</v>
+        <v>5.6511</v>
       </c>
     </row>
     <row r="19">
@@ -3247,10 +3247,10 @@
         <v>1.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.162</v>
+        <v>0.1644</v>
       </c>
       <c r="J19" t="n">
-        <v>4.374</v>
+        <v>4.4388</v>
       </c>
     </row>
     <row r="20">
@@ -3287,10 +3287,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3352</v>
+        <v>-0.3486</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.0504</v>
+        <v>-9.4122</v>
       </c>
     </row>
     <row r="21">
@@ -3327,10 +3327,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4562</v>
+        <v>-0.4645</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.3174</v>
+        <v>-12.5415</v>
       </c>
     </row>
     <row r="22">
@@ -3367,10 +3367,10 @@
         <v>1.54</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2246</v>
+        <v>1.252</v>
       </c>
       <c r="J22" t="n">
-        <v>31.8396</v>
+        <v>32.552</v>
       </c>
     </row>
     <row r="23">
@@ -3407,10 +3407,10 @@
         <v>1.22</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6072</v>
       </c>
       <c r="J23" t="n">
-        <v>16.5256</v>
+        <v>15.7872</v>
       </c>
     </row>
     <row r="24">
@@ -3447,10 +3447,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2542</v>
+        <v>-0.2479</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.6092</v>
+        <v>-6.4454</v>
       </c>
     </row>
     <row r="25">
@@ -3487,10 +3487,10 @@
         <v>0.9</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.375</v>
+        <v>-0.3602</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.75</v>
+        <v>-9.3652</v>
       </c>
     </row>
     <row r="26">
@@ -3527,10 +3527,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4877</v>
+        <v>-0.4628</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.6802</v>
+        <v>-12.0328</v>
       </c>
     </row>
     <row r="27">
@@ -3567,10 +3567,10 @@
         <v>1.11</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2796</v>
+        <v>0.2814</v>
       </c>
       <c r="J27" t="n">
-        <v>7.2696</v>
+        <v>7.3164</v>
       </c>
     </row>
     <row r="28">
@@ -3607,10 +3607,10 @@
         <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1729</v>
+        <v>0.1782</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4954</v>
+        <v>4.6332</v>
       </c>
     </row>
     <row r="29">
@@ -3647,10 +3647,10 @@
         <v>0.91</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1181</v>
+        <v>-0.1316</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.0706</v>
+        <v>-3.4216</v>
       </c>
     </row>
     <row r="30">
@@ -3687,10 +3687,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1616</v>
+        <v>-0.1761</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.2016</v>
+        <v>-4.5786</v>
       </c>
     </row>
     <row r="31">
@@ -3727,10 +3727,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2134</v>
+        <v>-0.2281</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.5484</v>
+        <v>-5.9306</v>
       </c>
     </row>
     <row r="32">
@@ -3767,10 +3767,10 @@
         <v>1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>0.426</v>
+        <v>0.473</v>
       </c>
       <c r="J32" t="n">
-        <v>11.502</v>
+        <v>12.771</v>
       </c>
     </row>
     <row r="33">
@@ -3807,10 +3807,10 @@
         <v>1.18</v>
       </c>
       <c r="I33" t="n">
-        <v>0.363</v>
+        <v>0.3858</v>
       </c>
       <c r="J33" t="n">
-        <v>9.801</v>
+        <v>10.4166</v>
       </c>
     </row>
     <row r="34">
@@ -3847,10 +3847,10 @@
         <v>1.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3089</v>
+        <v>0.3161</v>
       </c>
       <c r="J34" t="n">
-        <v>8.340299999999999</v>
+        <v>8.534700000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3887,10 +3887,10 @@
         <v>1.01</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0281</v>
+        <v>0.0366</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7587</v>
+        <v>0.9882</v>
       </c>
     </row>
     <row r="36">
@@ -3927,10 +3927,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2763</v>
+        <v>-0.2877</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.4601</v>
+        <v>-7.7679</v>
       </c>
     </row>
     <row r="37">
@@ -3967,10 +3967,10 @@
         <v>1.82</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3212</v>
+        <v>1.4278</v>
       </c>
       <c r="J37" t="n">
-        <v>35.6724</v>
+        <v>38.5506</v>
       </c>
     </row>
     <row r="38">
@@ -4007,10 +4007,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3638</v>
+        <v>0.3793</v>
       </c>
       <c r="J38" t="n">
-        <v>9.8226</v>
+        <v>10.2411</v>
       </c>
     </row>
     <row r="39">
@@ -4047,10 +4047,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3087</v>
+        <v>-0.3006</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.334899999999999</v>
+        <v>-8.116199999999999</v>
       </c>
     </row>
     <row r="40">
@@ -4087,10 +4087,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5077</v>
+        <v>-0.4824</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.7079</v>
+        <v>-13.0248</v>
       </c>
     </row>
     <row r="41">
@@ -4127,10 +4127,10 @@
         <v>0.62</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0849</v>
+        <v>-0.9887</v>
       </c>
       <c r="J41" t="n">
-        <v>-29.2923</v>
+        <v>-26.6949</v>
       </c>
     </row>
     <row r="42">
@@ -4167,10 +4167,10 @@
         <v>1.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2356</v>
+        <v>0.2348</v>
       </c>
       <c r="J42" t="n">
-        <v>7.068</v>
+        <v>7.044</v>
       </c>
     </row>
     <row r="43">
@@ -4207,10 +4207,10 @@
         <v>1.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0612</v>
+        <v>0.0603</v>
       </c>
       <c r="J43" t="n">
-        <v>1.836</v>
+        <v>1.809</v>
       </c>
     </row>
     <row r="44">
@@ -4247,10 +4247,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0788</v>
+        <v>-0.0919</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.364</v>
+        <v>-2.757</v>
       </c>
     </row>
     <row r="45">
@@ -4287,10 +4287,10 @@
         <v>0.89</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1344</v>
+        <v>-0.1499</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.032</v>
+        <v>-4.497</v>
       </c>
     </row>
     <row r="46">
@@ -4327,10 +4327,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4543</v>
+        <v>-0.463</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.629</v>
+        <v>-13.89</v>
       </c>
     </row>
     <row r="47">
@@ -4367,10 +4367,10 @@
         <v>1.5</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8764</v>
+        <v>0.9646</v>
       </c>
       <c r="J47" t="n">
-        <v>26.292</v>
+        <v>28.938</v>
       </c>
     </row>
     <row r="48">
@@ -4407,10 +4407,10 @@
         <v>1.45</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8114</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>24.342</v>
+        <v>26.841</v>
       </c>
     </row>
     <row r="49">
@@ -4447,10 +4447,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1607</v>
+        <v>0.1753</v>
       </c>
       <c r="J49" t="n">
-        <v>4.821</v>
+        <v>5.259</v>
       </c>
     </row>
     <row r="50">
@@ -4487,10 +4487,10 @@
         <v>0.99</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0949</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.847</v>
+        <v>-2.622</v>
       </c>
     </row>
     <row r="51">
@@ -4527,10 +4527,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5616</v>
+        <v>-0.5255</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.848</v>
+        <v>-15.765</v>
       </c>
     </row>
     <row r="52">
@@ -4567,10 +4567,10 @@
         <v>1.31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4989</v>
+        <v>0.5564</v>
       </c>
       <c r="J52" t="n">
-        <v>14.4681</v>
+        <v>16.1356</v>
       </c>
     </row>
     <row r="53">
@@ -4607,10 +4607,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2923</v>
+        <v>0.2995</v>
       </c>
       <c r="J53" t="n">
-        <v>8.476699999999999</v>
+        <v>8.685499999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4647,10 +4647,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2731</v>
+        <v>0.2812</v>
       </c>
       <c r="J54" t="n">
-        <v>7.9199</v>
+        <v>8.1548</v>
       </c>
     </row>
     <row r="55">
@@ -4687,10 +4687,10 @@
         <v>0.92</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1179</v>
+        <v>-0.1285</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.4191</v>
+        <v>-3.7265</v>
       </c>
     </row>
     <row r="56">
@@ -4727,10 +4727,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2355</v>
+        <v>-0.2476</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.8295</v>
+        <v>-7.1804</v>
       </c>
     </row>
     <row r="57">
@@ -4767,10 +4767,10 @@
         <v>0.46</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.4449</v>
+        <v>-1.297</v>
       </c>
       <c r="J57" t="n">
-        <v>-41.9021</v>
+        <v>-37.613</v>
       </c>
     </row>
     <row r="58">
@@ -4807,10 +4807,10 @@
         <v>1.25</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5746</v>
+        <v>0.6286</v>
       </c>
       <c r="J58" t="n">
-        <v>16.6634</v>
+        <v>18.2294</v>
       </c>
     </row>
     <row r="59">
@@ -4847,10 +4847,10 @@
         <v>1.19</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4842</v>
+        <v>0.5283</v>
       </c>
       <c r="J59" t="n">
-        <v>14.0418</v>
+        <v>15.3207</v>
       </c>
     </row>
     <row r="60">
@@ -4887,10 +4887,10 @@
         <v>1.11</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3568</v>
+        <v>0.3648</v>
       </c>
       <c r="J60" t="n">
-        <v>10.3472</v>
+        <v>10.5792</v>
       </c>
     </row>
     <row r="61">
@@ -4927,10 +4927,10 @@
         <v>1.06</v>
       </c>
       <c r="I61" t="n">
-        <v>0.225</v>
+        <v>0.2277</v>
       </c>
       <c r="J61" t="n">
-        <v>6.525</v>
+        <v>6.6033</v>
       </c>
     </row>
     <row r="62">
@@ -4967,10 +4967,10 @@
         <v>0.58</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.464</v>
+        <v>-0.4677</v>
       </c>
       <c r="J62" t="n">
-        <v>-11.6</v>
+        <v>-11.6925</v>
       </c>
     </row>
     <row r="63">
@@ -5007,10 +5007,10 @@
         <v>1.61</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.6595</v>
       </c>
       <c r="J63" t="n">
-        <v>14.4025</v>
+        <v>16.4875</v>
       </c>
     </row>
     <row r="64">
@@ -5047,10 +5047,10 @@
         <v>1.37</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4205</v>
+        <v>0.4771</v>
       </c>
       <c r="J64" t="n">
-        <v>10.5125</v>
+        <v>11.9275</v>
       </c>
     </row>
     <row r="65">
@@ -5087,10 +5087,10 @@
         <v>1.33</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3936</v>
+        <v>0.4432</v>
       </c>
       <c r="J65" t="n">
-        <v>9.84</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="66">
@@ -5127,10 +5127,10 @@
         <v>1.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1105</v>
       </c>
       <c r="J66" t="n">
-        <v>2.345</v>
+        <v>2.7625</v>
       </c>
     </row>
     <row r="67">
@@ -5167,10 +5167,10 @@
         <v>0.58</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.4383</v>
+        <v>-0.4474</v>
       </c>
       <c r="J67" t="n">
-        <v>-10.9575</v>
+        <v>-11.185</v>
       </c>
     </row>
     <row r="68">
@@ -5207,10 +5207,10 @@
         <v>1.09</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1915</v>
+        <v>0.1962</v>
       </c>
       <c r="J68" t="n">
-        <v>4.7875</v>
+        <v>4.905</v>
       </c>
     </row>
     <row r="69">
@@ -5247,10 +5247,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.123</v>
+        <v>0.128</v>
       </c>
       <c r="J69" t="n">
-        <v>3.075</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="70">
@@ -5287,10 +5287,10 @@
         <v>0.98</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0283</v>
+        <v>-0.0369</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.7075</v>
+        <v>-0.9225</v>
       </c>
     </row>
     <row r="71">
@@ -5327,10 +5327,10 @@
         <v>0.88</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1468</v>
+        <v>-0.1621</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.67</v>
+        <v>-4.0525</v>
       </c>
     </row>
     <row r="72">
@@ -5367,10 +5367,10 @@
         <v>0.59</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.3745</v>
+        <v>-0.3962</v>
       </c>
       <c r="J72" t="n">
-        <v>-10.1115</v>
+        <v>-10.6974</v>
       </c>
     </row>
     <row r="73">
@@ -5407,10 +5407,10 @@
         <v>0.7</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.263</v>
+        <v>-0.2907</v>
       </c>
       <c r="J73" t="n">
-        <v>-7.101</v>
+        <v>-7.8489</v>
       </c>
     </row>
     <row r="74">
@@ -5447,10 +5447,10 @@
         <v>0.6</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.365</v>
+        <v>-0.3872</v>
       </c>
       <c r="J74" t="n">
-        <v>-9.855</v>
+        <v>-10.4544</v>
       </c>
     </row>
     <row r="75">
@@ -5487,10 +5487,10 @@
         <v>0.46</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4926</v>
+        <v>-0.5074</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.3002</v>
+        <v>-13.6998</v>
       </c>
     </row>
     <row r="76">
@@ -5527,10 +5527,10 @@
         <v>0.4</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5502</v>
+        <v>-0.5606</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.8554</v>
+        <v>-15.1362</v>
       </c>
     </row>
     <row r="77">
@@ -5567,10 +5567,10 @@
         <v>0.74</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.7289</v>
+        <v>-0.6906</v>
       </c>
       <c r="J77" t="n">
-        <v>-19.6803</v>
+        <v>-18.6462</v>
       </c>
     </row>
     <row r="78">
@@ -5607,10 +5607,10 @@
         <v>1.27</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6616</v>
+        <v>0.712</v>
       </c>
       <c r="J78" t="n">
-        <v>17.8632</v>
+        <v>19.224</v>
       </c>
     </row>
     <row r="79">
@@ -5647,10 +5647,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.551</v>
+        <v>-0.5336</v>
       </c>
       <c r="J79" t="n">
-        <v>-14.877</v>
+        <v>-14.4072</v>
       </c>
     </row>
     <row r="80">
@@ -5687,10 +5687,10 @@
         <v>0.75</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.7038</v>
+        <v>-0.6686</v>
       </c>
       <c r="J80" t="n">
-        <v>-19.0026</v>
+        <v>-18.0522</v>
       </c>
     </row>
     <row r="81">
@@ -5727,10 +5727,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.754</v>
+        <v>-0.7125</v>
       </c>
       <c r="J81" t="n">
-        <v>-20.358</v>
+        <v>-19.2375</v>
       </c>
     </row>
     <row r="82">
@@ -5767,10 +5767,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6443</v>
+        <v>0.6262</v>
       </c>
       <c r="J82" t="n">
-        <v>19.329</v>
+        <v>18.786</v>
       </c>
     </row>
     <row r="83">
@@ -5807,10 +5807,10 @@
         <v>1.3</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5936</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>17.808</v>
+        <v>17.403</v>
       </c>
     </row>
     <row r="84">
@@ -5847,10 +5847,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2518</v>
+        <v>0.2612</v>
       </c>
       <c r="J84" t="n">
-        <v>7.554</v>
+        <v>7.836</v>
       </c>
     </row>
     <row r="85">
@@ -5887,10 +5887,10 @@
         <v>0.85</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1956</v>
+        <v>-0.2074</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.868</v>
+        <v>-6.222</v>
       </c>
     </row>
     <row r="86">
@@ -5927,10 +5927,10 @@
         <v>0.75</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2958</v>
+        <v>-0.3068</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.874000000000001</v>
+        <v>-9.204000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5967,10 +5967,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9095</v>
+        <v>0.8425</v>
       </c>
       <c r="J87" t="n">
-        <v>27.285</v>
+        <v>25.275</v>
       </c>
     </row>
     <row r="88">
@@ -6007,10 +6007,10 @@
         <v>1.21</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6364</v>
+        <v>0.6029</v>
       </c>
       <c r="J88" t="n">
-        <v>19.092</v>
+        <v>18.087</v>
       </c>
     </row>
     <row r="89">
@@ -6047,10 +6047,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1705</v>
+        <v>-0.173</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.115</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="90">
@@ -6087,10 +6087,10 @@
         <v>0.83</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5494</v>
+        <v>-0.5221</v>
       </c>
       <c r="J90" t="n">
-        <v>-16.482</v>
+        <v>-15.663</v>
       </c>
     </row>
     <row r="91">
@@ -6127,10 +6127,10 @@
         <v>0.8</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6283</v>
+        <v>-0.5925</v>
       </c>
       <c r="J91" t="n">
-        <v>-18.849</v>
+        <v>-17.775</v>
       </c>
     </row>
     <row r="92">
@@ -6167,10 +6167,10 @@
         <v>0.89</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.007</v>
+        <v>-0.0496</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.133</v>
+        <v>-0.9424</v>
       </c>
     </row>
     <row r="93">
@@ -6207,10 +6207,10 @@
         <v>0.62</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.3294</v>
+        <v>-0.3563</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.2586</v>
+        <v>-6.7697</v>
       </c>
     </row>
     <row r="94">
@@ -6247,10 +6247,10 @@
         <v>0.35</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.5884</v>
+        <v>-0.597</v>
       </c>
       <c r="J94" t="n">
-        <v>-11.1796</v>
+        <v>-11.343</v>
       </c>
     </row>
     <row r="95">
@@ -6287,10 +6287,10 @@
         <v>0.32</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.6183</v>
+        <v>-0.6243</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.7477</v>
+        <v>-11.8617</v>
       </c>
     </row>
     <row r="96">
@@ -6327,10 +6327,10 @@
         <v>0.32</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6183</v>
+        <v>-0.6243</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.7477</v>
+        <v>-11.8617</v>
       </c>
     </row>
     <row r="97">
@@ -6367,10 +6367,10 @@
         <v>1.82</v>
       </c>
       <c r="I97" t="n">
-        <v>1.445</v>
+        <v>1.442</v>
       </c>
       <c r="J97" t="n">
-        <v>27.455</v>
+        <v>27.398</v>
       </c>
     </row>
     <row r="98">
@@ -6407,10 +6407,10 @@
         <v>1.74</v>
       </c>
       <c r="I98" t="n">
-        <v>1.3562</v>
+        <v>1.3476</v>
       </c>
       <c r="J98" t="n">
-        <v>25.7678</v>
+        <v>25.6044</v>
       </c>
     </row>
     <row r="99">
@@ -6447,10 +6447,10 @@
         <v>1.59</v>
       </c>
       <c r="I99" t="n">
-        <v>1.1894</v>
+        <v>1.1683</v>
       </c>
       <c r="J99" t="n">
-        <v>22.5986</v>
+        <v>22.1977</v>
       </c>
     </row>
     <row r="100">
@@ -6487,10 +6487,10 @@
         <v>1.48</v>
       </c>
       <c r="I100" t="n">
-        <v>1.0614</v>
+        <v>1.0267</v>
       </c>
       <c r="J100" t="n">
-        <v>20.1666</v>
+        <v>19.5073</v>
       </c>
     </row>
     <row r="101">
@@ -6527,10 +6527,10 @@
         <v>1.38</v>
       </c>
       <c r="I101" t="n">
-        <v>0.8938</v>
+        <v>0.8555</v>
       </c>
       <c r="J101" t="n">
-        <v>16.9822</v>
+        <v>16.2545</v>
       </c>
     </row>
     <row r="102">
@@ -6567,10 +6567,10 @@
         <v>0.93</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0838</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.5084</v>
+        <v>-1.7838</v>
       </c>
     </row>
     <row r="103">
@@ -6607,10 +6607,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.1115</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.7226</v>
+        <v>-2.007</v>
       </c>
     </row>
     <row r="104">
@@ -6647,10 +6647,10 @@
         <v>0.86</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1613</v>
+        <v>-0.1785</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.9034</v>
+        <v>-3.213</v>
       </c>
     </row>
     <row r="105">
@@ -6687,10 +6687,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1907</v>
+        <v>-0.2084</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.4326</v>
+        <v>-3.7512</v>
       </c>
     </row>
     <row r="106">
@@ -6727,10 +6727,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3265</v>
+        <v>-0.3418</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.877</v>
+        <v>-6.1524</v>
       </c>
     </row>
     <row r="107">
@@ -6767,10 +6767,10 @@
         <v>1.04</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0159</v>
+        <v>0.0433</v>
       </c>
       <c r="J107" t="n">
-        <v>0.2862</v>
+        <v>0.7794</v>
       </c>
     </row>
     <row r="108">
@@ -6807,10 +6807,10 @@
         <v>2.44</v>
       </c>
       <c r="I108" t="n">
-        <v>1.3267</v>
+        <v>1.3428</v>
       </c>
       <c r="J108" t="n">
-        <v>23.8806</v>
+        <v>24.1704</v>
       </c>
     </row>
     <row r="109">
@@ -6847,10 +6847,10 @@
         <v>1.98</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0624</v>
+        <v>1.048</v>
       </c>
       <c r="J109" t="n">
-        <v>19.1232</v>
+        <v>18.864</v>
       </c>
     </row>
     <row r="110">
@@ -6887,10 +6887,10 @@
         <v>1.62</v>
       </c>
       <c r="I110" t="n">
-        <v>0.7432</v>
+        <v>0.7362</v>
       </c>
       <c r="J110" t="n">
-        <v>13.3776</v>
+        <v>13.2516</v>
       </c>
     </row>
     <row r="111">
@@ -6927,10 +6927,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0337</v>
+        <v>0.0615</v>
       </c>
       <c r="J111" t="n">
-        <v>0.6066</v>
+        <v>1.107</v>
       </c>
     </row>
     <row r="112">
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.9467</v>
+        <v>-0.9197</v>
       </c>
       <c r="J112" t="n">
-        <v>-38.8147</v>
+        <v>-37.7077</v>
       </c>
     </row>
     <row r="113">
@@ -7007,10 +7007,10 @@
         <v>0.78</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.1283</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.1283</v>
+        <v>-5.2603</v>
       </c>
     </row>
     <row r="114">
@@ -7047,10 +7047,10 @@
         <v>0.55</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3627</v>
+        <v>-0.3931</v>
       </c>
       <c r="J114" t="n">
-        <v>-14.8707</v>
+        <v>-16.1171</v>
       </c>
     </row>
     <row r="115">
@@ -7087,10 +7087,10 @@
         <v>0.43</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.49</v>
+        <v>-0.5098</v>
       </c>
       <c r="J115" t="n">
-        <v>-20.09</v>
+        <v>-20.9018</v>
       </c>
     </row>
     <row r="116">
@@ -7127,10 +7127,10 @@
         <v>0.27</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6471</v>
+        <v>-0.653</v>
       </c>
       <c r="J116" t="n">
-        <v>-26.5311</v>
+        <v>-26.773</v>
       </c>
     </row>
     <row r="117">
@@ -7167,10 +7167,10 @@
         <v>0.64</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.9816</v>
+        <v>-0.9084</v>
       </c>
       <c r="J117" t="n">
-        <v>-40.2456</v>
+        <v>-37.2444</v>
       </c>
     </row>
     <row r="118">
@@ -7207,10 +7207,10 @@
         <v>1.52</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2964</v>
+        <v>1.2468</v>
       </c>
       <c r="J118" t="n">
-        <v>53.1524</v>
+        <v>51.1188</v>
       </c>
     </row>
     <row r="119">
@@ -7247,10 +7247,10 @@
         <v>0.87</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3988</v>
+        <v>-0.3954</v>
       </c>
       <c r="J119" t="n">
-        <v>-16.3508</v>
+        <v>-16.2114</v>
       </c>
     </row>
     <row r="120">
@@ -7287,10 +7287,10 @@
         <v>0.75</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.7093</v>
+        <v>-0.6724</v>
       </c>
       <c r="J120" t="n">
-        <v>-29.0813</v>
+        <v>-27.5684</v>
       </c>
     </row>
     <row r="121">
@@ -7327,10 +7327,10 @@
         <v>0.6</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.0785</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="J121" t="n">
-        <v>-44.2185</v>
+        <v>-40.6474</v>
       </c>
     </row>
     <row r="122">
@@ -7367,10 +7367,10 @@
         <v>0.64</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.3838</v>
+        <v>-0.3951</v>
       </c>
       <c r="J122" t="n">
-        <v>-8.059799999999999</v>
+        <v>-8.2971</v>
       </c>
     </row>
     <row r="123">
@@ -7407,10 +7407,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4475</v>
+        <v>0.4366</v>
       </c>
       <c r="J123" t="n">
-        <v>9.397500000000001</v>
+        <v>9.1686</v>
       </c>
     </row>
     <row r="124">
@@ -7447,10 +7447,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1815</v>
+        <v>0.1845</v>
       </c>
       <c r="J124" t="n">
-        <v>3.8115</v>
+        <v>3.8745</v>
       </c>
     </row>
     <row r="125">
@@ -7487,10 +7487,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.057</v>
+        <v>-0.0678</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.197</v>
+        <v>-1.4238</v>
       </c>
     </row>
     <row r="126">
@@ -7527,10 +7527,10 @@
         <v>0.77</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2596</v>
+        <v>-0.2746</v>
       </c>
       <c r="J126" t="n">
-        <v>-5.4516</v>
+        <v>-5.7666</v>
       </c>
     </row>
     <row r="127">
@@ -7567,10 +7567,10 @@
         <v>0.83</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.0614</v>
+        <v>-0.1776</v>
       </c>
       <c r="J127" t="n">
-        <v>-1.2894</v>
+        <v>-3.7296</v>
       </c>
     </row>
     <row r="128">
@@ -7607,10 +7607,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.9355</v>
+        <v>-0.9064</v>
       </c>
       <c r="J128" t="n">
-        <v>-19.6455</v>
+        <v>-19.0344</v>
       </c>
     </row>
     <row r="129">
@@ -7647,10 +7647,10 @@
         <v>0.27</v>
       </c>
       <c r="I129" t="n">
-        <v>-1.6926</v>
+        <v>-1.5274</v>
       </c>
       <c r="J129" t="n">
-        <v>-35.5446</v>
+        <v>-32.0754</v>
       </c>
     </row>
     <row r="130">
@@ -7687,10 +7687,10 @@
         <v>0.24</v>
       </c>
       <c r="I130" t="n">
-        <v>-1.7752</v>
+        <v>-1.5939</v>
       </c>
       <c r="J130" t="n">
-        <v>-37.2792</v>
+        <v>-33.4719</v>
       </c>
     </row>
     <row r="131">
@@ -7727,10 +7727,10 @@
         <v>0.21</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.8587</v>
+        <v>-1.661</v>
       </c>
       <c r="J131" t="n">
-        <v>-39.0327</v>
+        <v>-34.881</v>
       </c>
     </row>
     <row r="132">
@@ -7767,10 +7767,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>1.067</v>
+        <v>1.0142</v>
       </c>
       <c r="J132" t="n">
-        <v>37.345</v>
+        <v>35.497</v>
       </c>
     </row>
     <row r="133">
@@ -7807,10 +7807,10 @@
         <v>1.17</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5111</v>
+        <v>0.4955</v>
       </c>
       <c r="J133" t="n">
-        <v>17.8885</v>
+        <v>17.3425</v>
       </c>
     </row>
     <row r="134">
@@ -7847,10 +7847,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4063</v>
+        <v>0.4005</v>
       </c>
       <c r="J134" t="n">
-        <v>14.2205</v>
+        <v>14.0175</v>
       </c>
     </row>
     <row r="135">
@@ -7887,10 +7887,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0354</v>
+        <v>0.0464</v>
       </c>
       <c r="J135" t="n">
-        <v>1.239</v>
+        <v>1.624</v>
       </c>
     </row>
     <row r="136">
@@ -7927,10 +7927,10 @@
         <v>0.7</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8974</v>
+        <v>-0.8258</v>
       </c>
       <c r="J136" t="n">
-        <v>-31.409</v>
+        <v>-28.903</v>
       </c>
     </row>
     <row r="137">
@@ -7967,10 +7967,10 @@
         <v>1.2</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4393</v>
+        <v>0.4342</v>
       </c>
       <c r="J137" t="n">
-        <v>15.3755</v>
+        <v>15.197</v>
       </c>
     </row>
     <row r="138">
@@ -8007,10 +8007,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3835</v>
+        <v>0.3822</v>
       </c>
       <c r="J138" t="n">
-        <v>13.4225</v>
+        <v>13.377</v>
       </c>
     </row>
     <row r="139">
@@ -8047,10 +8047,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2671</v>
+        <v>0.2722</v>
       </c>
       <c r="J139" t="n">
-        <v>9.3485</v>
+        <v>9.526999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -8087,10 +8087,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0922</v>
+        <v>0.1002</v>
       </c>
       <c r="J140" t="n">
-        <v>3.227</v>
+        <v>3.507</v>
       </c>
     </row>
     <row r="141">
@@ -8127,10 +8127,10 @@
         <v>0.48</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.537</v>
+        <v>-0.5396</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.795</v>
+        <v>-18.886</v>
       </c>
     </row>
     <row r="142">
@@ -8167,10 +8167,10 @@
         <v>1.52</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1858</v>
+        <v>1.1482</v>
       </c>
       <c r="J142" t="n">
-        <v>30.8308</v>
+        <v>29.8532</v>
       </c>
     </row>
     <row r="143">
@@ -8207,10 +8207,10 @@
         <v>1.41</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0395</v>
+        <v>0.984</v>
       </c>
       <c r="J143" t="n">
-        <v>27.027</v>
+        <v>25.584</v>
       </c>
     </row>
     <row r="144">
@@ -8247,10 +8247,10 @@
         <v>1.21</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5986</v>
+        <v>0.5766</v>
       </c>
       <c r="J144" t="n">
-        <v>15.5636</v>
+        <v>14.9916</v>
       </c>
     </row>
     <row r="145">
@@ -8287,10 +8287,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6364</v>
       </c>
       <c r="J145" t="n">
-        <v>-17.784</v>
+        <v>-16.5464</v>
       </c>
     </row>
     <row r="146">
@@ -8327,10 +8327,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.7695</v>
       </c>
       <c r="J146" t="n">
-        <v>-21.7152</v>
+        <v>-20.007</v>
       </c>
     </row>
     <row r="147">
@@ -8367,10 +8367,10 @@
         <v>1.33</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6635</v>
+        <v>0.6403</v>
       </c>
       <c r="J147" t="n">
-        <v>17.251</v>
+        <v>16.6478</v>
       </c>
     </row>
     <row r="148">
@@ -8407,10 +8407,10 @@
         <v>1.08</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2018</v>
+        <v>0.2102</v>
       </c>
       <c r="J148" t="n">
-        <v>5.2468</v>
+        <v>5.4652</v>
       </c>
     </row>
     <row r="149">
@@ -8447,10 +8447,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0896</v>
+        <v>0.0984</v>
       </c>
       <c r="J149" t="n">
-        <v>2.3296</v>
+        <v>2.5584</v>
       </c>
     </row>
     <row r="150">
@@ -8487,10 +8487,10 @@
         <v>0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1468</v>
+        <v>-0.1594</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.8168</v>
+        <v>-4.1444</v>
       </c>
     </row>
     <row r="151">
@@ -8527,10 +8527,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2996</v>
+        <v>-0.3117</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.7896</v>
+        <v>-8.104200000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8567,10 +8567,10 @@
         <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9913</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="J152" t="n">
-        <v>28.7477</v>
+        <v>26.8511</v>
       </c>
     </row>
     <row r="153">
@@ -8607,10 +8607,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5659</v>
       </c>
       <c r="J153" t="n">
-        <v>17.1158</v>
+        <v>16.4111</v>
       </c>
     </row>
     <row r="154">
@@ -8647,10 +8647,10 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0173</v>
+        <v>-0.0118</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.5017</v>
+        <v>-0.3422</v>
       </c>
     </row>
     <row r="155">
@@ -8687,10 +8687,10 @@
         <v>0.96</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1849</v>
+        <v>-0.183</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.3621</v>
+        <v>-5.307</v>
       </c>
     </row>
     <row r="156">
@@ -8727,10 +8727,10 @@
         <v>0.86</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4838</v>
+        <v>-0.4601</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.0302</v>
+        <v>-13.3429</v>
       </c>
     </row>
     <row r="157">
@@ -8767,10 +8767,10 @@
         <v>1.29</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6132</v>
+        <v>0.5915</v>
       </c>
       <c r="J157" t="n">
-        <v>17.7828</v>
+        <v>17.1535</v>
       </c>
     </row>
     <row r="158">
@@ -8807,10 +8807,10 @@
         <v>1.07</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1919</v>
+        <v>0.1976</v>
       </c>
       <c r="J158" t="n">
-        <v>5.5651</v>
+        <v>5.7304</v>
       </c>
     </row>
     <row r="159">
@@ -8847,10 +8847,10 @@
         <v>0.98</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0337</v>
+        <v>-0.041</v>
       </c>
       <c r="J159" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-1.189</v>
       </c>
     </row>
     <row r="160">
@@ -8887,10 +8887,10 @@
         <v>0.83</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2046</v>
+        <v>-0.2191</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.9334</v>
+        <v>-6.3539</v>
       </c>
     </row>
     <row r="161">
@@ -8927,10 +8927,10 @@
         <v>0.66</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.37</v>
+        <v>-0.381</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.73</v>
+        <v>-11.049</v>
       </c>
     </row>
     <row r="162">
@@ -8967,10 +8967,10 @@
         <v>1.27</v>
       </c>
       <c r="I162" t="n">
-        <v>0.401</v>
+        <v>0.4072</v>
       </c>
       <c r="J162" t="n">
-        <v>18.847</v>
+        <v>19.1384</v>
       </c>
     </row>
     <row r="163">
@@ -9007,10 +9007,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3621</v>
+        <v>0.3704</v>
       </c>
       <c r="J163" t="n">
-        <v>17.0187</v>
+        <v>17.4088</v>
       </c>
     </row>
     <row r="164">
@@ -9047,10 +9047,10 @@
         <v>1.15</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2418</v>
+        <v>0.2548</v>
       </c>
       <c r="J164" t="n">
-        <v>11.3646</v>
+        <v>11.9756</v>
       </c>
     </row>
     <row r="165">
@@ -9087,10 +9087,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0728</v>
+        <v>0.0859</v>
       </c>
       <c r="J165" t="n">
-        <v>3.4216</v>
+        <v>4.0373</v>
       </c>
     </row>
     <row r="166">
@@ -9127,10 +9127,10 @@
         <v>0.99</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0337</v>
+        <v>-0.0354</v>
       </c>
       <c r="J166" t="n">
-        <v>-1.5839</v>
+        <v>-1.6638</v>
       </c>
     </row>
     <row r="167">
@@ -9167,10 +9167,10 @@
         <v>1.05</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1071</v>
+        <v>0.1159</v>
       </c>
       <c r="J167" t="n">
-        <v>5.0337</v>
+        <v>5.4473</v>
       </c>
     </row>
     <row r="168">
@@ -9207,10 +9207,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0465</v>
+        <v>-0.0556</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.1855</v>
+        <v>-2.6132</v>
       </c>
     </row>
     <row r="169">
@@ -9247,10 +9247,10 @@
         <v>0.96</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0596</v>
+        <v>-0.0698</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.8012</v>
+        <v>-3.2806</v>
       </c>
     </row>
     <row r="170">
@@ -9287,10 +9287,10 @@
         <v>0.91</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1179</v>
+        <v>-0.1315</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.5413</v>
+        <v>-6.1805</v>
       </c>
     </row>
     <row r="171">
@@ -9327,10 +9327,10 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1614</v>
+        <v>-0.1759</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.5858</v>
+        <v>-8.267300000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9367,10 +9367,10 @@
         <v>1.82</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4701</v>
+        <v>1.464</v>
       </c>
       <c r="J172" t="n">
-        <v>29.402</v>
+        <v>29.28</v>
       </c>
     </row>
     <row r="173">
@@ -9407,10 +9407,10 @@
         <v>1.76</v>
       </c>
       <c r="I173" t="n">
-        <v>1.4014</v>
+        <v>1.3914</v>
       </c>
       <c r="J173" t="n">
-        <v>28.028</v>
+        <v>27.828</v>
       </c>
     </row>
     <row r="174">
@@ -9447,10 +9447,10 @@
         <v>1.35</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8562</v>
+        <v>0.8175</v>
       </c>
       <c r="J174" t="n">
-        <v>17.124</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="175">
@@ -9487,10 +9487,10 @@
         <v>1.24</v>
       </c>
       <c r="I175" t="n">
-        <v>0.6054</v>
+        <v>0.5961</v>
       </c>
       <c r="J175" t="n">
-        <v>12.108</v>
+        <v>11.922</v>
       </c>
     </row>
     <row r="176">
@@ -9527,10 +9527,10 @@
         <v>1.11</v>
       </c>
       <c r="I176" t="n">
-        <v>0.273</v>
+        <v>0.2959</v>
       </c>
       <c r="J176" t="n">
-        <v>5.46</v>
+        <v>5.918</v>
       </c>
     </row>
     <row r="177">
@@ -9567,10 +9567,10 @@
         <v>0.88</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.1253</v>
       </c>
       <c r="J177" t="n">
-        <v>-1.99</v>
+        <v>-2.506</v>
       </c>
     </row>
     <row r="178">
@@ -9607,10 +9607,10 @@
         <v>0.74</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2529</v>
+        <v>-0.2755</v>
       </c>
       <c r="J178" t="n">
-        <v>-5.058</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="179">
@@ -9647,10 +9647,10 @@
         <v>0.74</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2529</v>
+        <v>-0.2755</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.058</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="180">
@@ -9687,10 +9687,10 @@
         <v>0.49</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4854</v>
+        <v>-0.4975</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.708</v>
+        <v>-9.949999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -9727,10 +9727,10 @@
         <v>0.45</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5231</v>
+        <v>-0.5326</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.462</v>
+        <v>-10.652</v>
       </c>
     </row>
     <row r="182">
@@ -9767,10 +9767,10 @@
         <v>1.16</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5051</v>
+        <v>0.486</v>
       </c>
       <c r="J182" t="n">
-        <v>20.7091</v>
+        <v>19.926</v>
       </c>
     </row>
     <row r="183">
@@ -9807,10 +9807,10 @@
         <v>1.03</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1247</v>
+        <v>0.1318</v>
       </c>
       <c r="J183" t="n">
-        <v>5.1127</v>
+        <v>5.4038</v>
       </c>
     </row>
     <row r="184">
@@ -9847,10 +9847,10 @@
         <v>1.02</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0892</v>
+        <v>0.0965</v>
       </c>
       <c r="J184" t="n">
-        <v>3.6572</v>
+        <v>3.9565</v>
       </c>
     </row>
     <row r="185">
@@ -9887,10 +9887,10 @@
         <v>0.98</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.1035</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.0795</v>
+        <v>-4.2435</v>
       </c>
     </row>
     <row r="186">
@@ -9927,10 +9927,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2361</v>
+        <v>-0.2353</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.680099999999999</v>
+        <v>-9.6473</v>
       </c>
     </row>
     <row r="187">
@@ -9967,10 +9967,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8858</v>
+        <v>0.8414</v>
       </c>
       <c r="J187" t="n">
-        <v>36.3178</v>
+        <v>34.4974</v>
       </c>
     </row>
     <row r="188">
@@ -10007,10 +10007,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1967</v>
+        <v>0.2065</v>
       </c>
       <c r="J188" t="n">
-        <v>8.0647</v>
+        <v>8.4665</v>
       </c>
     </row>
     <row r="189">
@@ -10047,10 +10047,10 @@
         <v>0.99</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.024</v>
+        <v>-0.0278</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.984</v>
+        <v>-1.1398</v>
       </c>
     </row>
     <row r="190">
@@ -10087,10 +10087,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1497</v>
+        <v>-0.1617</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.1377</v>
+        <v>-6.6297</v>
       </c>
     </row>
     <row r="191">
@@ -10127,10 +10127,10 @@
         <v>0.77</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2733</v>
+        <v>-0.2853</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.2053</v>
+        <v>-11.6973</v>
       </c>
     </row>
     <row r="192">
@@ -10167,10 +10167,10 @@
         <v>1.44</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0715</v>
+        <v>1.0245</v>
       </c>
       <c r="J192" t="n">
-        <v>27.859</v>
+        <v>26.637</v>
       </c>
     </row>
     <row r="193">
@@ -10207,10 +10207,10 @@
         <v>1.36</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9392</v>
+        <v>0.8801</v>
       </c>
       <c r="J193" t="n">
-        <v>24.4192</v>
+        <v>22.8826</v>
       </c>
     </row>
     <row r="194">
@@ -10247,10 +10247,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4176</v>
+        <v>0.4144</v>
       </c>
       <c r="J194" t="n">
-        <v>10.8576</v>
+        <v>10.7744</v>
       </c>
     </row>
     <row r="195">
@@ -10287,10 +10287,10 @@
         <v>1.05</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1602</v>
+        <v>0.175</v>
       </c>
       <c r="J195" t="n">
-        <v>4.1652</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="196">
@@ -10327,10 +10327,10 @@
         <v>0.85</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5352</v>
+        <v>-0.5016</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.9152</v>
+        <v>-13.0416</v>
       </c>
     </row>
     <row r="197">
@@ -10367,10 +10367,10 @@
         <v>1.46</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.8601</v>
       </c>
       <c r="J197" t="n">
-        <v>23.7588</v>
+        <v>22.3626</v>
       </c>
     </row>
     <row r="198">
@@ -10407,10 +10407,10 @@
         <v>0.92</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1063</v>
+        <v>-0.1195</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.7638</v>
+        <v>-3.107</v>
       </c>
     </row>
     <row r="199">
@@ -10447,10 +10447,10 @@
         <v>0.89</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1395</v>
+        <v>-0.1538</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.627</v>
+        <v>-3.9988</v>
       </c>
     </row>
     <row r="200">
@@ -10487,10 +10487,10 @@
         <v>0.87</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1609</v>
+        <v>-0.1756</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.1834</v>
+        <v>-4.5656</v>
       </c>
     </row>
     <row r="201">
@@ -10527,10 +10527,10 @@
         <v>0.6</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4236</v>
+        <v>-0.4328</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.0136</v>
+        <v>-11.2528</v>
       </c>
     </row>
     <row r="202">
@@ -10567,10 +10567,10 @@
         <v>1.47</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0984</v>
+        <v>1.0582</v>
       </c>
       <c r="J202" t="n">
-        <v>27.46</v>
+        <v>26.455</v>
       </c>
     </row>
     <row r="203">
@@ -10607,10 +10607,10 @@
         <v>1.32</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8337</v>
+        <v>0.7893</v>
       </c>
       <c r="J203" t="n">
-        <v>20.8425</v>
+        <v>19.7325</v>
       </c>
     </row>
     <row r="204">
@@ -10647,10 +10647,10 @@
         <v>1.26</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6964</v>
+        <v>0.6681</v>
       </c>
       <c r="J204" t="n">
-        <v>17.41</v>
+        <v>16.7025</v>
       </c>
     </row>
     <row r="205">
@@ -10687,10 +10687,10 @@
         <v>1.19</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5333</v>
+        <v>0.5216</v>
       </c>
       <c r="J205" t="n">
-        <v>13.3325</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="206">
@@ -10727,10 +10727,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5208</v>
+        <v>-0.4861</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.02</v>
+        <v>-12.1525</v>
       </c>
     </row>
     <row r="207">
@@ -10767,10 +10767,10 @@
         <v>1.19</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4533</v>
+        <v>0.4409</v>
       </c>
       <c r="J207" t="n">
-        <v>11.3325</v>
+        <v>11.0225</v>
       </c>
     </row>
     <row r="208">
@@ -10807,10 +10807,10 @@
         <v>0.99</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0115</v>
+        <v>-0.0183</v>
       </c>
       <c r="J208" t="n">
-        <v>-0.2875</v>
+        <v>-0.4575</v>
       </c>
     </row>
     <row r="209">
@@ -10847,10 +10847,10 @@
         <v>0.95</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.7025</v>
+        <v>-2.005</v>
       </c>
     </row>
     <row r="210">
@@ -10887,10 +10887,10 @@
         <v>0.89</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1356</v>
+        <v>-0.1508</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.39</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="211">
@@ -10927,10 +10927,10 @@
         <v>0.53</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4833</v>
+        <v>-0.4902</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.0825</v>
+        <v>-12.255</v>
       </c>
     </row>
     <row r="212">
@@ -10967,10 +10967,10 @@
         <v>1.84</v>
       </c>
       <c r="I212" t="n">
-        <v>1.4737</v>
+        <v>1.4712</v>
       </c>
       <c r="J212" t="n">
-        <v>28.0003</v>
+        <v>27.9528</v>
       </c>
     </row>
     <row r="213">
@@ -11007,10 +11007,10 @@
         <v>1.55</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1473</v>
+        <v>1.1219</v>
       </c>
       <c r="J213" t="n">
-        <v>21.7987</v>
+        <v>21.3161</v>
       </c>
     </row>
     <row r="214">
@@ -11047,10 +11047,10 @@
         <v>1.54</v>
       </c>
       <c r="I214" t="n">
-        <v>1.136</v>
+        <v>1.1095</v>
       </c>
       <c r="J214" t="n">
-        <v>21.584</v>
+        <v>21.0805</v>
       </c>
     </row>
     <row r="215">
@@ -11087,10 +11087,10 @@
         <v>1.49</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0776</v>
+        <v>1.0448</v>
       </c>
       <c r="J215" t="n">
-        <v>20.4744</v>
+        <v>19.8512</v>
       </c>
     </row>
     <row r="216">
@@ -11127,10 +11127,10 @@
         <v>1.38</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9015</v>
+        <v>0.861</v>
       </c>
       <c r="J216" t="n">
-        <v>17.1285</v>
+        <v>16.359</v>
       </c>
     </row>
     <row r="217">
@@ -11167,10 +11167,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I217" t="n">
-        <v>0.0295</v>
+        <v>-0.0173</v>
       </c>
       <c r="J217" t="n">
-        <v>0.5605</v>
+        <v>-0.3287</v>
       </c>
     </row>
     <row r="218">
@@ -11207,10 +11207,10 @@
         <v>0.66</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3121</v>
+        <v>-0.3361</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.9299</v>
+        <v>-6.3859</v>
       </c>
     </row>
     <row r="219">
@@ -11247,10 +11247,10 @@
         <v>0.59</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3791</v>
+        <v>-0.3998</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.2029</v>
+        <v>-7.5962</v>
       </c>
     </row>
     <row r="220">
@@ -11287,10 +11287,10 @@
         <v>0.42</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.5467</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.1802</v>
+        <v>-10.3873</v>
       </c>
     </row>
     <row r="221">
@@ -11327,10 +11327,10 @@
         <v>0.26</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6889</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.129</v>
+        <v>-13.0891</v>
       </c>
     </row>
     <row r="222">
@@ -11367,10 +11367,10 @@
         <v>1.14</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4414</v>
+        <v>0.4306</v>
       </c>
       <c r="J222" t="n">
-        <v>11.9178</v>
+        <v>11.6262</v>
       </c>
     </row>
     <row r="223">
@@ -11407,10 +11407,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3597</v>
+        <v>0.3559</v>
       </c>
       <c r="J223" t="n">
-        <v>9.7119</v>
+        <v>9.609299999999999</v>
       </c>
     </row>
     <row r="224">
@@ -11447,10 +11447,10 @@
         <v>1.06</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2158</v>
+        <v>0.2214</v>
       </c>
       <c r="J224" t="n">
-        <v>5.8266</v>
+        <v>5.9778</v>
       </c>
     </row>
     <row r="225">
@@ -11487,10 +11487,10 @@
         <v>0.99</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0663</v>
+        <v>-0.0675</v>
       </c>
       <c r="J225" t="n">
-        <v>-1.7901</v>
+        <v>-1.8225</v>
       </c>
     </row>
     <row r="226">
@@ -11527,10 +11527,10 @@
         <v>0.98</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1071</v>
+        <v>-0.1087</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.8917</v>
+        <v>-2.9349</v>
       </c>
     </row>
     <row r="227">
@@ -11567,10 +11567,10 @@
         <v>1.37</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7103</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="J227" t="n">
-        <v>19.1781</v>
+        <v>18.522</v>
       </c>
     </row>
     <row r="228">
@@ -11607,10 +11607,10 @@
         <v>1.32</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6269</v>
+        <v>0.6105</v>
       </c>
       <c r="J228" t="n">
-        <v>16.9263</v>
+        <v>16.4835</v>
       </c>
     </row>
     <row r="229">
@@ -11647,10 +11647,10 @@
         <v>1.19</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4009</v>
+        <v>0.4025</v>
       </c>
       <c r="J229" t="n">
-        <v>10.8243</v>
+        <v>10.8675</v>
       </c>
     </row>
     <row r="230">
@@ -11687,10 +11687,10 @@
         <v>0.82</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2267</v>
+        <v>-0.2385</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.1209</v>
+        <v>-6.4395</v>
       </c>
     </row>
     <row r="231">
@@ -11727,10 +11727,10 @@
         <v>0.65</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3903</v>
+        <v>-0.3987</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.5381</v>
+        <v>-10.7649</v>
       </c>
     </row>
     <row r="232">
@@ -11767,10 +11767,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2633</v>
+        <v>1.2308</v>
       </c>
       <c r="J232" t="n">
-        <v>37.899</v>
+        <v>36.924</v>
       </c>
     </row>
     <row r="233">
@@ -11807,10 +11807,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3718</v>
+        <v>0.3707</v>
       </c>
       <c r="J233" t="n">
-        <v>11.154</v>
+        <v>11.121</v>
       </c>
     </row>
     <row r="234">
@@ -11847,10 +11847,10 @@
         <v>1.07</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2312</v>
+        <v>0.2399</v>
       </c>
       <c r="J234" t="n">
-        <v>6.936</v>
+        <v>7.197</v>
       </c>
     </row>
     <row r="235">
@@ -11887,10 +11887,10 @@
         <v>1.01</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0236</v>
+        <v>0.0383</v>
       </c>
       <c r="J235" t="n">
-        <v>0.708</v>
+        <v>1.149</v>
       </c>
     </row>
     <row r="236">
@@ -11927,10 +11927,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.443</v>
+        <v>-0.42</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.29</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="237">
@@ -11967,10 +11967,10 @@
         <v>1.09</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2604</v>
+        <v>0.2579</v>
       </c>
       <c r="J237" t="n">
-        <v>7.812</v>
+        <v>7.737</v>
       </c>
     </row>
     <row r="238">
@@ -12007,10 +12007,10 @@
         <v>0.9</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1235</v>
+        <v>-0.1387</v>
       </c>
       <c r="J238" t="n">
-        <v>-3.705</v>
+        <v>-4.161</v>
       </c>
     </row>
     <row r="239">
@@ -12047,10 +12047,10 @@
         <v>0.89</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.134</v>
+        <v>-0.1496</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.02</v>
+        <v>-4.488</v>
       </c>
     </row>
     <row r="240">
@@ -12087,10 +12087,10 @@
         <v>0.83</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1953</v>
+        <v>-0.2119</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.859</v>
+        <v>-6.357</v>
       </c>
     </row>
     <row r="241">
@@ -12127,10 +12127,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2939</v>
+        <v>-0.3091</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.817</v>
+        <v>-9.273</v>
       </c>
     </row>
     <row r="242">
@@ -12167,10 +12167,10 @@
         <v>0.85</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.4836</v>
+        <v>-0.4655</v>
       </c>
       <c r="J242" t="n">
-        <v>-13.0572</v>
+        <v>-12.5685</v>
       </c>
     </row>
     <row r="243">
@@ -12207,10 +12207,10 @@
         <v>0.68</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.9182</v>
+        <v>-0.8484</v>
       </c>
       <c r="J243" t="n">
-        <v>-24.7914</v>
+        <v>-22.9068</v>
       </c>
     </row>
     <row r="244">
@@ -12247,10 +12247,10 @@
         <v>0.57</v>
       </c>
       <c r="I244" t="n">
-        <v>-1.1822</v>
+        <v>-1.0751</v>
       </c>
       <c r="J244" t="n">
-        <v>-31.9194</v>
+        <v>-29.0277</v>
       </c>
     </row>
     <row r="245">
@@ -12287,10 +12287,10 @@
         <v>1.51</v>
       </c>
       <c r="I245" t="n">
-        <v>1.2266</v>
+        <v>1.1821</v>
       </c>
       <c r="J245" t="n">
-        <v>33.1182</v>
+        <v>31.9167</v>
       </c>
     </row>
     <row r="246">
@@ -12327,10 +12327,10 @@
         <v>1.31</v>
       </c>
       <c r="I246" t="n">
-        <v>0.9071</v>
+        <v>0.8368</v>
       </c>
       <c r="J246" t="n">
-        <v>24.4917</v>
+        <v>22.5936</v>
       </c>
     </row>
     <row r="247">
@@ -12367,10 +12367,10 @@
         <v>1.16</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4089</v>
+        <v>0.397</v>
       </c>
       <c r="J247" t="n">
-        <v>11.0403</v>
+        <v>10.719</v>
       </c>
     </row>
     <row r="248">
@@ -12407,10 +12407,10 @@
         <v>0.72</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.3022</v>
+        <v>-0.3174</v>
       </c>
       <c r="J248" t="n">
-        <v>-8.1594</v>
+        <v>-8.569800000000001</v>
       </c>
     </row>
     <row r="249">
@@ -12447,10 +12447,10 @@
         <v>0.37</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.6238</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="J249" t="n">
-        <v>-16.8426</v>
+        <v>-16.8075</v>
       </c>
     </row>
     <row r="250">
@@ -12487,10 +12487,10 @@
         <v>1.12</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3278</v>
+        <v>0.3211</v>
       </c>
       <c r="J250" t="n">
-        <v>8.8506</v>
+        <v>8.669700000000001</v>
       </c>
     </row>
     <row r="251">
@@ -12527,10 +12527,10 @@
         <v>1.02</v>
       </c>
       <c r="I251" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0955</v>
       </c>
       <c r="J251" t="n">
-        <v>2.6082</v>
+        <v>2.5785</v>
       </c>
     </row>
     <row r="252">
@@ -12567,10 +12567,10 @@
         <v>0.8</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.6082</v>
+        <v>-0.5784</v>
       </c>
       <c r="J252" t="n">
-        <v>-17.6378</v>
+        <v>-16.7736</v>
       </c>
     </row>
     <row r="253">
@@ -12607,10 +12607,10 @@
         <v>0.67</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.9348</v>
+        <v>-0.864</v>
       </c>
       <c r="J253" t="n">
-        <v>-27.1092</v>
+        <v>-25.056</v>
       </c>
     </row>
     <row r="254">
@@ -12647,10 +12647,10 @@
         <v>0.67</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.9348</v>
+        <v>-0.864</v>
       </c>
       <c r="J254" t="n">
-        <v>-27.1092</v>
+        <v>-25.056</v>
       </c>
     </row>
     <row r="255">
@@ -12687,10 +12687,10 @@
         <v>1.5</v>
       </c>
       <c r="I255" t="n">
-        <v>1.2246</v>
+        <v>1.1781</v>
       </c>
       <c r="J255" t="n">
-        <v>35.5134</v>
+        <v>34.1649</v>
       </c>
     </row>
     <row r="256">
@@ -12727,10 +12727,10 @@
         <v>1.15</v>
       </c>
       <c r="I256" t="n">
-        <v>0.5069</v>
+        <v>0.4818</v>
       </c>
       <c r="J256" t="n">
-        <v>14.7001</v>
+        <v>13.9722</v>
       </c>
     </row>
     <row r="257">
@@ -12767,10 +12767,10 @@
         <v>0.88</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.1456</v>
+        <v>-0.1612</v>
       </c>
       <c r="J257" t="n">
-        <v>-4.2224</v>
+        <v>-4.6748</v>
       </c>
     </row>
     <row r="258">
@@ -12807,10 +12807,10 @@
         <v>0.86</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1665</v>
+        <v>-0.1824</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.8285</v>
+        <v>-5.2896</v>
       </c>
     </row>
     <row r="259">
@@ -12847,10 +12847,10 @@
         <v>0.61</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4092</v>
+        <v>-0.4199</v>
       </c>
       <c r="J259" t="n">
-        <v>-11.8668</v>
+        <v>-12.1771</v>
       </c>
     </row>
     <row r="260">
@@ -12887,10 +12887,10 @@
         <v>1.14</v>
       </c>
       <c r="I260" t="n">
-        <v>0.358</v>
+        <v>0.3517</v>
       </c>
       <c r="J260" t="n">
-        <v>10.382</v>
+        <v>10.1993</v>
       </c>
     </row>
     <row r="261">
@@ -12927,10 +12927,10 @@
         <v>1.03</v>
       </c>
       <c r="I261" t="n">
-        <v>0.1152</v>
+        <v>0.1169</v>
       </c>
       <c r="J261" t="n">
-        <v>3.3408</v>
+        <v>3.3901</v>
       </c>
     </row>
     <row r="262">
@@ -12967,10 +12967,10 @@
         <v>1.64</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2949</v>
+        <v>1.272</v>
       </c>
       <c r="J262" t="n">
-        <v>29.7827</v>
+        <v>29.256</v>
       </c>
     </row>
     <row r="263">
@@ -13007,10 +13007,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0172</v>
+        <v>0.9664</v>
       </c>
       <c r="J263" t="n">
-        <v>23.3956</v>
+        <v>22.2272</v>
       </c>
     </row>
     <row r="264">
@@ -13047,10 +13047,10 @@
         <v>1.3</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7743</v>
+        <v>0.7398</v>
       </c>
       <c r="J264" t="n">
-        <v>17.8089</v>
+        <v>17.0154</v>
       </c>
     </row>
     <row r="265">
@@ -13087,10 +13087,10 @@
         <v>1.27</v>
       </c>
       <c r="I265" t="n">
-        <v>0.7087</v>
+        <v>0.6813</v>
       </c>
       <c r="J265" t="n">
-        <v>16.3001</v>
+        <v>15.6699</v>
       </c>
     </row>
     <row r="266">
@@ -13127,10 +13127,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6691</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-15.3893</v>
+        <v>-14.1772</v>
       </c>
     </row>
     <row r="267">
@@ -13167,10 +13167,10 @@
         <v>1.07</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2346</v>
+        <v>0.2288</v>
       </c>
       <c r="J267" t="n">
-        <v>5.3958</v>
+        <v>5.2624</v>
       </c>
     </row>
     <row r="268">
@@ -13207,10 +13207,10 @@
         <v>1.06</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2114</v>
+        <v>0.2063</v>
       </c>
       <c r="J268" t="n">
-        <v>4.8622</v>
+        <v>4.7449</v>
       </c>
     </row>
     <row r="269">
@@ -13247,10 +13247,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2393</v>
+        <v>-0.2568</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.5039</v>
+        <v>-5.9064</v>
       </c>
     </row>
     <row r="270">
@@ -13287,10 +13287,10 @@
         <v>0.68</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3354</v>
+        <v>-0.3505</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.7142</v>
+        <v>-8.061500000000001</v>
       </c>
     </row>
     <row r="271">
@@ -13327,10 +13327,10 @@
         <v>0.62</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3919</v>
+        <v>-0.4047</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.0137</v>
+        <v>-9.3081</v>
       </c>
     </row>
     <row r="272">
@@ -13367,10 +13367,10 @@
         <v>1.55</v>
       </c>
       <c r="I272" t="n">
-        <v>1.2031</v>
+        <v>1.1706</v>
       </c>
       <c r="J272" t="n">
-        <v>32.4837</v>
+        <v>31.6062</v>
       </c>
     </row>
     <row r="273">
@@ -13407,10 +13407,10 @@
         <v>1.3</v>
       </c>
       <c r="I273" t="n">
-        <v>0.7913</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="J273" t="n">
-        <v>21.3651</v>
+        <v>20.2905</v>
       </c>
     </row>
     <row r="274">
@@ -13447,10 +13447,10 @@
         <v>1.29</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7684</v>
+        <v>0.7312</v>
       </c>
       <c r="J274" t="n">
-        <v>20.7468</v>
+        <v>19.7424</v>
       </c>
     </row>
     <row r="275">
@@ -13487,10 +13487,10 @@
         <v>1.18</v>
       </c>
       <c r="I275" t="n">
-        <v>0.511</v>
+        <v>0.501</v>
       </c>
       <c r="J275" t="n">
-        <v>13.797</v>
+        <v>13.527</v>
       </c>
     </row>
     <row r="276">
@@ -13527,10 +13527,10 @@
         <v>0.72</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8776</v>
+        <v>-0.8037</v>
       </c>
       <c r="J276" t="n">
-        <v>-23.6952</v>
+        <v>-21.6999</v>
       </c>
     </row>
     <row r="277">
@@ -13567,10 +13567,10 @@
         <v>1.06</v>
       </c>
       <c r="I277" t="n">
-        <v>0.184</v>
+        <v>0.1863</v>
       </c>
       <c r="J277" t="n">
-        <v>4.968</v>
+        <v>5.0301</v>
       </c>
     </row>
     <row r="278">
@@ -13607,10 +13607,10 @@
         <v>1.02</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0849</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J278" t="n">
-        <v>2.2923</v>
+        <v>2.349</v>
       </c>
     </row>
     <row r="279">
@@ -13647,10 +13647,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0164</v>
+        <v>0.0117</v>
       </c>
       <c r="J279" t="n">
-        <v>0.4428</v>
+        <v>0.3159</v>
       </c>
     </row>
     <row r="280">
@@ -13687,10 +13687,10 @@
         <v>0.8</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2289</v>
+        <v>-0.2445</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.1803</v>
+        <v>-6.6015</v>
       </c>
     </row>
     <row r="281">
@@ -13727,10 +13727,10 @@
         <v>0.7</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3262</v>
+        <v>-0.3398</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.807399999999999</v>
+        <v>-9.1746</v>
       </c>
     </row>
     <row r="282">
@@ -13767,10 +13767,10 @@
         <v>0.99</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.0538</v>
+        <v>-0.0589</v>
       </c>
       <c r="J282" t="n">
-        <v>-1.9368</v>
+        <v>-2.1204</v>
       </c>
     </row>
     <row r="283">
@@ -13807,10 +13807,10 @@
         <v>0.96</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1648</v>
+        <v>-0.1691</v>
       </c>
       <c r="J283" t="n">
-        <v>-5.9328</v>
+        <v>-6.0876</v>
       </c>
     </row>
     <row r="284">
@@ -13847,10 +13847,10 @@
         <v>0.91</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3203</v>
+        <v>-0.3155</v>
       </c>
       <c r="J284" t="n">
-        <v>-11.5308</v>
+        <v>-11.358</v>
       </c>
     </row>
     <row r="285">
@@ -13887,10 +13887,10 @@
         <v>1.09</v>
       </c>
       <c r="I285" t="n">
-        <v>0.3191</v>
+        <v>0.3147</v>
       </c>
       <c r="J285" t="n">
-        <v>11.4876</v>
+        <v>11.3292</v>
       </c>
     </row>
     <row r="286">
@@ -13927,10 +13927,10 @@
         <v>1.06</v>
       </c>
       <c r="I286" t="n">
-        <v>0.2284</v>
+        <v>0.23</v>
       </c>
       <c r="J286" t="n">
-        <v>8.2224</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13967,10 +13967,10 @@
         <v>0.78</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.2436</v>
+        <v>-0.2602</v>
       </c>
       <c r="J287" t="n">
-        <v>-8.769600000000001</v>
+        <v>-9.3672</v>
       </c>
     </row>
     <row r="288">
@@ -14007,10 +14007,10 @@
         <v>0.61</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.4057</v>
+        <v>-0.4171</v>
       </c>
       <c r="J288" t="n">
-        <v>-14.6052</v>
+        <v>-15.0156</v>
       </c>
     </row>
     <row r="289">
@@ -14047,10 +14047,10 @@
         <v>0.33</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.6591</v>
+        <v>-0.6554</v>
       </c>
       <c r="J289" t="n">
-        <v>-23.7276</v>
+        <v>-23.5944</v>
       </c>
     </row>
     <row r="290">
@@ -14087,10 +14087,10 @@
         <v>1.34</v>
       </c>
       <c r="I290" t="n">
-        <v>0.7472</v>
+        <v>0.705</v>
       </c>
       <c r="J290" t="n">
-        <v>26.8992</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="291">
@@ -14127,10 +14127,10 @@
         <v>1.32</v>
       </c>
       <c r="I291" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6727</v>
       </c>
       <c r="J291" t="n">
-        <v>25.6032</v>
+        <v>24.2172</v>
       </c>
     </row>
     <row r="292">
@@ -14167,10 +14167,10 @@
         <v>0.76</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.2479</v>
+        <v>-0.2677</v>
       </c>
       <c r="J292" t="n">
-        <v>-5.7017</v>
+        <v>-6.1571</v>
       </c>
     </row>
     <row r="293">
@@ -14207,10 +14207,10 @@
         <v>0.74</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.2659</v>
+        <v>-0.2855</v>
       </c>
       <c r="J293" t="n">
-        <v>-6.1157</v>
+        <v>-6.5665</v>
       </c>
     </row>
     <row r="294">
@@ -14247,10 +14247,10 @@
         <v>0.58</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.4153</v>
+        <v>-0.4293</v>
       </c>
       <c r="J294" t="n">
-        <v>-9.5519</v>
+        <v>-9.873900000000001</v>
       </c>
     </row>
     <row r="295">
@@ -14287,10 +14287,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1345</v>
+        <v>-0.1553</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.0935</v>
+        <v>-3.5719</v>
       </c>
     </row>
     <row r="296">
@@ -14327,10 +14327,10 @@
         <v>0.78</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2288</v>
+        <v>-0.2488</v>
       </c>
       <c r="J296" t="n">
-        <v>-5.2624</v>
+        <v>-5.7224</v>
       </c>
     </row>
     <row r="297">
@@ -14367,10 +14367,10 @@
         <v>0.46</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.5423</v>
+        <v>-0.5465</v>
       </c>
       <c r="J297" t="n">
-        <v>-12.4729</v>
+        <v>-12.5695</v>
       </c>
     </row>
     <row r="298">
@@ -14407,10 +14407,10 @@
         <v>0.23</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.7469</v>
+        <v>-0.7366</v>
       </c>
       <c r="J298" t="n">
-        <v>-17.1787</v>
+        <v>-16.9418</v>
       </c>
     </row>
     <row r="299">
@@ -14447,10 +14447,10 @@
         <v>0.21</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.7644</v>
+        <v>-0.7528</v>
       </c>
       <c r="J299" t="n">
-        <v>-17.5812</v>
+        <v>-17.3144</v>
       </c>
     </row>
     <row r="300">
@@ -14487,10 +14487,10 @@
         <v>2</v>
       </c>
       <c r="I300" t="n">
-        <v>1.1908</v>
+        <v>1.1801</v>
       </c>
       <c r="J300" t="n">
-        <v>27.3884</v>
+        <v>27.1423</v>
       </c>
     </row>
     <row r="301">
@@ -14527,10 +14527,10 @@
         <v>1.45</v>
       </c>
       <c r="I301" t="n">
-        <v>0.673</v>
+        <v>0.6543</v>
       </c>
       <c r="J301" t="n">
-        <v>15.479</v>
+        <v>15.0489</v>
       </c>
     </row>
     <row r="302">
@@ -14567,10 +14567,10 @@
         <v>1.21</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6314</v>
+        <v>0.5994</v>
       </c>
       <c r="J302" t="n">
-        <v>18.3106</v>
+        <v>17.3826</v>
       </c>
     </row>
     <row r="303">
@@ -14607,10 +14607,10 @@
         <v>0.95</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2068</v>
+        <v>-0.2069</v>
       </c>
       <c r="J303" t="n">
-        <v>-5.9972</v>
+        <v>-6.0001</v>
       </c>
     </row>
     <row r="304">
@@ -14647,10 +14647,10 @@
         <v>0.78</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.6835</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="J304" t="n">
-        <v>-19.8215</v>
+        <v>-18.5774</v>
       </c>
     </row>
     <row r="305">
@@ -14687,10 +14687,10 @@
         <v>1.13</v>
       </c>
       <c r="I305" t="n">
-        <v>0.4208</v>
+        <v>0.4104</v>
       </c>
       <c r="J305" t="n">
-        <v>12.2032</v>
+        <v>11.9016</v>
       </c>
     </row>
     <row r="306">
@@ -14727,10 +14727,10 @@
         <v>1.11</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3655</v>
+        <v>0.3599</v>
       </c>
       <c r="J306" t="n">
-        <v>10.5995</v>
+        <v>10.4371</v>
       </c>
     </row>
     <row r="307">
@@ -14767,10 +14767,10 @@
         <v>1.1</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2255</v>
+        <v>0.2376</v>
       </c>
       <c r="J307" t="n">
-        <v>6.5395</v>
+        <v>6.8904</v>
       </c>
     </row>
     <row r="308">
@@ -14807,10 +14807,10 @@
         <v>0.98</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0481</v>
+        <v>-0.0521</v>
       </c>
       <c r="J308" t="n">
-        <v>-1.3949</v>
+        <v>-1.5109</v>
       </c>
     </row>
     <row r="309">
@@ -14847,10 +14847,10 @@
         <v>0.98</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0481</v>
+        <v>-0.0521</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.3949</v>
+        <v>-1.5109</v>
       </c>
     </row>
     <row r="310">
@@ -14887,10 +14887,10 @@
         <v>1.57</v>
       </c>
       <c r="I310" t="n">
-        <v>0.9974</v>
+        <v>0.9545</v>
       </c>
       <c r="J310" t="n">
-        <v>28.9246</v>
+        <v>27.6805</v>
       </c>
     </row>
     <row r="311">
@@ -14927,10 +14927,10 @@
         <v>0.99</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.0323</v>
+        <v>-0.0343</v>
       </c>
       <c r="J311" t="n">
-        <v>-0.9367</v>
+        <v>-0.9947</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5528/event_5528_evp_summary.xlsx
+++ b/database/event/5528/event_5528_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2645</v>
+        <v>6.3478</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6219</v>
+        <v>2.6567</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2275</v>
+        <v>2.2859</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2645</v>
+        <v>6.3478</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7396</v>
+        <v>2.7992</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5249</v>
+        <v>3.5486</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1449</v>
+        <v>4.0667</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2382</v>
+        <v>2.2833</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5249</v>
+        <v>3.5486</v>
       </c>
       <c r="K2" t="n">
         <v>197</v>
@@ -529,7 +529,7 @@
         <v>134</v>
       </c>
       <c r="M2" t="n">
-        <v>5.7631</v>
+        <v>5.8319</v>
       </c>
       <c r="N2" t="n">
         <v>331</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.6072</v>
+        <v>4.6208</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9282</v>
+        <v>1.9339</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4731</v>
+        <v>1.4992</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6072</v>
+        <v>4.6208</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7795</v>
+        <v>2.775</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8277</v>
+        <v>1.8458</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2765</v>
+        <v>3.9758</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3093</v>
+        <v>2.2323</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8277</v>
+        <v>1.8458</v>
       </c>
       <c r="K3" t="n">
         <v>167</v>
@@ -575,7 +575,7 @@
         <v>137</v>
       </c>
       <c r="M3" t="n">
-        <v>4.137</v>
+        <v>4.0781</v>
       </c>
       <c r="N3" t="n">
         <v>304</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4511</v>
+        <v>4.2703</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8629</v>
+        <v>1.7872</v>
       </c>
       <c r="D4" t="n">
-        <v>1.402</v>
+        <v>1.3395</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4511</v>
+        <v>4.2703</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1453</v>
+        <v>3.0268</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3058</v>
+        <v>1.2435</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4832</v>
+        <v>4.9214</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9609</v>
+        <v>2.7632</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3058</v>
+        <v>1.2435</v>
       </c>
       <c r="K4" t="n">
         <v>167</v>
@@ -621,7 +621,7 @@
         <v>137</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2667</v>
+        <v>4.0067</v>
       </c>
       <c r="N4" t="n">
         <v>304</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4888</v>
+        <v>3.3608</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4602</v>
+        <v>1.4066</v>
       </c>
       <c r="D5" t="n">
-        <v>0.964</v>
+        <v>0.9252</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4888</v>
+        <v>3.3608</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9297</v>
+        <v>3.8031</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4409</v>
+        <v>-0.4423</v>
       </c>
       <c r="H5" t="n">
-        <v>8.071199999999999</v>
+        <v>7.8359</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3584</v>
+        <v>4.3996</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4409</v>
+        <v>-0.4423</v>
       </c>
       <c r="K5" t="n">
         <v>117</v>
@@ -667,7 +667,7 @@
         <v>56</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9175</v>
+        <v>3.9573</v>
       </c>
       <c r="N5" t="n">
         <v>173</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7646</v>
+        <v>2.7767</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1571</v>
+        <v>1.1621</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6343</v>
+        <v>0.6591</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7646</v>
+        <v>2.7767</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3835</v>
+        <v>2.428</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3811</v>
+        <v>0.3487</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9699</v>
+        <v>2.6732</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6037</v>
+        <v>1.5009</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3811</v>
+        <v>0.3487</v>
       </c>
       <c r="K6" t="n">
         <v>96</v>
@@ -713,7 +713,7 @@
         <v>57</v>
       </c>
       <c r="M6" t="n">
-        <v>1.9848</v>
+        <v>1.8496</v>
       </c>
       <c r="N6" t="n">
         <v>153</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7234</v>
+        <v>2.6354</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1398</v>
+        <v>1.103</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6155</v>
+        <v>0.5948</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7234</v>
+        <v>2.6354</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0481</v>
+        <v>2.9462</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3247</v>
+        <v>-0.3108</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1625</v>
+        <v>4.6188</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7877</v>
+        <v>2.5933</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3247</v>
+        <v>-0.3108</v>
       </c>
       <c r="K7" t="n">
         <v>144</v>
@@ -759,7 +759,7 @@
         <v>106</v>
       </c>
       <c r="M7" t="n">
-        <v>2.463</v>
+        <v>2.2825</v>
       </c>
       <c r="N7" t="n">
         <v>250</v>
@@ -768,185 +768,185 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5105</v>
+        <v>2.4925</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0507</v>
+        <v>1.0432</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5105</v>
+        <v>2.4925</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5105</v>
+        <v>2.4925</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7697</v>
+        <v>2.7619</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1454</v>
+        <v>3.1512</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1454</v>
+        <v>3.1512</v>
       </c>
       <c r="N8" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4424</v>
+        <v>2.4452</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0222</v>
+        <v>1.0234</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4876</v>
+        <v>0.5081</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4424</v>
+        <v>2.4452</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4424</v>
+        <v>2.4452</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6207</v>
+        <v>2.6535</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7575</v>
+        <v>3.0275</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7575</v>
+        <v>3.0275</v>
       </c>
       <c r="N9" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4092</v>
+        <v>2.4412</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0083</v>
+        <v>1.0217</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4725</v>
+        <v>0.5063</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4092</v>
+        <v>2.4412</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4092</v>
+        <v>2.4916</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.0504</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5479</v>
+        <v>2.912</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8936</v>
+        <v>1.635</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.0504</v>
       </c>
       <c r="K10" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8936</v>
+        <v>1.5846</v>
       </c>
       <c r="N10" t="n">
-        <v>170</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3658</v>
+        <v>2.3745</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9901</v>
+        <v>0.9938</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4528</v>
+        <v>0.4759</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3658</v>
+        <v>2.3745</v>
       </c>
       <c r="F11" t="n">
-        <v>2.409</v>
+        <v>2.3745</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0432</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0539</v>
+        <v>2.4914</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6491</v>
+        <v>2.6264</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0432</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="L11" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6059</v>
+        <v>2.6264</v>
       </c>
       <c r="N11" t="n">
-        <v>304</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.845</v>
+        <v>1.7954</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7722</v>
+        <v>0.7514</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2157</v>
+        <v>0.2121</v>
       </c>
       <c r="E12" t="n">
-        <v>1.845</v>
+        <v>1.7954</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2171</v>
+        <v>1.1929</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6279</v>
+        <v>0.6025</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2171</v>
+        <v>1.1929</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6572</v>
+        <v>0.6698</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6279</v>
+        <v>0.6025</v>
       </c>
       <c r="K12" t="n">
         <v>156</v>
@@ -989,7 +989,7 @@
         <v>134</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2851</v>
+        <v>1.2723</v>
       </c>
       <c r="N12" t="n">
         <v>290</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7625</v>
+        <v>1.58</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7377</v>
+        <v>0.6613</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1781</v>
+        <v>0.114</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7625</v>
+        <v>1.58</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1363</v>
+        <v>1.4006</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6262</v>
+        <v>0.1794</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1363</v>
+        <v>1.4006</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6136</v>
+        <v>0.7864</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6262</v>
+        <v>0.1794</v>
       </c>
       <c r="K13" t="n">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="L13" t="n">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2398</v>
+        <v>0.9658</v>
       </c>
       <c r="N13" t="n">
-        <v>337</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6309</v>
+        <v>1.4745</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6826</v>
+        <v>0.6171</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1182</v>
+        <v>0.0659</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6309</v>
+        <v>1.4745</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4347</v>
+        <v>0.9764</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1962</v>
+        <v>0.4981</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4347</v>
+        <v>0.9764</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.5482</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1962</v>
+        <v>0.4981</v>
       </c>
       <c r="K14" t="n">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="L14" t="n">
-        <v>25</v>
+        <v>161</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9709000000000001</v>
+        <v>1.0463</v>
       </c>
       <c r="N14" t="n">
-        <v>115</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4877</v>
+        <v>1.3049</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6226</v>
+        <v>0.5461</v>
       </c>
       <c r="D15" t="n">
-        <v>0.053</v>
+        <v>-0.0113</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4877</v>
+        <v>1.3049</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4877</v>
+        <v>1.3049</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4877</v>
+        <v>1.3049</v>
       </c>
       <c r="I15" t="n">
-        <v>1.526</v>
+        <v>1.3398</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.526</v>
+        <v>1.3398</v>
       </c>
       <c r="N15" t="n">
         <v>153</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2272</v>
+        <v>1.2984</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5434</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0143</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2272</v>
+        <v>1.2984</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5446</v>
+        <v>2.6446</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3174</v>
+        <v>-1.3462</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5015</v>
+        <v>3.4862</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8908</v>
+        <v>1.9574</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3174</v>
+        <v>-1.3462</v>
       </c>
       <c r="K16" t="n">
         <v>167</v>
@@ -1173,7 +1173,7 @@
         <v>137</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5734000000000001</v>
+        <v>0.6112</v>
       </c>
       <c r="N16" t="n">
         <v>304</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2227</v>
+        <v>1.1161</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5117</v>
+        <v>0.4671</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0974</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2227</v>
+        <v>1.1161</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2227</v>
+        <v>1.1161</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2227</v>
+        <v>1.1161</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2865</v>
+        <v>1.1765</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2865</v>
+        <v>1.1765</v>
       </c>
       <c r="N17" t="n">
         <v>172</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0061</v>
+        <v>1.0695</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4211</v>
+        <v>0.4476</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1662</v>
+        <v>-0.1186</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0061</v>
+        <v>1.0695</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1226</v>
+        <v>1.0695</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1165</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1226</v>
+        <v>1.0695</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6062</v>
+        <v>1.2202</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1165</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="L18" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4897</v>
+        <v>1.2202</v>
       </c>
       <c r="N18" t="n">
-        <v>304</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9629</v>
+        <v>0.8496</v>
       </c>
       <c r="C19" t="n">
-        <v>0.403</v>
+        <v>0.3556</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1859</v>
+        <v>-0.2188</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9629</v>
+        <v>0.8496</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9629</v>
+        <v>1.0603</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.2107</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9629</v>
+        <v>1.0603</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0935</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.2107</v>
       </c>
       <c r="K19" t="n">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0935</v>
+        <v>0.3846000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>189</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8864</v>
+        <v>0.8024</v>
       </c>
       <c r="C20" t="n">
-        <v>0.371</v>
+        <v>0.3358</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2207</v>
+        <v>-0.2403</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8864</v>
+        <v>0.8024</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7202</v>
+        <v>0.6688</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1662</v>
+        <v>0.1336</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7202</v>
+        <v>0.6688</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3889</v>
+        <v>0.3755</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1662</v>
+        <v>0.1336</v>
       </c>
       <c r="K20" t="n">
         <v>155</v>
@@ -1357,7 +1357,7 @@
         <v>57</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5551</v>
+        <v>0.5091</v>
       </c>
       <c r="N20" t="n">
         <v>212</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5938</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2411</v>
+        <v>0.2485</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.362</v>
+        <v>-0.3353</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5938</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5938</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5938</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6542</v>
+        <v>0.6775</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6542</v>
+        <v>0.6775</v>
       </c>
       <c r="N21" t="n">
         <v>216</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3093</v>
+        <v>0.1658</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1295</v>
+        <v>0.0694</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4834</v>
+        <v>-0.5303</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3093</v>
+        <v>0.1658</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3093</v>
+        <v>0.1658</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3093</v>
+        <v>0.1658</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3093</v>
+        <v>0.1658</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3093</v>
+        <v>0.1658</v>
       </c>
       <c r="N22" t="n">
         <v>94</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0258</v>
+        <v>-0.0431</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0108</v>
+        <v>-0.018</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6125</v>
+        <v>-0.6254</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0258</v>
+        <v>-0.0431</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7758</v>
+        <v>-0.8814</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8016</v>
+        <v>0.8383</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7758</v>
+        <v>-0.8814</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4189</v>
+        <v>-0.4949</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8016</v>
+        <v>0.8383</v>
       </c>
       <c r="K23" t="n">
         <v>238</v>
@@ -1495,7 +1495,7 @@
         <v>188</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3827</v>
+        <v>0.3434</v>
       </c>
       <c r="N23" t="n">
         <v>426</v>
@@ -1504,369 +1504,369 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2011</v>
+        <v>-0.1637</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0842</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7157</v>
+        <v>-0.6804</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2011</v>
+        <v>-0.1637</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1239</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0772</v>
+        <v>0.5193</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1239</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0669</v>
+        <v>-0.3835</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0772</v>
+        <v>0.5193</v>
       </c>
       <c r="K24" t="n">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="L24" t="n">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1441</v>
+        <v>0.1358</v>
       </c>
       <c r="N24" t="n">
-        <v>248</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2125</v>
+        <v>-0.212</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.0887</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7209</v>
+        <v>-0.7024</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2125</v>
+        <v>-0.212</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4839</v>
+        <v>-0.5347</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2714</v>
+        <v>0.3227</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4839</v>
+        <v>-0.5347</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2613</v>
+        <v>-0.3002</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2714</v>
+        <v>0.3227</v>
       </c>
       <c r="K25" t="n">
-        <v>178</v>
+        <v>27</v>
       </c>
       <c r="L25" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0101</v>
+        <v>0.02249999999999996</v>
       </c>
       <c r="N25" t="n">
-        <v>235</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Bubzkji</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.223</v>
+        <v>-0.2787</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1166</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7257</v>
+        <v>-0.7327</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.223</v>
+        <v>-0.2787</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5878</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3648</v>
+        <v>-0.2787</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5878</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3174</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3648</v>
+        <v>-0.2787</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>27</v>
       </c>
-      <c r="L26" t="n">
-        <v>29</v>
-      </c>
       <c r="M26" t="n">
-        <v>0.0474</v>
+        <v>-0.2787</v>
       </c>
       <c r="N26" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2475</v>
+        <v>-0.361</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1036</v>
+        <v>-0.1511</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7369</v>
+        <v>-0.7702</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2475</v>
+        <v>-0.361</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.361</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4879</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.361</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3971</v>
+        <v>-0.4012</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4879</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="L27" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.09079999999999999</v>
+        <v>-0.4012</v>
       </c>
       <c r="N27" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bubzkji</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2907</v>
+        <v>-0.4199</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1217</v>
+        <v>-0.1757</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7565</v>
+        <v>-0.7971</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2907</v>
+        <v>-0.4199</v>
       </c>
       <c r="F28" t="n">
+        <v>-0.4199</v>
+      </c>
+      <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="G28" t="n">
-        <v>-0.2907</v>
-      </c>
       <c r="H28" t="n">
+        <v>-0.4199</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.4311</v>
+      </c>
+      <c r="J28" t="n">
         <v>0</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
+        <v>153</v>
+      </c>
+      <c r="L28" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="n">
-        <v>-0.2907</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>27</v>
-      </c>
       <c r="M28" t="n">
-        <v>-0.2907</v>
+        <v>-0.4311</v>
       </c>
       <c r="N28" t="n">
-        <v>27</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.367</v>
+        <v>-0.4442</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1536</v>
+        <v>-0.1859</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7913</v>
+        <v>-0.8081</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.367</v>
+        <v>-0.4442</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.367</v>
+        <v>-0.4442</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.367</v>
+        <v>-0.4442</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4063</v>
+        <v>-0.4561</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4063</v>
+        <v>-0.4561</v>
       </c>
       <c r="N29" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4229</v>
+        <v>-0.4517</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.177</v>
+        <v>-0.189</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8167</v>
+        <v>-0.8116</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4229</v>
+        <v>-0.4517</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4229</v>
+        <v>-0.6674</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.2157</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4229</v>
+        <v>-0.6674</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4338</v>
+        <v>-0.3747</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.2157</v>
       </c>
       <c r="K30" t="n">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4338</v>
+        <v>-0.159</v>
       </c>
       <c r="N30" t="n">
-        <v>153</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4302</v>
+        <v>-0.527</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1801</v>
+        <v>-0.2206</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.82</v>
+        <v>-0.8459</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4302</v>
+        <v>-0.527</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4302</v>
+        <v>-0.3993</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.1277</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4302</v>
+        <v>-0.3993</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4413</v>
+        <v>-0.2242</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.1277</v>
       </c>
       <c r="K31" t="n">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4413</v>
+        <v>-0.3519</v>
       </c>
       <c r="N31" t="n">
-        <v>153</v>
+        <v>248</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6014</v>
+        <v>-0.641</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2517</v>
+        <v>-0.2683</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.898</v>
+        <v>-0.8978</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6014</v>
+        <v>-0.641</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6014</v>
+        <v>-0.641</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6014</v>
+        <v>-0.641</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6328</v>
+        <v>-0.6757</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6328</v>
+        <v>-0.6757</v>
       </c>
       <c r="N32" t="n">
         <v>67</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6083</v>
+        <v>-0.6434</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2546</v>
+        <v>-0.2693</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9011</v>
+        <v>-0.8989</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6083</v>
+        <v>-0.6434</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6083</v>
+        <v>-0.6434</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6083</v>
+        <v>-0.6434</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6083</v>
+        <v>-0.6434</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6083</v>
+        <v>-0.6434</v>
       </c>
       <c r="N33" t="n">
         <v>94</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7631</v>
+        <v>-0.6732</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3194</v>
+        <v>-0.2818</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9716</v>
+        <v>-0.9125</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7631</v>
+        <v>-0.6732</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7631</v>
+        <v>-0.6732</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7631</v>
+        <v>-0.6732</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7631</v>
+        <v>-0.6732</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7631</v>
+        <v>-0.6732</v>
       </c>
       <c r="N34" t="n">
         <v>94</v>
@@ -2010,277 +2010,277 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Nivera</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8202</v>
+        <v>-0.803</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3433</v>
+        <v>-0.3361</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9976</v>
+        <v>-0.9716</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8202</v>
+        <v>-0.803</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8202</v>
+        <v>-0.803</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8202</v>
+        <v>-0.803</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8413</v>
+        <v>-0.9407</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8413</v>
+        <v>-0.9407</v>
       </c>
       <c r="N35" t="n">
-        <v>153</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nivera</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8511</v>
+        <v>-0.8092</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3562</v>
+        <v>-0.3387</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0116</v>
+        <v>-0.9744</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8511</v>
+        <v>-0.8092</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8511</v>
+        <v>-0.8092</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8511</v>
+        <v>-0.8092</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9915</v>
+        <v>-0.8308</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9915</v>
+        <v>-0.8308</v>
       </c>
       <c r="N36" t="n">
-        <v>218</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.877</v>
+        <v>-0.8845</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.367</v>
+        <v>-0.3702</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0234</v>
+        <v>-1.0087</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.877</v>
+        <v>-0.8845</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.877</v>
+        <v>-0.8845</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.877</v>
+        <v>-0.8845</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.877</v>
+        <v>-0.9829</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>94</v>
+        <v>230</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.877</v>
+        <v>-0.9829</v>
       </c>
       <c r="N37" t="n">
-        <v>94</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9797</v>
+        <v>-0.9055</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.41</v>
+        <v>-0.379</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0702</v>
+        <v>-1.0183</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9797</v>
+        <v>-0.9055</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9797</v>
+        <v>-0.9055</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9797</v>
+        <v>-0.9055</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0846</v>
+        <v>-0.9055</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>230</v>
+        <v>94</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0846</v>
+        <v>-0.9055</v>
       </c>
       <c r="N38" t="n">
-        <v>230</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0629</v>
+        <v>-1.0725</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4449</v>
+        <v>-0.4489</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1081</v>
+        <v>-1.0944</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0629</v>
+        <v>-1.0725</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0629</v>
+        <v>-1.0725</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0629</v>
+        <v>-1.0725</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1768</v>
+        <v>-1.1012</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1768</v>
+        <v>-1.1012</v>
       </c>
       <c r="N39" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.145</v>
+        <v>-1.0727</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4792</v>
+        <v>-0.449</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1454</v>
+        <v>-1.0945</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.145</v>
+        <v>-1.0727</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.145</v>
+        <v>-1.0727</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.145</v>
+        <v>-1.0727</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1745</v>
+        <v>-1.192</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1745</v>
+        <v>-1.192</v>
       </c>
       <c r="N40" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.1755</v>
+        <v>-1.1624</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.492</v>
+        <v>-0.4865</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1593</v>
+        <v>-1.1353</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.1755</v>
+        <v>-1.1624</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4898</v>
+        <v>-1.4421</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3143</v>
+        <v>0.2797</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4898</v>
+        <v>-1.4421</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8045</v>
+        <v>-0.8097</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3143</v>
+        <v>0.2797</v>
       </c>
       <c r="K41" t="n">
         <v>218</v>
@@ -2323,7 +2323,7 @@
         <v>161</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.4902</v>
+        <v>-0.53</v>
       </c>
       <c r="N41" t="n">
         <v>379</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.2245</v>
+        <v>-1.1777</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.5125</v>
+        <v>-0.4929</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.1816</v>
+        <v>-1.1423</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.2245</v>
+        <v>-1.1777</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.2245</v>
+        <v>-1.1777</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.2245</v>
+        <v>-1.1777</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.2245</v>
+        <v>-1.1777</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.2245</v>
+        <v>-1.1777</v>
       </c>
       <c r="N42" t="n">
         <v>94</v>
@@ -2382,31 +2382,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-3.1999</v>
+        <v>-2.9717</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.3392</v>
+        <v>-1.2437</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.0809</v>
+        <v>-1.9595</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.1999</v>
+        <v>-2.9717</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.9725</v>
+        <v>-2.7439</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.2274</v>
+        <v>-0.2278</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.9725</v>
+        <v>-2.7439</v>
       </c>
       <c r="I43" t="n">
-        <v>-1.6051</v>
+        <v>-1.5406</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.2274</v>
+        <v>-0.2278</v>
       </c>
       <c r="K43" t="n">
         <v>155</v>
@@ -2415,7 +2415,7 @@
         <v>57</v>
       </c>
       <c r="M43" t="n">
-        <v>-1.8325</v>
+        <v>-1.7684</v>
       </c>
       <c r="N43" t="n">
         <v>212</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-5.4449</v>
+        <v>-5.1931</v>
       </c>
       <c r="C44" t="n">
-        <v>-2.2788</v>
+        <v>-2.1734</v>
       </c>
       <c r="D44" t="n">
-        <v>-3.1028</v>
+        <v>-2.9715</v>
       </c>
       <c r="E44" t="n">
-        <v>-5.4449</v>
+        <v>-5.1931</v>
       </c>
       <c r="F44" t="n">
-        <v>-4.4449</v>
+        <v>-4.1931</v>
       </c>
       <c r="G44" t="n">
         <v>-1</v>
       </c>
       <c r="H44" t="n">
-        <v>-4.4449</v>
+        <v>-4.1931</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.4002</v>
+        <v>-2.3543</v>
       </c>
       <c r="J44" t="n">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>81</v>
       </c>
       <c r="M44" t="n">
-        <v>-3.4002</v>
+        <v>-3.3543</v>
       </c>
       <c r="N44" t="n">
         <v>198</v>
@@ -2567,10 +2567,10 @@
         <v>1.44</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0232</v>
+        <v>1.0177</v>
       </c>
       <c r="J2" t="n">
-        <v>27.6264</v>
+        <v>27.4779</v>
       </c>
     </row>
     <row r="3">
@@ -2607,10 +2607,10 @@
         <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7504</v>
+        <v>0.7237</v>
       </c>
       <c r="J3" t="n">
-        <v>20.2608</v>
+        <v>19.5399</v>
       </c>
     </row>
     <row r="4">
@@ -2647,10 +2647,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6068</v>
+        <v>0.5747</v>
       </c>
       <c r="J4" t="n">
-        <v>16.3836</v>
+        <v>15.5169</v>
       </c>
     </row>
     <row r="5">
@@ -2687,10 +2687,10 @@
         <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4778</v>
+        <v>0.4438</v>
       </c>
       <c r="J5" t="n">
-        <v>12.9006</v>
+        <v>11.9826</v>
       </c>
     </row>
     <row r="6">
@@ -2727,10 +2727,10 @@
         <v>0.93</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2996</v>
+        <v>-0.2604</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.0892</v>
+        <v>-7.0308</v>
       </c>
     </row>
     <row r="7">
@@ -2767,10 +2767,10 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3752</v>
+        <v>0.322</v>
       </c>
       <c r="J7" t="n">
-        <v>10.1304</v>
+        <v>8.694000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2807,10 +2807,10 @@
         <v>1.14</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3565</v>
+        <v>0.304</v>
       </c>
       <c r="J8" t="n">
-        <v>9.625500000000001</v>
+        <v>8.208</v>
       </c>
     </row>
     <row r="9">
@@ -2847,10 +2847,10 @@
         <v>0.92</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1158</v>
+        <v>-0.1001</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.1266</v>
+        <v>-2.7027</v>
       </c>
     </row>
     <row r="10">
@@ -2887,10 +2887,10 @@
         <v>0.75</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2902</v>
+        <v>-0.2717</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.8354</v>
+        <v>-7.3359</v>
       </c>
     </row>
     <row r="11">
@@ -2927,10 +2927,10 @@
         <v>0.48</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5311</v>
+        <v>-0.5356</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.3397</v>
+        <v>-14.4612</v>
       </c>
     </row>
     <row r="12">
@@ -2967,10 +2967,10 @@
         <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5405</v>
+        <v>1.5731</v>
       </c>
       <c r="J12" t="n">
-        <v>41.5935</v>
+        <v>42.4737</v>
       </c>
     </row>
     <row r="13">
@@ -3007,10 +3007,10 @@
         <v>1.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.494</v>
+        <v>1.5291</v>
       </c>
       <c r="J13" t="n">
-        <v>40.338</v>
+        <v>41.2857</v>
       </c>
     </row>
     <row r="14">
@@ -3047,10 +3047,10 @@
         <v>1.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1035</v>
+        <v>0.083</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7945</v>
+        <v>2.241</v>
       </c>
     </row>
     <row r="15">
@@ -3087,10 +3087,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.603</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-16.281</v>
+        <v>-15.336</v>
       </c>
     </row>
     <row r="16">
@@ -3127,10 +3127,10 @@
         <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7381</v>
+        <v>-0.7124</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.9287</v>
+        <v>-19.2348</v>
       </c>
     </row>
     <row r="17">
@@ -3167,10 +3167,10 @@
         <v>1.19</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4403</v>
+        <v>0.3843</v>
       </c>
       <c r="J17" t="n">
-        <v>11.8881</v>
+        <v>10.3761</v>
       </c>
     </row>
     <row r="18">
@@ -3207,10 +3207,10 @@
         <v>1.07</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2093</v>
+        <v>0.1669</v>
       </c>
       <c r="J18" t="n">
-        <v>5.6511</v>
+        <v>4.5063</v>
       </c>
     </row>
     <row r="19">
@@ -3247,10 +3247,10 @@
         <v>1.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1644</v>
+        <v>0.1274</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4388</v>
+        <v>3.4398</v>
       </c>
     </row>
     <row r="20">
@@ -3287,10 +3287,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3486</v>
+        <v>-0.3334</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.4122</v>
+        <v>-9.001799999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3327,10 +3327,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4645</v>
+        <v>-0.4604</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.5415</v>
+        <v>-12.4308</v>
       </c>
     </row>
     <row r="22">
@@ -3367,10 +3367,10 @@
         <v>1.54</v>
       </c>
       <c r="I22" t="n">
-        <v>1.252</v>
+        <v>1.2777</v>
       </c>
       <c r="J22" t="n">
-        <v>32.552</v>
+        <v>33.2202</v>
       </c>
     </row>
     <row r="23">
@@ -3407,10 +3407,10 @@
         <v>1.22</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6072</v>
+        <v>0.5696</v>
       </c>
       <c r="J23" t="n">
-        <v>15.7872</v>
+        <v>14.8096</v>
       </c>
     </row>
     <row r="24">
@@ -3447,10 +3447,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2479</v>
+        <v>-0.2091</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.4454</v>
+        <v>-5.4366</v>
       </c>
     </row>
     <row r="25">
@@ -3487,10 +3487,10 @@
         <v>0.9</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3602</v>
+        <v>-0.3176</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.3652</v>
+        <v>-8.2576</v>
       </c>
     </row>
     <row r="26">
@@ -3527,10 +3527,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4628</v>
+        <v>-0.4204</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.0328</v>
+        <v>-10.9304</v>
       </c>
     </row>
     <row r="27">
@@ -3567,10 +3567,10 @@
         <v>1.11</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2814</v>
+        <v>0.2321</v>
       </c>
       <c r="J27" t="n">
-        <v>7.3164</v>
+        <v>6.0346</v>
       </c>
     </row>
     <row r="28">
@@ -3607,10 +3607,10 @@
         <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1782</v>
+        <v>0.1393</v>
       </c>
       <c r="J28" t="n">
-        <v>4.6332</v>
+        <v>3.6218</v>
       </c>
     </row>
     <row r="29">
@@ -3647,10 +3647,10 @@
         <v>0.91</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1316</v>
+        <v>-0.1133</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.4216</v>
+        <v>-2.9458</v>
       </c>
     </row>
     <row r="30">
@@ -3687,10 +3687,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1761</v>
+        <v>-0.1561</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.5786</v>
+        <v>-4.0586</v>
       </c>
     </row>
     <row r="31">
@@ -3727,10 +3727,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2281</v>
+        <v>-0.2078</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.9306</v>
+        <v>-5.4028</v>
       </c>
     </row>
     <row r="32">
@@ -3767,10 +3767,10 @@
         <v>1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>0.473</v>
+        <v>0.4265</v>
       </c>
       <c r="J32" t="n">
-        <v>12.771</v>
+        <v>11.5155</v>
       </c>
     </row>
     <row r="33">
@@ -3807,10 +3807,10 @@
         <v>1.18</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3858</v>
+        <v>0.3309</v>
       </c>
       <c r="J33" t="n">
-        <v>10.4166</v>
+        <v>8.9343</v>
       </c>
     </row>
     <row r="34">
@@ -3847,10 +3847,10 @@
         <v>1.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3161</v>
+        <v>0.2656</v>
       </c>
       <c r="J34" t="n">
-        <v>8.534700000000001</v>
+        <v>7.1712</v>
       </c>
     </row>
     <row r="35">
@@ -3887,10 +3887,10 @@
         <v>1.01</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0366</v>
+        <v>0.0256</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9882</v>
+        <v>0.6912</v>
       </c>
     </row>
     <row r="36">
@@ -3927,10 +3927,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2877</v>
+        <v>-0.2696</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.7679</v>
+        <v>-7.2792</v>
       </c>
     </row>
     <row r="37">
@@ -3967,10 +3967,10 @@
         <v>1.82</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4278</v>
+        <v>1.4562</v>
       </c>
       <c r="J37" t="n">
-        <v>38.5506</v>
+        <v>39.3174</v>
       </c>
     </row>
     <row r="38">
@@ -4007,10 +4007,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3793</v>
+        <v>0.3388</v>
       </c>
       <c r="J38" t="n">
-        <v>10.2411</v>
+        <v>9.147600000000001</v>
       </c>
     </row>
     <row r="39">
@@ -4047,10 +4047,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3006</v>
+        <v>-0.2593</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.116199999999999</v>
+        <v>-7.0011</v>
       </c>
     </row>
     <row r="40">
@@ -4087,10 +4087,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4824</v>
+        <v>-0.4401</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.0248</v>
+        <v>-11.8827</v>
       </c>
     </row>
     <row r="41">
@@ -4127,10 +4127,10 @@
         <v>0.62</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9887</v>
+        <v>-0.9853</v>
       </c>
       <c r="J41" t="n">
-        <v>-26.6949</v>
+        <v>-26.6031</v>
       </c>
     </row>
     <row r="42">
@@ -4167,10 +4167,10 @@
         <v>1.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2348</v>
+        <v>0.1901</v>
       </c>
       <c r="J42" t="n">
-        <v>7.044</v>
+        <v>5.703</v>
       </c>
     </row>
     <row r="43">
@@ -4207,10 +4207,10 @@
         <v>1.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0603</v>
+        <v>0.0418</v>
       </c>
       <c r="J43" t="n">
-        <v>1.809</v>
+        <v>1.254</v>
       </c>
     </row>
     <row r="44">
@@ -4247,10 +4247,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0919</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.757</v>
+        <v>-2.334</v>
       </c>
     </row>
     <row r="45">
@@ -4287,10 +4287,10 @@
         <v>0.89</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1499</v>
+        <v>-0.132</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.497</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="46">
@@ -4327,10 +4327,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.463</v>
+        <v>-0.4586</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.89</v>
+        <v>-13.758</v>
       </c>
     </row>
     <row r="47">
@@ -4367,10 +4367,10 @@
         <v>1.5</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9646</v>
+        <v>0.9512</v>
       </c>
       <c r="J47" t="n">
-        <v>28.938</v>
+        <v>28.536</v>
       </c>
     </row>
     <row r="48">
@@ -4407,10 +4407,10 @@
         <v>1.45</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8796</v>
       </c>
       <c r="J48" t="n">
-        <v>26.841</v>
+        <v>26.388</v>
       </c>
     </row>
     <row r="49">
@@ -4447,10 +4447,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1753</v>
+        <v>0.1486</v>
       </c>
       <c r="J49" t="n">
-        <v>5.259</v>
+        <v>4.458</v>
       </c>
     </row>
     <row r="50">
@@ -4487,10 +4487,10 @@
         <v>0.99</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0664</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.622</v>
+        <v>-1.992</v>
       </c>
     </row>
     <row r="51">
@@ -4527,10 +4527,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5255</v>
+        <v>-0.4861</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.765</v>
+        <v>-14.583</v>
       </c>
     </row>
     <row r="52">
@@ -4567,10 +4567,10 @@
         <v>1.31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5564</v>
+        <v>0.5296</v>
       </c>
       <c r="J52" t="n">
-        <v>16.1356</v>
+        <v>15.3584</v>
       </c>
     </row>
     <row r="53">
@@ -4607,10 +4607,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2995</v>
+        <v>0.2501</v>
       </c>
       <c r="J53" t="n">
-        <v>8.685499999999999</v>
+        <v>7.2529</v>
       </c>
     </row>
     <row r="54">
@@ -4647,10 +4647,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2812</v>
+        <v>0.2333</v>
       </c>
       <c r="J54" t="n">
-        <v>8.1548</v>
+        <v>6.7657</v>
       </c>
     </row>
     <row r="55">
@@ -4687,10 +4687,10 @@
         <v>0.92</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1285</v>
+        <v>-0.1094</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.7265</v>
+        <v>-3.1726</v>
       </c>
     </row>
     <row r="56">
@@ -4727,10 +4727,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2476</v>
+        <v>-0.2278</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.1804</v>
+        <v>-6.6062</v>
       </c>
     </row>
     <row r="57">
@@ -4767,10 +4767,10 @@
         <v>0.46</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.297</v>
+        <v>-1.338</v>
       </c>
       <c r="J57" t="n">
-        <v>-37.613</v>
+        <v>-38.802</v>
       </c>
     </row>
     <row r="58">
@@ -4807,10 +4807,10 @@
         <v>1.25</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6286</v>
+        <v>0.6148</v>
       </c>
       <c r="J58" t="n">
-        <v>18.2294</v>
+        <v>17.8292</v>
       </c>
     </row>
     <row r="59">
@@ -4847,10 +4847,10 @@
         <v>1.19</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5283</v>
+        <v>0.5148</v>
       </c>
       <c r="J59" t="n">
-        <v>15.3207</v>
+        <v>14.9292</v>
       </c>
     </row>
     <row r="60">
@@ -4887,10 +4887,10 @@
         <v>1.11</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3648</v>
+        <v>0.3227</v>
       </c>
       <c r="J60" t="n">
-        <v>10.5792</v>
+        <v>9.3583</v>
       </c>
     </row>
     <row r="61">
@@ -4927,10 +4927,10 @@
         <v>1.06</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2277</v>
+        <v>0.1917</v>
       </c>
       <c r="J61" t="n">
-        <v>6.6033</v>
+        <v>5.5593</v>
       </c>
     </row>
     <row r="62">
@@ -4967,10 +4967,10 @@
         <v>0.58</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.4677</v>
+        <v>-0.4676</v>
       </c>
       <c r="J62" t="n">
-        <v>-11.6925</v>
+        <v>-11.69</v>
       </c>
     </row>
     <row r="63">
@@ -5007,10 +5007,10 @@
         <v>1.61</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6595</v>
+        <v>0.6175</v>
       </c>
       <c r="J63" t="n">
-        <v>16.4875</v>
+        <v>15.4375</v>
       </c>
     </row>
     <row r="64">
@@ -5047,10 +5047,10 @@
         <v>1.37</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4771</v>
+        <v>0.4231</v>
       </c>
       <c r="J64" t="n">
-        <v>11.9275</v>
+        <v>10.5775</v>
       </c>
     </row>
     <row r="65">
@@ -5087,10 +5087,10 @@
         <v>1.33</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4432</v>
+        <v>0.382</v>
       </c>
       <c r="J65" t="n">
-        <v>11.08</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -5127,10 +5127,10 @@
         <v>1.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1105</v>
+        <v>0.0835</v>
       </c>
       <c r="J66" t="n">
-        <v>2.7625</v>
+        <v>2.0875</v>
       </c>
     </row>
     <row r="67">
@@ -5167,10 +5167,10 @@
         <v>0.58</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.4474</v>
+        <v>-0.4414</v>
       </c>
       <c r="J67" t="n">
-        <v>-11.185</v>
+        <v>-11.035</v>
       </c>
     </row>
     <row r="68">
@@ -5207,10 +5207,10 @@
         <v>1.09</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1962</v>
+        <v>0.1794</v>
       </c>
       <c r="J68" t="n">
-        <v>4.905</v>
+        <v>4.485</v>
       </c>
     </row>
     <row r="69">
@@ -5247,10 +5247,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.128</v>
+        <v>0.1112</v>
       </c>
       <c r="J69" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="70">
@@ -5287,10 +5287,10 @@
         <v>0.98</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0369</v>
+        <v>-0.0288</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.9225</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="71">
@@ -5327,10 +5327,10 @@
         <v>0.88</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1621</v>
+        <v>-0.1431</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.0525</v>
+        <v>-3.5775</v>
       </c>
     </row>
     <row r="72">
@@ -5367,10 +5367,10 @@
         <v>0.59</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.3962</v>
+        <v>-0.3906</v>
       </c>
       <c r="J72" t="n">
-        <v>-10.6974</v>
+        <v>-10.5462</v>
       </c>
     </row>
     <row r="73">
@@ -5407,10 +5407,10 @@
         <v>0.7</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2907</v>
+        <v>-0.2787</v>
       </c>
       <c r="J73" t="n">
-        <v>-7.8489</v>
+        <v>-7.5249</v>
       </c>
     </row>
     <row r="74">
@@ -5447,10 +5447,10 @@
         <v>0.6</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3872</v>
+        <v>-0.3812</v>
       </c>
       <c r="J74" t="n">
-        <v>-10.4544</v>
+        <v>-10.2924</v>
       </c>
     </row>
     <row r="75">
@@ -5487,10 +5487,10 @@
         <v>0.46</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5074</v>
+        <v>-0.5069</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.6998</v>
+        <v>-13.6863</v>
       </c>
     </row>
     <row r="76">
@@ -5527,10 +5527,10 @@
         <v>0.4</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5606</v>
+        <v>-0.5658</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.1362</v>
+        <v>-15.2766</v>
       </c>
     </row>
     <row r="77">
@@ -5567,10 +5567,10 @@
         <v>0.74</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.6906</v>
+        <v>-0.6571</v>
       </c>
       <c r="J77" t="n">
-        <v>-18.6462</v>
+        <v>-17.7417</v>
       </c>
     </row>
     <row r="78">
@@ -5607,10 +5607,10 @@
         <v>1.27</v>
       </c>
       <c r="I78" t="n">
-        <v>0.712</v>
+        <v>0.7047</v>
       </c>
       <c r="J78" t="n">
-        <v>19.224</v>
+        <v>19.0269</v>
       </c>
     </row>
     <row r="79">
@@ -5647,10 +5647,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5336</v>
+        <v>-0.4954</v>
       </c>
       <c r="J79" t="n">
-        <v>-14.4072</v>
+        <v>-13.3758</v>
       </c>
     </row>
     <row r="80">
@@ -5687,10 +5687,10 @@
         <v>0.75</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6686</v>
+        <v>-0.634</v>
       </c>
       <c r="J80" t="n">
-        <v>-18.0522</v>
+        <v>-17.118</v>
       </c>
     </row>
     <row r="81">
@@ -5727,10 +5727,10 @@
         <v>0.73</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7125</v>
+        <v>-0.6801</v>
       </c>
       <c r="J81" t="n">
-        <v>-19.2375</v>
+        <v>-18.3627</v>
       </c>
     </row>
     <row r="82">
@@ -5767,10 +5767,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6262</v>
+        <v>0.5666</v>
       </c>
       <c r="J82" t="n">
-        <v>18.786</v>
+        <v>16.998</v>
       </c>
     </row>
     <row r="83">
@@ -5807,10 +5807,10 @@
         <v>1.3</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="J83" t="n">
-        <v>17.403</v>
+        <v>15.606</v>
       </c>
     </row>
     <row r="84">
@@ -5847,10 +5847,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2612</v>
+        <v>0.2155</v>
       </c>
       <c r="J84" t="n">
-        <v>7.836</v>
+        <v>6.465</v>
       </c>
     </row>
     <row r="85">
@@ -5887,10 +5887,10 @@
         <v>0.85</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2074</v>
+        <v>-0.1869</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.222</v>
+        <v>-5.607</v>
       </c>
     </row>
     <row r="86">
@@ -5927,10 +5927,10 @@
         <v>0.75</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3068</v>
+        <v>-0.2898</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.204000000000001</v>
+        <v>-8.694000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5967,10 +5967,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8425</v>
+        <v>0.8203</v>
       </c>
       <c r="J87" t="n">
-        <v>25.275</v>
+        <v>24.609</v>
       </c>
     </row>
     <row r="88">
@@ -6007,10 +6007,10 @@
         <v>1.21</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6029</v>
+        <v>0.5642</v>
       </c>
       <c r="J88" t="n">
-        <v>18.087</v>
+        <v>16.926</v>
       </c>
     </row>
     <row r="89">
@@ -6047,10 +6047,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.173</v>
+        <v>-0.1403</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.19</v>
+        <v>-4.209</v>
       </c>
     </row>
     <row r="90">
@@ -6087,10 +6087,10 @@
         <v>0.83</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5221</v>
+        <v>-0.4805</v>
       </c>
       <c r="J90" t="n">
-        <v>-15.663</v>
+        <v>-14.415</v>
       </c>
     </row>
     <row r="91">
@@ -6127,10 +6127,10 @@
         <v>0.8</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5925</v>
+        <v>-0.5535</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.775</v>
+        <v>-16.605</v>
       </c>
     </row>
     <row r="92">
@@ -6167,10 +6167,10 @@
         <v>0.89</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0496</v>
+        <v>-0.0074</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.9424</v>
+        <v>-0.1406</v>
       </c>
     </row>
     <row r="93">
@@ -6207,10 +6207,10 @@
         <v>0.62</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.3563</v>
+        <v>-0.3491</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.7697</v>
+        <v>-6.6329</v>
       </c>
     </row>
     <row r="94">
@@ -6247,10 +6247,10 @@
         <v>0.35</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.597</v>
+        <v>-0.6069</v>
       </c>
       <c r="J94" t="n">
-        <v>-11.343</v>
+        <v>-11.5311</v>
       </c>
     </row>
     <row r="95">
@@ -6287,10 +6287,10 @@
         <v>0.32</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.6243</v>
+        <v>-0.6383</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.8617</v>
+        <v>-12.1277</v>
       </c>
     </row>
     <row r="96">
@@ -6327,10 +6327,10 @@
         <v>0.32</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6243</v>
+        <v>-0.6383</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.8617</v>
+        <v>-12.1277</v>
       </c>
     </row>
     <row r="97">
@@ -6367,10 +6367,10 @@
         <v>1.82</v>
       </c>
       <c r="I97" t="n">
-        <v>1.442</v>
+        <v>1.4719</v>
       </c>
       <c r="J97" t="n">
-        <v>27.398</v>
+        <v>27.9661</v>
       </c>
     </row>
     <row r="98">
@@ -6407,10 +6407,10 @@
         <v>1.74</v>
       </c>
       <c r="I98" t="n">
-        <v>1.3476</v>
+        <v>1.3734</v>
       </c>
       <c r="J98" t="n">
-        <v>25.6044</v>
+        <v>26.0946</v>
       </c>
     </row>
     <row r="99">
@@ -6447,10 +6447,10 @@
         <v>1.59</v>
       </c>
       <c r="I99" t="n">
-        <v>1.1683</v>
+        <v>1.19</v>
       </c>
       <c r="J99" t="n">
-        <v>22.1977</v>
+        <v>22.61</v>
       </c>
     </row>
     <row r="100">
@@ -6487,10 +6487,10 @@
         <v>1.48</v>
       </c>
       <c r="I100" t="n">
-        <v>1.0267</v>
+        <v>1.0417</v>
       </c>
       <c r="J100" t="n">
-        <v>19.5073</v>
+        <v>19.7923</v>
       </c>
     </row>
     <row r="101">
@@ -6527,10 +6527,10 @@
         <v>1.38</v>
       </c>
       <c r="I101" t="n">
-        <v>0.8555</v>
+        <v>0.8505</v>
       </c>
       <c r="J101" t="n">
-        <v>16.2545</v>
+        <v>16.1595</v>
       </c>
     </row>
     <row r="102">
@@ -6567,10 +6567,10 @@
         <v>0.93</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.0852</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.7838</v>
+        <v>-1.5336</v>
       </c>
     </row>
     <row r="103">
@@ -6607,10 +6607,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1115</v>
+        <v>-0.0968</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.007</v>
+        <v>-1.7424</v>
       </c>
     </row>
     <row r="104">
@@ -6647,10 +6647,10 @@
         <v>0.86</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1785</v>
+        <v>-0.1608</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.213</v>
+        <v>-2.8944</v>
       </c>
     </row>
     <row r="105">
@@ -6687,10 +6687,10 @@
         <v>0.83</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2084</v>
+        <v>-0.1899</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.7512</v>
+        <v>-3.4182</v>
       </c>
     </row>
     <row r="106">
@@ -6727,10 +6727,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3418</v>
+        <v>-0.3261</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.1524</v>
+        <v>-5.8698</v>
       </c>
     </row>
     <row r="107">
@@ -6767,10 +6767,10 @@
         <v>1.04</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0433</v>
+        <v>0.0262</v>
       </c>
       <c r="J107" t="n">
-        <v>0.7794</v>
+        <v>0.4716</v>
       </c>
     </row>
     <row r="108">
@@ -6807,10 +6807,10 @@
         <v>2.44</v>
       </c>
       <c r="I108" t="n">
-        <v>1.3428</v>
+        <v>1.4785</v>
       </c>
       <c r="J108" t="n">
-        <v>24.1704</v>
+        <v>26.613</v>
       </c>
     </row>
     <row r="109">
@@ -6847,10 +6847,10 @@
         <v>1.98</v>
       </c>
       <c r="I109" t="n">
-        <v>1.048</v>
+        <v>1.1395</v>
       </c>
       <c r="J109" t="n">
-        <v>18.864</v>
+        <v>20.511</v>
       </c>
     </row>
     <row r="110">
@@ -6887,10 +6887,10 @@
         <v>1.62</v>
       </c>
       <c r="I110" t="n">
-        <v>0.7362</v>
+        <v>0.7901</v>
       </c>
       <c r="J110" t="n">
-        <v>13.2516</v>
+        <v>14.2218</v>
       </c>
     </row>
     <row r="111">
@@ -6927,10 +6927,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0615</v>
+        <v>0.0441</v>
       </c>
       <c r="J111" t="n">
-        <v>1.107</v>
+        <v>0.7938</v>
       </c>
     </row>
     <row r="112">
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.9197</v>
+        <v>-1.0086</v>
       </c>
       <c r="J112" t="n">
-        <v>-37.7077</v>
+        <v>-41.3526</v>
       </c>
     </row>
     <row r="113">
@@ -7007,10 +7007,10 @@
         <v>0.78</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1283</v>
+        <v>-0.0743</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.2603</v>
+        <v>-3.0463</v>
       </c>
     </row>
     <row r="114">
@@ -7047,10 +7047,10 @@
         <v>0.55</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3931</v>
+        <v>-0.3881</v>
       </c>
       <c r="J114" t="n">
-        <v>-16.1171</v>
+        <v>-15.9121</v>
       </c>
     </row>
     <row r="115">
@@ -7087,10 +7087,10 @@
         <v>0.43</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5098</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="J115" t="n">
-        <v>-20.9018</v>
+        <v>-21.1396</v>
       </c>
     </row>
     <row r="116">
@@ -7127,10 +7127,10 @@
         <v>0.27</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.653</v>
+        <v>-0.6708</v>
       </c>
       <c r="J116" t="n">
-        <v>-26.773</v>
+        <v>-27.5028</v>
       </c>
     </row>
     <row r="117">
@@ -7167,10 +7167,10 @@
         <v>0.64</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.9084</v>
+        <v>-0.8914</v>
       </c>
       <c r="J117" t="n">
-        <v>-37.2444</v>
+        <v>-36.5474</v>
       </c>
     </row>
     <row r="118">
@@ -7207,10 +7207,10 @@
         <v>1.52</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2468</v>
+        <v>1.2869</v>
       </c>
       <c r="J118" t="n">
-        <v>51.1188</v>
+        <v>52.7629</v>
       </c>
     </row>
     <row r="119">
@@ -7247,10 +7247,10 @@
         <v>0.87</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3954</v>
+        <v>-0.3574</v>
       </c>
       <c r="J119" t="n">
-        <v>-16.2114</v>
+        <v>-14.6534</v>
       </c>
     </row>
     <row r="120">
@@ -7287,10 +7287,10 @@
         <v>0.75</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6724</v>
+        <v>-0.6377</v>
       </c>
       <c r="J120" t="n">
-        <v>-27.5684</v>
+        <v>-26.1457</v>
       </c>
     </row>
     <row r="121">
@@ -7327,10 +7327,10 @@
         <v>0.6</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.9913999999999999</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>-40.6474</v>
+        <v>-40.3194</v>
       </c>
     </row>
     <row r="122">
@@ -7367,10 +7367,10 @@
         <v>0.64</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.3951</v>
+        <v>-0.3837</v>
       </c>
       <c r="J122" t="n">
-        <v>-8.2971</v>
+        <v>-8.057700000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7407,10 +7407,10 @@
         <v>1.19</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4366</v>
+        <v>0.3803</v>
       </c>
       <c r="J123" t="n">
-        <v>9.1686</v>
+        <v>7.9863</v>
       </c>
     </row>
     <row r="124">
@@ -7447,10 +7447,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1845</v>
+        <v>0.1448</v>
       </c>
       <c r="J124" t="n">
-        <v>3.8745</v>
+        <v>3.0408</v>
       </c>
     </row>
     <row r="125">
@@ -7487,10 +7487,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0678</v>
+        <v>-0.0556</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.4238</v>
+        <v>-1.1676</v>
       </c>
     </row>
     <row r="126">
@@ -7527,10 +7527,10 @@
         <v>0.77</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2746</v>
+        <v>-0.2555</v>
       </c>
       <c r="J126" t="n">
-        <v>-5.7666</v>
+        <v>-5.3655</v>
       </c>
     </row>
     <row r="127">
@@ -7567,10 +7567,10 @@
         <v>0.83</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.1776</v>
+        <v>-0.0396</v>
       </c>
       <c r="J127" t="n">
-        <v>-3.7296</v>
+        <v>-0.8316</v>
       </c>
     </row>
     <row r="128">
@@ -7607,10 +7607,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.9064</v>
+        <v>-0.9065</v>
       </c>
       <c r="J128" t="n">
-        <v>-19.0344</v>
+        <v>-19.0365</v>
       </c>
     </row>
     <row r="129">
@@ -7647,10 +7647,10 @@
         <v>0.27</v>
       </c>
       <c r="I129" t="n">
-        <v>-1.5274</v>
+        <v>-1.5905</v>
       </c>
       <c r="J129" t="n">
-        <v>-32.0754</v>
+        <v>-33.4005</v>
       </c>
     </row>
     <row r="130">
@@ -7687,10 +7687,10 @@
         <v>0.24</v>
       </c>
       <c r="I130" t="n">
-        <v>-1.5939</v>
+        <v>-1.6701</v>
       </c>
       <c r="J130" t="n">
-        <v>-33.4719</v>
+        <v>-35.0721</v>
       </c>
     </row>
     <row r="131">
@@ -7727,10 +7727,10 @@
         <v>0.21</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.661</v>
+        <v>-1.752</v>
       </c>
       <c r="J131" t="n">
-        <v>-34.881</v>
+        <v>-36.792</v>
       </c>
     </row>
     <row r="132">
@@ -7767,10 +7767,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0142</v>
+        <v>1.0143</v>
       </c>
       <c r="J132" t="n">
-        <v>35.497</v>
+        <v>35.5005</v>
       </c>
     </row>
     <row r="133">
@@ -7807,10 +7807,10 @@
         <v>1.17</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4955</v>
+        <v>0.4552</v>
       </c>
       <c r="J133" t="n">
-        <v>17.3425</v>
+        <v>15.932</v>
       </c>
     </row>
     <row r="134">
@@ -7847,10 +7847,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4005</v>
+        <v>0.3605</v>
       </c>
       <c r="J134" t="n">
-        <v>14.0175</v>
+        <v>12.6175</v>
       </c>
     </row>
     <row r="135">
@@ -7887,10 +7887,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0464</v>
+        <v>0.0349</v>
       </c>
       <c r="J135" t="n">
-        <v>1.624</v>
+        <v>1.2215</v>
       </c>
     </row>
     <row r="136">
@@ -7927,10 +7927,10 @@
         <v>0.7</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8258</v>
+        <v>-0.8047</v>
       </c>
       <c r="J136" t="n">
-        <v>-28.903</v>
+        <v>-28.1645</v>
       </c>
     </row>
     <row r="137">
@@ -7967,10 +7967,10 @@
         <v>1.2</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4342</v>
+        <v>0.3766</v>
       </c>
       <c r="J137" t="n">
-        <v>15.197</v>
+        <v>13.181</v>
       </c>
     </row>
     <row r="138">
@@ -8007,10 +8007,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3822</v>
+        <v>0.3267</v>
       </c>
       <c r="J138" t="n">
-        <v>13.377</v>
+        <v>11.4345</v>
       </c>
     </row>
     <row r="139">
@@ -8047,10 +8047,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2722</v>
+        <v>0.2239</v>
       </c>
       <c r="J139" t="n">
-        <v>9.526999999999999</v>
+        <v>7.8365</v>
       </c>
     </row>
     <row r="140">
@@ -8087,10 +8087,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1002</v>
+        <v>0.074</v>
       </c>
       <c r="J140" t="n">
-        <v>3.507</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="141">
@@ -8127,10 +8127,10 @@
         <v>0.48</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5396</v>
+        <v>-0.547</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.886</v>
+        <v>-19.145</v>
       </c>
     </row>
     <row r="142">
@@ -8167,10 +8167,10 @@
         <v>1.52</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1482</v>
+        <v>1.1622</v>
       </c>
       <c r="J142" t="n">
-        <v>29.8532</v>
+        <v>30.2172</v>
       </c>
     </row>
     <row r="143">
@@ -8207,10 +8207,10 @@
         <v>1.41</v>
       </c>
       <c r="I143" t="n">
-        <v>0.984</v>
+        <v>0.9778</v>
       </c>
       <c r="J143" t="n">
-        <v>25.584</v>
+        <v>25.4228</v>
       </c>
     </row>
     <row r="144">
@@ -8247,10 +8247,10 @@
         <v>1.21</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5766</v>
+        <v>0.5396</v>
       </c>
       <c r="J144" t="n">
-        <v>14.9916</v>
+        <v>14.0296</v>
       </c>
     </row>
     <row r="145">
@@ -8287,10 +8287,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6364</v>
+        <v>-0.6015</v>
       </c>
       <c r="J145" t="n">
-        <v>-16.5464</v>
+        <v>-15.639</v>
       </c>
     </row>
     <row r="146">
@@ -8327,10 +8327,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7695</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>-20.007</v>
+        <v>-19.357</v>
       </c>
     </row>
     <row r="147">
@@ -8367,10 +8367,10 @@
         <v>1.33</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6403</v>
+        <v>0.5818</v>
       </c>
       <c r="J147" t="n">
-        <v>16.6478</v>
+        <v>15.1268</v>
       </c>
     </row>
     <row r="148">
@@ -8407,10 +8407,10 @@
         <v>1.08</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2102</v>
+        <v>0.1683</v>
       </c>
       <c r="J148" t="n">
-        <v>5.4652</v>
+        <v>4.3758</v>
       </c>
     </row>
     <row r="149">
@@ -8447,10 +8447,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0984</v>
+        <v>0.073</v>
       </c>
       <c r="J149" t="n">
-        <v>2.5584</v>
+        <v>1.898</v>
       </c>
     </row>
     <row r="150">
@@ -8487,10 +8487,10 @@
         <v>0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1594</v>
+        <v>-0.1393</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.1444</v>
+        <v>-3.6218</v>
       </c>
     </row>
     <row r="151">
@@ -8527,10 +8527,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3117</v>
+        <v>-0.2945</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.104200000000001</v>
+        <v>-7.657</v>
       </c>
     </row>
     <row r="152">
@@ -8567,10 +8567,10 @@
         <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.9111</v>
       </c>
       <c r="J152" t="n">
-        <v>26.8511</v>
+        <v>26.4219</v>
       </c>
     </row>
     <row r="153">
@@ -8607,10 +8607,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5659</v>
+        <v>0.5266</v>
       </c>
       <c r="J153" t="n">
-        <v>16.4111</v>
+        <v>15.2714</v>
       </c>
     </row>
     <row r="154">
@@ -8647,10 +8647,10 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0118</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.3422</v>
+        <v>-0.2291</v>
       </c>
     </row>
     <row r="155">
@@ -8687,10 +8687,10 @@
         <v>0.96</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.183</v>
+        <v>-0.1488</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.307</v>
+        <v>-4.3152</v>
       </c>
     </row>
     <row r="156">
@@ -8727,10 +8727,10 @@
         <v>0.86</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4601</v>
+        <v>-0.4175</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.3429</v>
+        <v>-12.1075</v>
       </c>
     </row>
     <row r="157">
@@ -8767,10 +8767,10 @@
         <v>1.29</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5915</v>
+        <v>0.5335</v>
       </c>
       <c r="J157" t="n">
-        <v>17.1535</v>
+        <v>15.4715</v>
       </c>
     </row>
     <row r="158">
@@ -8807,10 +8807,10 @@
         <v>1.07</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1976</v>
+        <v>0.1564</v>
       </c>
       <c r="J158" t="n">
-        <v>5.7304</v>
+        <v>4.5356</v>
       </c>
     </row>
     <row r="159">
@@ -8847,10 +8847,10 @@
         <v>0.98</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.041</v>
+        <v>-0.0317</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.189</v>
+        <v>-0.9193</v>
       </c>
     </row>
     <row r="160">
@@ -8887,10 +8887,10 @@
         <v>0.83</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2191</v>
+        <v>-0.1986</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.3539</v>
+        <v>-5.7594</v>
       </c>
     </row>
     <row r="161">
@@ -8927,10 +8927,10 @@
         <v>0.66</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.381</v>
+        <v>-0.3687</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.049</v>
+        <v>-10.6923</v>
       </c>
     </row>
     <row r="162">
@@ -8967,10 +8967,10 @@
         <v>1.27</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4072</v>
+        <v>0.4056</v>
       </c>
       <c r="J162" t="n">
-        <v>19.1384</v>
+        <v>19.0632</v>
       </c>
     </row>
     <row r="163">
@@ -9007,10 +9007,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3704</v>
+        <v>0.3655</v>
       </c>
       <c r="J163" t="n">
-        <v>17.4088</v>
+        <v>17.1785</v>
       </c>
     </row>
     <row r="164">
@@ -9047,10 +9047,10 @@
         <v>1.15</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2548</v>
+        <v>0.2431</v>
       </c>
       <c r="J164" t="n">
-        <v>11.9756</v>
+        <v>11.4257</v>
       </c>
     </row>
     <row r="165">
@@ -9087,10 +9087,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0859</v>
+        <v>0.0747</v>
       </c>
       <c r="J165" t="n">
-        <v>4.0373</v>
+        <v>3.5109</v>
       </c>
     </row>
     <row r="166">
@@ -9127,10 +9127,10 @@
         <v>0.99</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0354</v>
+        <v>-0.0261</v>
       </c>
       <c r="J166" t="n">
-        <v>-1.6638</v>
+        <v>-1.2267</v>
       </c>
     </row>
     <row r="167">
@@ -9167,10 +9167,10 @@
         <v>1.05</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1159</v>
+        <v>0.0844</v>
       </c>
       <c r="J167" t="n">
-        <v>5.4473</v>
+        <v>3.9668</v>
       </c>
     </row>
     <row r="168">
@@ -9207,10 +9207,10 @@
         <v>0.97</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0556</v>
+        <v>-0.0443</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.6132</v>
+        <v>-2.0821</v>
       </c>
     </row>
     <row r="169">
@@ -9247,10 +9247,10 @@
         <v>0.96</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0698</v>
+        <v>-0.0568</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.2806</v>
+        <v>-2.6696</v>
       </c>
     </row>
     <row r="170">
@@ -9287,10 +9287,10 @@
         <v>0.91</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1315</v>
+        <v>-0.1132</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.1805</v>
+        <v>-5.3204</v>
       </c>
     </row>
     <row r="171">
@@ -9327,10 +9327,10 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1759</v>
+        <v>-0.1559</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.267300000000001</v>
+        <v>-7.3273</v>
       </c>
     </row>
     <row r="172">
@@ -9367,10 +9367,10 @@
         <v>1.82</v>
       </c>
       <c r="I172" t="n">
-        <v>1.464</v>
+        <v>1.4931</v>
       </c>
       <c r="J172" t="n">
-        <v>29.28</v>
+        <v>29.862</v>
       </c>
     </row>
     <row r="173">
@@ -9407,10 +9407,10 @@
         <v>1.76</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3914</v>
+        <v>1.4162</v>
       </c>
       <c r="J173" t="n">
-        <v>27.828</v>
+        <v>28.324</v>
       </c>
     </row>
     <row r="174">
@@ -9447,10 +9447,10 @@
         <v>1.35</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8175</v>
+        <v>0.8061</v>
       </c>
       <c r="J174" t="n">
-        <v>16.35</v>
+        <v>16.122</v>
       </c>
     </row>
     <row r="175">
@@ -9487,10 +9487,10 @@
         <v>1.24</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5961</v>
+        <v>0.5713</v>
       </c>
       <c r="J175" t="n">
-        <v>11.922</v>
+        <v>11.426</v>
       </c>
     </row>
     <row r="176">
@@ -9527,10 +9527,10 @@
         <v>1.11</v>
       </c>
       <c r="I176" t="n">
-        <v>0.2959</v>
+        <v>0.2629</v>
       </c>
       <c r="J176" t="n">
-        <v>5.918</v>
+        <v>5.258</v>
       </c>
     </row>
     <row r="177">
@@ -9567,10 +9567,10 @@
         <v>0.88</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1253</v>
+        <v>-0.1077</v>
       </c>
       <c r="J177" t="n">
-        <v>-2.506</v>
+        <v>-2.154</v>
       </c>
     </row>
     <row r="178">
@@ -9607,10 +9607,10 @@
         <v>0.74</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2755</v>
+        <v>-0.2624</v>
       </c>
       <c r="J178" t="n">
-        <v>-5.51</v>
+        <v>-5.248</v>
       </c>
     </row>
     <row r="179">
@@ -9647,10 +9647,10 @@
         <v>0.74</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2755</v>
+        <v>-0.2624</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.51</v>
+        <v>-5.248</v>
       </c>
     </row>
     <row r="180">
@@ -9687,10 +9687,10 @@
         <v>0.49</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4975</v>
+        <v>-0.4954</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.949999999999999</v>
+        <v>-9.907999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -9727,10 +9727,10 @@
         <v>0.45</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5326</v>
+        <v>-0.5347</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.652</v>
+        <v>-10.694</v>
       </c>
     </row>
     <row r="182">
@@ -9767,10 +9767,10 @@
         <v>1.16</v>
       </c>
       <c r="I182" t="n">
-        <v>0.486</v>
+        <v>0.4439</v>
       </c>
       <c r="J182" t="n">
-        <v>19.926</v>
+        <v>18.1999</v>
       </c>
     </row>
     <row r="183">
@@ -9807,10 +9807,10 @@
         <v>1.03</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1318</v>
+        <v>0.1056</v>
       </c>
       <c r="J183" t="n">
-        <v>5.4038</v>
+        <v>4.3296</v>
       </c>
     </row>
     <row r="184">
@@ -9847,10 +9847,10 @@
         <v>1.02</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0965</v>
+        <v>0.0752</v>
       </c>
       <c r="J184" t="n">
-        <v>3.9565</v>
+        <v>3.0832</v>
       </c>
     </row>
     <row r="185">
@@ -9887,10 +9887,10 @@
         <v>0.98</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1035</v>
+        <v>-0.0791</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.2435</v>
+        <v>-3.2431</v>
       </c>
     </row>
     <row r="186">
@@ -9927,10 +9927,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2353</v>
+        <v>-0.1976</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.6473</v>
+        <v>-8.101599999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9967,10 +9967,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8414</v>
+        <v>0.7905</v>
       </c>
       <c r="J187" t="n">
-        <v>34.4974</v>
+        <v>32.4105</v>
       </c>
     </row>
     <row r="188">
@@ -10007,10 +10007,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2065</v>
+        <v>0.1658</v>
       </c>
       <c r="J188" t="n">
-        <v>8.4665</v>
+        <v>6.7978</v>
       </c>
     </row>
     <row r="189">
@@ -10047,10 +10047,10 @@
         <v>0.99</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0278</v>
+        <v>-0.0197</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.1398</v>
+        <v>-0.8077</v>
       </c>
     </row>
     <row r="190">
@@ -10087,10 +10087,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1617</v>
+        <v>-0.1414</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.6297</v>
+        <v>-5.7974</v>
       </c>
     </row>
     <row r="191">
@@ -10127,10 +10127,10 @@
         <v>0.77</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2853</v>
+        <v>-0.2669</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.6973</v>
+        <v>-10.9429</v>
       </c>
     </row>
     <row r="192">
@@ -10167,10 +10167,10 @@
         <v>1.44</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0245</v>
+        <v>1.0256</v>
       </c>
       <c r="J192" t="n">
-        <v>26.637</v>
+        <v>26.6656</v>
       </c>
     </row>
     <row r="193">
@@ -10207,10 +10207,10 @@
         <v>1.36</v>
       </c>
       <c r="I193" t="n">
-        <v>0.8801</v>
+        <v>0.8607</v>
       </c>
       <c r="J193" t="n">
-        <v>22.8826</v>
+        <v>22.3782</v>
       </c>
     </row>
     <row r="194">
@@ -10247,10 +10247,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4144</v>
+        <v>0.3785</v>
       </c>
       <c r="J194" t="n">
-        <v>10.7744</v>
+        <v>9.840999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10287,10 +10287,10 @@
         <v>1.05</v>
       </c>
       <c r="I195" t="n">
-        <v>0.175</v>
+        <v>0.1483</v>
       </c>
       <c r="J195" t="n">
-        <v>4.55</v>
+        <v>3.8558</v>
       </c>
     </row>
     <row r="196">
@@ -10327,10 +10327,10 @@
         <v>0.85</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5016</v>
+        <v>-0.4615</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.0416</v>
+        <v>-11.999</v>
       </c>
     </row>
     <row r="197">
@@ -10367,10 +10367,10 @@
         <v>1.46</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8601</v>
+        <v>0.8163</v>
       </c>
       <c r="J197" t="n">
-        <v>22.3626</v>
+        <v>21.2238</v>
       </c>
     </row>
     <row r="198">
@@ -10407,10 +10407,10 @@
         <v>0.92</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1195</v>
+        <v>-0.1021</v>
       </c>
       <c r="J198" t="n">
-        <v>-3.107</v>
+        <v>-2.6546</v>
       </c>
     </row>
     <row r="199">
@@ -10447,10 +10447,10 @@
         <v>0.89</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1538</v>
+        <v>-0.1345</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.9988</v>
+        <v>-3.497</v>
       </c>
     </row>
     <row r="200">
@@ -10487,10 +10487,10 @@
         <v>0.87</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1756</v>
+        <v>-0.1556</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.5656</v>
+        <v>-4.0456</v>
       </c>
     </row>
     <row r="201">
@@ -10527,10 +10527,10 @@
         <v>0.6</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4328</v>
+        <v>-0.4254</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.2528</v>
+        <v>-11.0604</v>
       </c>
     </row>
     <row r="202">
@@ -10567,10 +10567,10 @@
         <v>1.47</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0582</v>
+        <v>1.0649</v>
       </c>
       <c r="J202" t="n">
-        <v>26.455</v>
+        <v>26.6225</v>
       </c>
     </row>
     <row r="203">
@@ -10607,10 +10607,10 @@
         <v>1.32</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7893</v>
+        <v>0.765</v>
       </c>
       <c r="J203" t="n">
-        <v>19.7325</v>
+        <v>19.125</v>
       </c>
     </row>
     <row r="204">
@@ -10647,10 +10647,10 @@
         <v>1.26</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6681</v>
+        <v>0.6381</v>
       </c>
       <c r="J204" t="n">
-        <v>16.7025</v>
+        <v>15.9525</v>
       </c>
     </row>
     <row r="205">
@@ -10687,10 +10687,10 @@
         <v>1.19</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5216</v>
+        <v>0.4883</v>
       </c>
       <c r="J205" t="n">
-        <v>13.04</v>
+        <v>12.2075</v>
       </c>
     </row>
     <row r="206">
@@ -10727,10 +10727,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4861</v>
+        <v>-0.4467</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.1525</v>
+        <v>-11.1675</v>
       </c>
     </row>
     <row r="207">
@@ -10767,10 +10767,10 @@
         <v>1.19</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4409</v>
+        <v>0.385</v>
       </c>
       <c r="J207" t="n">
-        <v>11.0225</v>
+        <v>9.625</v>
       </c>
     </row>
     <row r="208">
@@ -10807,10 +10807,10 @@
         <v>0.99</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0183</v>
+        <v>-0.0135</v>
       </c>
       <c r="J208" t="n">
-        <v>-0.4575</v>
+        <v>-0.3375</v>
       </c>
     </row>
     <row r="209">
@@ -10847,10 +10847,10 @@
         <v>0.95</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0669</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.005</v>
+        <v>-1.6725</v>
       </c>
     </row>
     <row r="210">
@@ -10887,10 +10887,10 @@
         <v>0.89</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1508</v>
+        <v>-0.1325</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.77</v>
+        <v>-3.3125</v>
       </c>
     </row>
     <row r="211">
@@ -10927,10 +10927,10 @@
         <v>0.53</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4902</v>
+        <v>-0.4894</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.255</v>
+        <v>-12.235</v>
       </c>
     </row>
     <row r="212">
@@ -10967,10 +10967,10 @@
         <v>1.84</v>
       </c>
       <c r="I212" t="n">
-        <v>1.4712</v>
+        <v>1.5018</v>
       </c>
       <c r="J212" t="n">
-        <v>27.9528</v>
+        <v>28.5342</v>
       </c>
     </row>
     <row r="213">
@@ -11007,10 +11007,10 @@
         <v>1.55</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1219</v>
+        <v>1.1418</v>
       </c>
       <c r="J213" t="n">
-        <v>21.3161</v>
+        <v>21.6942</v>
       </c>
     </row>
     <row r="214">
@@ -11047,10 +11047,10 @@
         <v>1.54</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1095</v>
+        <v>1.1294</v>
       </c>
       <c r="J214" t="n">
-        <v>21.0805</v>
+        <v>21.4586</v>
       </c>
     </row>
     <row r="215">
@@ -11087,10 +11087,10 @@
         <v>1.49</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0448</v>
+        <v>1.0606</v>
       </c>
       <c r="J215" t="n">
-        <v>19.8512</v>
+        <v>20.1514</v>
       </c>
     </row>
     <row r="216">
@@ -11127,10 +11127,10 @@
         <v>1.38</v>
       </c>
       <c r="I216" t="n">
-        <v>0.861</v>
+        <v>0.8556</v>
       </c>
       <c r="J216" t="n">
-        <v>16.359</v>
+        <v>16.2564</v>
       </c>
     </row>
     <row r="217">
@@ -11167,10 +11167,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.0173</v>
+        <v>0.0193</v>
       </c>
       <c r="J217" t="n">
-        <v>-0.3287</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="218">
@@ -11207,10 +11207,10 @@
         <v>0.66</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3361</v>
+        <v>-0.327</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.3859</v>
+        <v>-6.213</v>
       </c>
     </row>
     <row r="219">
@@ -11247,10 +11247,10 @@
         <v>0.59</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3998</v>
+        <v>-0.3931</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.5962</v>
+        <v>-7.4689</v>
       </c>
     </row>
     <row r="220">
@@ -11287,10 +11287,10 @@
         <v>0.42</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5467</v>
+        <v>-0.5502</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.3873</v>
+        <v>-10.4538</v>
       </c>
     </row>
     <row r="221">
@@ -11327,10 +11327,10 @@
         <v>0.26</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6889</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.0891</v>
+        <v>-13.6078</v>
       </c>
     </row>
     <row r="222">
@@ -11367,10 +11367,10 @@
         <v>1.14</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4306</v>
+        <v>0.389</v>
       </c>
       <c r="J222" t="n">
-        <v>11.6262</v>
+        <v>10.503</v>
       </c>
     </row>
     <row r="223">
@@ -11407,10 +11407,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3559</v>
+        <v>0.3155</v>
       </c>
       <c r="J223" t="n">
-        <v>9.609299999999999</v>
+        <v>8.5185</v>
       </c>
     </row>
     <row r="224">
@@ -11447,10 +11447,10 @@
         <v>1.06</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2214</v>
+        <v>0.1879</v>
       </c>
       <c r="J224" t="n">
-        <v>5.9778</v>
+        <v>5.0733</v>
       </c>
     </row>
     <row r="225">
@@ -11487,10 +11487,10 @@
         <v>0.99</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0675</v>
+        <v>-0.0486</v>
       </c>
       <c r="J225" t="n">
-        <v>-1.8225</v>
+        <v>-1.3122</v>
       </c>
     </row>
     <row r="226">
@@ -11527,10 +11527,10 @@
         <v>0.98</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1087</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.9349</v>
+        <v>-2.2437</v>
       </c>
     </row>
     <row r="227">
@@ -11567,10 +11567,10 @@
         <v>1.37</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="J227" t="n">
-        <v>18.522</v>
+        <v>16.9425</v>
       </c>
     </row>
     <row r="228">
@@ -11607,10 +11607,10 @@
         <v>1.32</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6105</v>
+        <v>0.5507</v>
       </c>
       <c r="J228" t="n">
-        <v>16.4835</v>
+        <v>14.8689</v>
       </c>
     </row>
     <row r="229">
@@ -11647,10 +11647,10 @@
         <v>1.19</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4025</v>
+        <v>0.3467</v>
       </c>
       <c r="J229" t="n">
-        <v>10.8675</v>
+        <v>9.360900000000001</v>
       </c>
     </row>
     <row r="230">
@@ -11687,10 +11687,10 @@
         <v>0.82</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2385</v>
+        <v>-0.2185</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.4395</v>
+        <v>-5.8995</v>
       </c>
     </row>
     <row r="231">
@@ -11727,10 +11727,10 @@
         <v>0.65</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3987</v>
+        <v>-0.3891</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.7649</v>
+        <v>-10.5057</v>
       </c>
     </row>
     <row r="232">
@@ -11767,10 +11767,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2308</v>
+        <v>1.2489</v>
       </c>
       <c r="J232" t="n">
-        <v>36.924</v>
+        <v>37.467</v>
       </c>
     </row>
     <row r="233">
@@ -11807,10 +11807,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3707</v>
+        <v>0.3338</v>
       </c>
       <c r="J233" t="n">
-        <v>11.121</v>
+        <v>10.014</v>
       </c>
     </row>
     <row r="234">
@@ -11847,10 +11847,10 @@
         <v>1.07</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2399</v>
+        <v>0.2084</v>
       </c>
       <c r="J234" t="n">
-        <v>7.197</v>
+        <v>6.252</v>
       </c>
     </row>
     <row r="235">
@@ -11887,10 +11887,10 @@
         <v>1.01</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0383</v>
+        <v>0.0279</v>
       </c>
       <c r="J235" t="n">
-        <v>1.149</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="236">
@@ -11927,10 +11927,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.42</v>
+        <v>-0.3777</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.6</v>
+        <v>-11.331</v>
       </c>
     </row>
     <row r="237">
@@ -11967,10 +11967,10 @@
         <v>1.09</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2579</v>
+        <v>0.2114</v>
       </c>
       <c r="J237" t="n">
-        <v>7.737</v>
+        <v>6.342</v>
       </c>
     </row>
     <row r="238">
@@ -12007,10 +12007,10 @@
         <v>0.9</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1387</v>
+        <v>-0.1216</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.161</v>
+        <v>-3.648</v>
       </c>
     </row>
     <row r="239">
@@ -12047,10 +12047,10 @@
         <v>0.89</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1496</v>
+        <v>-0.1319</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.488</v>
+        <v>-3.957</v>
       </c>
     </row>
     <row r="240">
@@ -12087,10 +12087,10 @@
         <v>0.83</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2119</v>
+        <v>-0.1923</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.357</v>
+        <v>-5.769</v>
       </c>
     </row>
     <row r="241">
@@ -12127,10 +12127,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3091</v>
+        <v>-0.2914</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.273</v>
+        <v>-8.742000000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12167,10 +12167,10 @@
         <v>0.85</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.4655</v>
+        <v>-0.4229</v>
       </c>
       <c r="J242" t="n">
-        <v>-12.5685</v>
+        <v>-11.4183</v>
       </c>
     </row>
     <row r="243">
@@ -12207,10 +12207,10 @@
         <v>0.68</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.8484</v>
+        <v>-0.8272</v>
       </c>
       <c r="J243" t="n">
-        <v>-22.9068</v>
+        <v>-22.3344</v>
       </c>
     </row>
     <row r="244">
@@ -12247,10 +12247,10 @@
         <v>0.57</v>
       </c>
       <c r="I244" t="n">
-        <v>-1.0751</v>
+        <v>-1.0806</v>
       </c>
       <c r="J244" t="n">
-        <v>-29.0277</v>
+        <v>-29.1762</v>
       </c>
     </row>
     <row r="245">
@@ -12287,10 +12287,10 @@
         <v>1.51</v>
       </c>
       <c r="I245" t="n">
-        <v>1.1821</v>
+        <v>1.2049</v>
       </c>
       <c r="J245" t="n">
-        <v>31.9167</v>
+        <v>32.5323</v>
       </c>
     </row>
     <row r="246">
@@ -12327,10 +12327,10 @@
         <v>1.31</v>
       </c>
       <c r="I246" t="n">
-        <v>0.8368</v>
+        <v>0.8155</v>
       </c>
       <c r="J246" t="n">
-        <v>22.5936</v>
+        <v>22.0185</v>
       </c>
     </row>
     <row r="247">
@@ -12367,10 +12367,10 @@
         <v>1.16</v>
       </c>
       <c r="I247" t="n">
-        <v>0.397</v>
+        <v>0.3436</v>
       </c>
       <c r="J247" t="n">
-        <v>10.719</v>
+        <v>9.277200000000001</v>
       </c>
     </row>
     <row r="248">
@@ -12407,10 +12407,10 @@
         <v>0.72</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.3174</v>
+        <v>-0.3002</v>
       </c>
       <c r="J248" t="n">
-        <v>-8.569800000000001</v>
+        <v>-8.105399999999999</v>
       </c>
     </row>
     <row r="249">
@@ -12447,10 +12447,10 @@
         <v>0.37</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.6421</v>
       </c>
       <c r="J249" t="n">
-        <v>-16.8075</v>
+        <v>-17.3367</v>
       </c>
     </row>
     <row r="250">
@@ -12487,10 +12487,10 @@
         <v>1.12</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3211</v>
+        <v>0.2707</v>
       </c>
       <c r="J250" t="n">
-        <v>8.669700000000001</v>
+        <v>7.3089</v>
       </c>
     </row>
     <row r="251">
@@ -12527,10 +12527,10 @@
         <v>1.02</v>
       </c>
       <c r="I251" t="n">
-        <v>0.0955</v>
+        <v>0.0701</v>
       </c>
       <c r="J251" t="n">
-        <v>2.5785</v>
+        <v>1.8927</v>
       </c>
     </row>
     <row r="252">
@@ -12567,10 +12567,10 @@
         <v>0.8</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.5784</v>
+        <v>-0.5387</v>
       </c>
       <c r="J252" t="n">
-        <v>-16.7736</v>
+        <v>-15.6223</v>
       </c>
     </row>
     <row r="253">
@@ -12607,10 +12607,10 @@
         <v>0.67</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.864</v>
+        <v>-0.8438</v>
       </c>
       <c r="J253" t="n">
-        <v>-25.056</v>
+        <v>-24.4702</v>
       </c>
     </row>
     <row r="254">
@@ -12647,10 +12647,10 @@
         <v>0.67</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.864</v>
+        <v>-0.8438</v>
       </c>
       <c r="J254" t="n">
-        <v>-25.056</v>
+        <v>-24.4702</v>
       </c>
     </row>
     <row r="255">
@@ -12687,10 +12687,10 @@
         <v>1.5</v>
       </c>
       <c r="I255" t="n">
-        <v>1.1781</v>
+        <v>1.2026</v>
       </c>
       <c r="J255" t="n">
-        <v>34.1649</v>
+        <v>34.8754</v>
       </c>
     </row>
     <row r="256">
@@ -12727,10 +12727,10 @@
         <v>1.15</v>
       </c>
       <c r="I256" t="n">
-        <v>0.4818</v>
+        <v>0.4394</v>
       </c>
       <c r="J256" t="n">
-        <v>13.9722</v>
+        <v>12.7426</v>
       </c>
     </row>
     <row r="257">
@@ -12767,10 +12767,10 @@
         <v>0.88</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.1612</v>
+        <v>-0.1425</v>
       </c>
       <c r="J257" t="n">
-        <v>-4.6748</v>
+        <v>-4.1325</v>
       </c>
     </row>
     <row r="258">
@@ -12807,10 +12807,10 @@
         <v>0.86</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1824</v>
+        <v>-0.163</v>
       </c>
       <c r="J258" t="n">
-        <v>-5.2896</v>
+        <v>-4.727</v>
       </c>
     </row>
     <row r="259">
@@ -12847,10 +12847,10 @@
         <v>0.61</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4199</v>
+        <v>-0.4107</v>
       </c>
       <c r="J259" t="n">
-        <v>-12.1771</v>
+        <v>-11.9103</v>
       </c>
     </row>
     <row r="260">
@@ -12887,10 +12887,10 @@
         <v>1.14</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3517</v>
+        <v>0.2988</v>
       </c>
       <c r="J260" t="n">
-        <v>10.1993</v>
+        <v>8.6652</v>
       </c>
     </row>
     <row r="261">
@@ -12927,10 +12927,10 @@
         <v>1.03</v>
       </c>
       <c r="I261" t="n">
-        <v>0.1169</v>
+        <v>0.0871</v>
       </c>
       <c r="J261" t="n">
-        <v>3.3901</v>
+        <v>2.5259</v>
       </c>
     </row>
     <row r="262">
@@ -12967,10 +12967,10 @@
         <v>1.64</v>
       </c>
       <c r="I262" t="n">
-        <v>1.272</v>
+        <v>1.2899</v>
       </c>
       <c r="J262" t="n">
-        <v>29.256</v>
+        <v>29.6677</v>
       </c>
     </row>
     <row r="263">
@@ -13007,10 +13007,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9664</v>
+        <v>0.9601</v>
       </c>
       <c r="J263" t="n">
-        <v>22.2272</v>
+        <v>22.0823</v>
       </c>
     </row>
     <row r="264">
@@ -13047,10 +13047,10 @@
         <v>1.3</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7398</v>
+        <v>0.7164</v>
       </c>
       <c r="J264" t="n">
-        <v>17.0154</v>
+        <v>16.4772</v>
       </c>
     </row>
     <row r="265">
@@ -13087,10 +13087,10 @@
         <v>1.27</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6813</v>
+        <v>0.6553</v>
       </c>
       <c r="J265" t="n">
-        <v>15.6699</v>
+        <v>15.0719</v>
       </c>
     </row>
     <row r="266">
@@ -13127,10 +13127,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.5845</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.1772</v>
+        <v>-13.4435</v>
       </c>
     </row>
     <row r="267">
@@ -13167,10 +13167,10 @@
         <v>1.07</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2288</v>
+        <v>0.1868</v>
       </c>
       <c r="J267" t="n">
-        <v>5.2624</v>
+        <v>4.2964</v>
       </c>
     </row>
     <row r="268">
@@ -13207,10 +13207,10 @@
         <v>1.06</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2063</v>
+        <v>0.1665</v>
       </c>
       <c r="J268" t="n">
-        <v>4.7449</v>
+        <v>3.8295</v>
       </c>
     </row>
     <row r="269">
@@ -13247,10 +13247,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2568</v>
+        <v>-0.2382</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.9064</v>
+        <v>-5.4786</v>
       </c>
     </row>
     <row r="270">
@@ -13287,10 +13287,10 @@
         <v>0.68</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3505</v>
+        <v>-0.3353</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.061500000000001</v>
+        <v>-7.7119</v>
       </c>
     </row>
     <row r="271">
@@ -13327,10 +13327,10 @@
         <v>0.62</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4047</v>
+        <v>-0.3937</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.3081</v>
+        <v>-9.055099999999999</v>
       </c>
     </row>
     <row r="272">
@@ -13367,10 +13367,10 @@
         <v>1.55</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1706</v>
+        <v>1.1844</v>
       </c>
       <c r="J272" t="n">
-        <v>31.6062</v>
+        <v>31.9788</v>
       </c>
     </row>
     <row r="273">
@@ -13407,10 +13407,10 @@
         <v>1.3</v>
       </c>
       <c r="I273" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7245</v>
       </c>
       <c r="J273" t="n">
-        <v>20.2905</v>
+        <v>19.5615</v>
       </c>
     </row>
     <row r="274">
@@ -13447,10 +13447,10 @@
         <v>1.29</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7312</v>
+        <v>0.7033</v>
       </c>
       <c r="J274" t="n">
-        <v>19.7424</v>
+        <v>18.9891</v>
       </c>
     </row>
     <row r="275">
@@ -13487,10 +13487,10 @@
         <v>1.18</v>
       </c>
       <c r="I275" t="n">
-        <v>0.501</v>
+        <v>0.4668</v>
       </c>
       <c r="J275" t="n">
-        <v>13.527</v>
+        <v>12.6036</v>
       </c>
     </row>
     <row r="276">
@@ -13527,10 +13527,10 @@
         <v>0.72</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8037</v>
+        <v>-0.7839</v>
       </c>
       <c r="J276" t="n">
-        <v>-21.6999</v>
+        <v>-21.1653</v>
       </c>
     </row>
     <row r="277">
@@ -13567,10 +13567,10 @@
         <v>1.06</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1863</v>
+        <v>0.1465</v>
       </c>
       <c r="J277" t="n">
-        <v>5.0301</v>
+        <v>3.9555</v>
       </c>
     </row>
     <row r="278">
@@ -13607,10 +13607,10 @@
         <v>1.02</v>
       </c>
       <c r="I278" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0624</v>
       </c>
       <c r="J278" t="n">
-        <v>2.349</v>
+        <v>1.6848</v>
       </c>
     </row>
     <row r="279">
@@ -13647,10 +13647,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0117</v>
+        <v>0.0077</v>
       </c>
       <c r="J279" t="n">
-        <v>0.3159</v>
+        <v>0.2079</v>
       </c>
     </row>
     <row r="280">
@@ -13687,10 +13687,10 @@
         <v>0.8</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2445</v>
+        <v>-0.2247</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.6015</v>
+        <v>-6.0669</v>
       </c>
     </row>
     <row r="281">
@@ -13727,10 +13727,10 @@
         <v>0.7</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3398</v>
+        <v>-0.324</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.1746</v>
+        <v>-8.747999999999999</v>
       </c>
     </row>
     <row r="282">
@@ -13767,10 +13767,10 @@
         <v>0.99</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.0589</v>
+        <v>-0.0428</v>
       </c>
       <c r="J282" t="n">
-        <v>-2.1204</v>
+        <v>-1.5408</v>
       </c>
     </row>
     <row r="283">
@@ -13807,10 +13807,10 @@
         <v>0.96</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1691</v>
+        <v>-0.1375</v>
       </c>
       <c r="J283" t="n">
-        <v>-6.0876</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="284">
@@ -13847,10 +13847,10 @@
         <v>0.91</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3155</v>
+        <v>-0.2744</v>
       </c>
       <c r="J284" t="n">
-        <v>-11.358</v>
+        <v>-9.878399999999999</v>
       </c>
     </row>
     <row r="285">
@@ -13887,10 +13887,10 @@
         <v>1.09</v>
       </c>
       <c r="I285" t="n">
-        <v>0.3147</v>
+        <v>0.2737</v>
       </c>
       <c r="J285" t="n">
-        <v>11.3292</v>
+        <v>9.853199999999999</v>
       </c>
     </row>
     <row r="286">
@@ -13927,10 +13927,10 @@
         <v>1.06</v>
       </c>
       <c r="I286" t="n">
-        <v>0.23</v>
+        <v>0.1934</v>
       </c>
       <c r="J286" t="n">
-        <v>8.279999999999999</v>
+        <v>6.9624</v>
       </c>
     </row>
     <row r="287">
@@ -13967,10 +13967,10 @@
         <v>0.78</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.2602</v>
+        <v>-0.241</v>
       </c>
       <c r="J287" t="n">
-        <v>-9.3672</v>
+        <v>-8.676</v>
       </c>
     </row>
     <row r="288">
@@ -14007,10 +14007,10 @@
         <v>0.61</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.4171</v>
+        <v>-0.4075</v>
       </c>
       <c r="J288" t="n">
-        <v>-15.0156</v>
+        <v>-14.67</v>
       </c>
     </row>
     <row r="289">
@@ -14047,10 +14047,10 @@
         <v>0.33</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.6554</v>
+        <v>-0.6811</v>
       </c>
       <c r="J289" t="n">
-        <v>-23.5944</v>
+        <v>-24.5196</v>
       </c>
     </row>
     <row r="290">
@@ -14087,10 +14087,10 @@
         <v>1.34</v>
       </c>
       <c r="I290" t="n">
-        <v>0.705</v>
+        <v>0.6571</v>
       </c>
       <c r="J290" t="n">
-        <v>25.38</v>
+        <v>23.6556</v>
       </c>
     </row>
     <row r="291">
@@ -14127,10 +14127,10 @@
         <v>1.32</v>
       </c>
       <c r="I291" t="n">
-        <v>0.6727</v>
+        <v>0.6231</v>
       </c>
       <c r="J291" t="n">
-        <v>24.2172</v>
+        <v>22.4316</v>
       </c>
     </row>
     <row r="292">
@@ -14167,10 +14167,10 @@
         <v>0.76</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.2677</v>
+        <v>-0.2519</v>
       </c>
       <c r="J292" t="n">
-        <v>-6.1571</v>
+        <v>-5.7937</v>
       </c>
     </row>
     <row r="293">
@@ -14207,10 +14207,10 @@
         <v>0.74</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.2855</v>
+        <v>-0.2698</v>
       </c>
       <c r="J293" t="n">
-        <v>-6.5665</v>
+        <v>-6.2054</v>
       </c>
     </row>
     <row r="294">
@@ -14247,10 +14247,10 @@
         <v>0.58</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.4293</v>
+        <v>-0.4203</v>
       </c>
       <c r="J294" t="n">
-        <v>-9.873900000000001</v>
+        <v>-9.6669</v>
       </c>
     </row>
     <row r="295">
@@ -14287,10 +14287,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1553</v>
+        <v>-0.1397</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.5719</v>
+        <v>-3.2131</v>
       </c>
     </row>
     <row r="296">
@@ -14327,10 +14327,10 @@
         <v>0.78</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2488</v>
+        <v>-0.2331</v>
       </c>
       <c r="J296" t="n">
-        <v>-5.7224</v>
+        <v>-5.3613</v>
       </c>
     </row>
     <row r="297">
@@ -14367,10 +14367,10 @@
         <v>0.46</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.5465</v>
+        <v>-0.5531</v>
       </c>
       <c r="J297" t="n">
-        <v>-12.5695</v>
+        <v>-12.7213</v>
       </c>
     </row>
     <row r="298">
@@ -14407,10 +14407,10 @@
         <v>0.23</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.7366</v>
+        <v>-0.7792</v>
       </c>
       <c r="J298" t="n">
-        <v>-16.9418</v>
+        <v>-17.9216</v>
       </c>
     </row>
     <row r="299">
@@ -14447,10 +14447,10 @@
         <v>0.21</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.7528</v>
+        <v>-0.799</v>
       </c>
       <c r="J299" t="n">
-        <v>-17.3144</v>
+        <v>-18.377</v>
       </c>
     </row>
     <row r="300">
@@ -14487,10 +14487,10 @@
         <v>2</v>
       </c>
       <c r="I300" t="n">
-        <v>1.1801</v>
+        <v>1.1846</v>
       </c>
       <c r="J300" t="n">
-        <v>27.1423</v>
+        <v>27.2458</v>
       </c>
     </row>
     <row r="301">
@@ -14527,10 +14527,10 @@
         <v>1.45</v>
       </c>
       <c r="I301" t="n">
-        <v>0.6543</v>
+        <v>0.5956</v>
       </c>
       <c r="J301" t="n">
-        <v>15.0489</v>
+        <v>13.6988</v>
       </c>
     </row>
     <row r="302">
@@ -14567,10 +14567,10 @@
         <v>1.21</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5994</v>
+        <v>0.5606</v>
       </c>
       <c r="J302" t="n">
-        <v>17.3826</v>
+        <v>16.2574</v>
       </c>
     </row>
     <row r="303">
@@ -14607,10 +14607,10 @@
         <v>0.95</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2069</v>
+        <v>-0.1711</v>
       </c>
       <c r="J303" t="n">
-        <v>-6.0001</v>
+        <v>-4.9619</v>
       </c>
     </row>
     <row r="304">
@@ -14647,10 +14647,10 @@
         <v>0.78</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="J304" t="n">
-        <v>-18.5774</v>
+        <v>-17.5247</v>
       </c>
     </row>
     <row r="305">
@@ -14687,10 +14687,10 @@
         <v>1.13</v>
       </c>
       <c r="I305" t="n">
-        <v>0.4104</v>
+        <v>0.3683</v>
       </c>
       <c r="J305" t="n">
-        <v>11.9016</v>
+        <v>10.6807</v>
       </c>
     </row>
     <row r="306">
@@ -14727,10 +14727,10 @@
         <v>1.11</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3599</v>
+        <v>0.3186</v>
       </c>
       <c r="J306" t="n">
-        <v>10.4371</v>
+        <v>9.2394</v>
       </c>
     </row>
     <row r="307">
@@ -14767,10 +14767,10 @@
         <v>1.1</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2376</v>
+        <v>0.1963</v>
       </c>
       <c r="J307" t="n">
-        <v>6.8904</v>
+        <v>5.6927</v>
       </c>
     </row>
     <row r="308">
@@ -14807,10 +14807,10 @@
         <v>0.98</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0521</v>
+        <v>-0.0399</v>
       </c>
       <c r="J308" t="n">
-        <v>-1.5109</v>
+        <v>-1.1571</v>
       </c>
     </row>
     <row r="309">
@@ -14847,10 +14847,10 @@
         <v>0.98</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0521</v>
+        <v>-0.0399</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.5109</v>
+        <v>-1.1571</v>
       </c>
     </row>
     <row r="310">
@@ -14887,10 +14887,10 @@
         <v>1.57</v>
       </c>
       <c r="I310" t="n">
-        <v>0.9545</v>
+        <v>0.9101</v>
       </c>
       <c r="J310" t="n">
-        <v>27.6805</v>
+        <v>26.3929</v>
       </c>
     </row>
     <row r="311">
@@ -14927,10 +14927,10 @@
         <v>0.99</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.0343</v>
+        <v>-0.0251</v>
       </c>
       <c r="J311" t="n">
-        <v>-0.9947</v>
+        <v>-0.7279</v>
       </c>
     </row>
   </sheetData>
